--- a/References/Madhyasth-Darshan/KD-Karm-Darshan-English/KD-Translation-Glossary.xlsx
+++ b/References/Madhyasth-Darshan/KD-Karm-Darshan-English/KD-Translation-Glossary.xlsx
@@ -60817,7 +60817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D173"/>
+  <dimension ref="A1:D186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" style="114" min="1" max="1"/>
@@ -60851,1007 +60851,1007 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>मध्यांश</t>
+          <t>वस्तुस्थिति सत्य, वस्तुगत सत्य, स्थिति सत्य</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>madhyansh</t>
+          <t>vastusthiti satya, vastugat satya, sthiti satya</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nucleus</t>
+          <t>relative truth, objective truth, absolute truth</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Settled per Raghava (July 2026); KD 3.1/3.11 core term: the central particle(s) of the atom</t>
+          <t>Base-alignment correction (2026-10-04): KD p.3 distributes the shared सत्य across these three terms. MD-Mapping Sheet1 rows103/102/101 give these equivalents; the former existent-state/objective/context rendering lost the established triad.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>प्रस्थापन</t>
+          <t>अधम मध्यम</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>prasthapan</t>
+          <t>adham madhyam</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>absorption (absorbed)</t>
+          <t>low-to-intermediate (provisional)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Settled per Raghava (July 2026); KD 3.1: particle absorbed into an atom (paired with visthapan)</t>
+          <t>KD p.4 prints the kama/artha ranks as उत्तम अधम मध्यम without clarifying punctuation. The local compound reading is plausible, but the stated sevenfold count does not by itself prove it. Preserve the uncertainty; do not silently repair the Hindi.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>विस्थापन</t>
+          <t>विभव</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>visthapan</t>
+          <t>vibhav</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>displacement (displaced/shed)</t>
+          <t>sustainment</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Settled per Raghava (July 2026); KD 3.1: particle shed from an excited atom</t>
+          <t>Base-alignment correction (2026-10-04): MD-Mapping Sheet1 row761; MVD printed/PDF p.82 directly pairs उद्भव–विभव–प्रलय with creation–sustainment–dissolution and describes awakened tradition as human sustainment. Applied to reviewed KD Chapter1 occurrences, replacing potency; वैभव remains grandeur. No change to unrelated शक्ति or क्षमता.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>सत्यता</t>
+          <t>तिरोभाव</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>satyata</t>
+          <t>tirobhav</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>truthfulness</t>
+          <t>disappearance (contextual)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Settled per Raghava (July 2026): "truthfulness", overriding MD-Mapping's "verity". Aligns with JV and KD usage; distinguishes सत्य = truth from सत्यता = truthfulness.</t>
+          <t>MD-Mapping Sheet1 row1305 gives disappearance/annihilation. Source-image review (2026-10-04) uses disappearance for the absence/presence passage on p.23 and retains tirobhav alongside it on p.139. Do not merge with प्रलय = dissolution or supply a death/salvation mechanism.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>प्रसन्नता</t>
+          <t>सप्त धातु, सप्त-धातु</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>prasannata</t>
+          <t>sapt-dhatu</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>happiness</t>
+          <t>seven dhatus</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Settled per Raghava (July 2026): "happiness" (noun), "happily" (adverb for प्रसन्नतापूर्वक). Aligns with MVD, JV, and MD-Mapping (overriding legacy "gladness").</t>
+          <t>Base-alignment correction (2026-10-04): KD p.142; MD-Mapping Sheet1 row283 retains sapt-dhatu. Replaces seven metals (elements), which imposed a specific material interpretation not warranted by this source clause.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>आवेशित</t>
+          <t>व्यंजनीयता</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>aveshit</t>
+          <t>vyanjaniyata</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>excited</t>
+          <t>impressionability</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Settled per Raghava (2026-08-23): the disturbed motion or state of a unit is **excited**, in contrast to natural-state motion. This keeps the adjective aligned with आवेश = excitation. KD p.124's battery wording "charge/charged" translates the Hindi loanword चार्ज, not आवेश, and therefore remains unchanged.</t>
+          <t>Base-alignment correction (2026-10-04), KD pp.16–17: MD-Mapping Sheet1 B603 gives Impressionability; directly inspected MVD printed/PDF p.318 uses impressionability and defines व्यंजना as Impression. Related adjectival constructions use capacity for impression. This is not a replacement for अभिव्यक्ति or प्रकाशन elsewhere.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>आवेश</t>
+          <t>स्थितिवत्ता</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>avesh</t>
+          <t>sthitivatta</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>excitation</t>
+          <t>state-fullness (provisional)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Settled per Raghava (2026-08-23): use **excitation** for आवेश throughout KD, including generative-degenerative excitation. This supersedes the former excitation/charge contextual split. The literal battery term चार्ज on KD p.124 remains **charge**.</t>
+          <t>Retained on KD p.17 after source-image review (2026-10-04); the source's repeated copulas establish relations, not necessarily a temporal sequence. A precise contextual English equivalent remains unresolved.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>मात्रा</t>
+          <t>आगम क्रिया</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>matra</t>
+          <t>agam kriya</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>measure</t>
+          <t>testimony-activity (provisional), with agam kriya</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Settled per Raghava (2026-08-23): use **measure** for the noun मात्रा, including chapter 3.9, unit-measure, root measure, and the measure principle. Keep **quantity** for राशि, including राशि विधि = the arrangement of quantity; मात्रात्मक remains the established adjective **quantitative**.</t>
+          <t>KD p.20 defines this as existence beyond the possibility of proximity. Source-image review (2026-10-04) preserves that unusual definition. MD-Mapping B410 leaves aagam transliterated; do not import an external epistemological account of scriptural testimony as though established here.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>श्रम</t>
+          <t>परिणामशीलता</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>shram</t>
+          <t>parinamsheelta</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>effort</t>
+          <t>continually arising results / process of result (contextual, provisional)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Per MD-Mapping ("effort, physical labour"), whose notes state: "We are using 'effort' for shram in the sense of shram-gati-parinam." "Labour" only in economic compounds (श्रम मूल्य \= evaluation of labour, श्रम विनिमय \= exchange of labour, श्रम नियोजन \= utilisation of labour — updated 2026-07-08 per MVD; these compounds have not yet appeared in translated KD text). KD 3.11 (p. 117): श्रम-गति-परिणाम triad → "effort, motion, and result" — aligned with MVD/SB "Effort – Motion – Result"; effort \= grandeur of the existent-state, motion \= spreading of effect, result \= grandeur of a different existent-state</t>
+          <t>Source-image review (2026-10-04): KD p.22 does not say result-fullness. MVD printed/PDF p.26 translates the related परिणामशील in continuous activity of effort, motion, and result. P.22 now preserves continuity rather than fullness, while p.152 retains the conservative process of result. These local renderings do not settle a universal English equivalent.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>पोषण</t>
+          <t>मध्यांश</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>poshan</t>
+          <t>madhyansh</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>nourishment</t>
+          <t>nucleus</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Settled per Raghava (2026-08-23). Use **nourishment** for the noun, including relational uses ("provides nourishment to"); ordinary grammatical derivatives such as "nourishing" remain available where the Hindi is adjectival. This deliberately prefers the KD source's nourishment sense over MD-Mapping's bare "nurturing" row; पोषक remains "nourisher" and is not collapsed into this noun.</t>
+          <t>Settled per Raghava (July 2026); KD 3.1/3.11 core term: the central particle(s) of the atom</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>अनुकूल</t>
+          <t>प्रस्थापन</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>anukul</t>
+          <t>prasthapan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>aligned / favourable (contextual)</t>
+          <t>absorption (absorbed)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Settled per Raghava (2026-08-23): **aligned** when one faculty, activity, or result functions in relation to another. KD 1 p.15 therefore reads "endeavour aligned with knowledge, work aligned with endeavour, result aligned with work, realisation aligned with result, and knowledge aligned with realisation." Keep **favourable** for environmental/circumstantial uses such as अनुकूल वातावरण. Supersedes the opaque "consonant with" chain; MD-Mapping's bare row is "conducive."</t>
+          <t>Settled per Raghava (July 2026); KD 3.1: particle absorbed into an atom (paired with visthapan)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>प्रयास, प्रयत्न</t>
+          <t>विस्थापन</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>prayas, prayatna</t>
+          <t>visthapan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>endeavour</t>
+          <t>displacement (displaced/shed)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Settled per Raghava (2026-08-23), with the standard British spelling **endeavour**. Reserve **effort** for श्रम in the श्रम–गति–परिणाम / Effort–Motion–Result sense. Where यत्न and प्रयत्न occur together (KD 3.16 p.143), distinguish them as "attempt and endeavour." Matches MD-Mapping's प्रयास = "endeavour."</t>
+          <t>Settled per Raghava (July 2026); KD 3.1: particle shed from an excited atom</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>प्रयोग</t>
+          <t>सत्यता</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>prayog</t>
+          <t>satyata</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>application / apply</t>
+          <t>truthfulness</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Settled per Raghava (2026-08-23). Use **application** as the noun and **apply** as the verb, including scientific passages; supersedes "experiment / experimentation." This is an explicit KD terminology choice differing from MD-Mapping and Rakesh's frequent "experiment / experimentation" rendering.</t>
+          <t>Settled per Raghava (July 2026): "truthfulness", overriding MD-Mapping's "verity". Aligns with JV and KD usage; distinguishes सत्य = truth from सत्यता = truthfulness.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>द्वेष</t>
+          <t>सत्यानुभूति</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>dvesh</t>
+          <t>satyanubhuti</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>malice</t>
+          <t>Experiencing Truth</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Aligned 2026-08-23 with MVD's direct definition: "Malice (*dvesh*)" is imagining one's happiness only in the destruction of others. Use **malice** in राग–द्वेष and ईर्ष्या–द्वेष contexts too. Keep घृणा = **hatred** where the two occur separately in the same list (KD 2 p.41), and विद्वेष = **hostility**. Supersedes both "hatred" and "aversion" for द्वेष.</t>
+          <t>Settled per Raghava (2026-08-31) for KD 1 p.3; supersedes "true experiencing" and renders the compound as an active experiential attainment. Source-image review (2026-10-04) also restored this rendering for सत्यानुभूति on p.29, replacing true realisation.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>भोग</t>
+          <t>प्रसन्नता</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>bhog</t>
+          <t>prasannata</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>enjoyment</t>
+          <t>happiness</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Confirmed per Raghava (2026-08-23) for bare भोग in KD (e.g. भोग एवं बहुभोगवादी जीवन; भोग परिणाम). Contextual distinctions remain: फल भोगना = **experience consequences/results**; भोक्ता = **enjoyer**; उपभोग = **consumption**. Rakesh's MVD often uses "indulgence" or "sensory enjoyments" for bare/compound भोग, while JV commonly uses "consumption" for उपभोग; KD deliberately retains **enjoyment** for bare भोग.</t>
+          <t>Settled per Raghava (July 2026): "happiness" (noun), "happily" (adverb for प्रसन्नतापूर्वक). Aligns with MVD, JV, and MD-Mapping (overriding legacy "gladness").</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>योगाभ्यास, योग्याभ्यास</t>
+          <t>आवेशित</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>yogabhyas, yogyabhyas</t>
+          <t>aveshit</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>study of yoga</t>
+          <t>excited</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Settled per Raghava (2026-08-23) for both forms on KD 1 p.18. Keep **yoga** transliterated in English rather than translating the technical term as "union"; render the full term as **study of yoga**. Supersedes "yoga-practice" and "union-worthy practice." The following source explanation मिलन का अभ्यास remains translated compositionally as "the study of meeting."</t>
+          <t>Settled per Raghava (2026-08-23): the disturbed motion or state of a unit is **excited**, in contrast to natural-state motion. This keeps the adjective aligned with आवेश = excitation. KD p.124's battery wording "charge/charged" translates the Hindi loanword चार्ज, not आवेश, and therefore remains unchanged.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>सत्यान्वेषण, ऐषणान्वेषण, विषयान्वेषण</t>
+          <t>आवेश</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>satyanveshan, eshananveshan, vishayanveshan</t>
+          <t>avesh</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>truth-oriented exploration, motive-oriented exploration, instincts-oriented exploration</t>
+          <t>excitation</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Settled 2026-08-23 after source-image review of KD 1 pp.4–6. The exact compounds do not occur in MVD/JV; the rendering is compositional and aligns their established base vocabulary: सत्य = truth, ऐषणा = motive, विषय = instincts, अन्वेषण = exploration. Supersedes truth-/desire-/object-investigation. Their collective अन्वेषण-त्रय is **exploration-trio**.</t>
+          <t>Settled per Raghava (2026-08-23): use **excitation** for आवेश throughout KD, including generative-degenerative excitation. This supersedes the former excitation/charge contextual split. The literal battery term चार्ज on KD p.124 remains **charge**.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>अच्छी दूरी</t>
+          <t>मात्रा</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>acchi doori</t>
+          <t>matra</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>good distance</t>
+          <t>measure</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>KD: equilibrium separation maintained by the nucleus / between bodies</t>
+          <t>Settled per Raghava (2026-08-23): use **measure** for the noun मात्रा, including chapter 3.9, unit-measure, root measure, and the measure principle. Keep **quantity** for राशि, including राशि विधि = the arrangement of quantity; मात्रात्मक remains the established adjective **quantitative**.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>विन्यास</t>
+          <t>श्रम</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>vinyas</t>
+          <t>shram</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>*vinyas* (contextual gloss: arrangement; unresolved)</t>
+          <t>effort</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>DEFERRED REVIEW (2026-08-23): retain the transliteration and current contextual gloss pending explicit review of its technical physical sense. KD 3.11 presents weight/falling as *vinyas* evidencing coexistence; do not promote **arrangement** to a settled technical equivalent.</t>
+          <t>Per MD-Mapping ("effort, physical labour"), whose notes state: "We are using 'effort' for shram in the sense of shram-gati-parinam." "Labour" only in economic compounds (श्रम मूल्य \= evaluation of labour, श्रम विनिमय \= exchange of labour, श्रम नियोजन \= utilisation of labour — updated 2026-07-08 per MVD; these compounds have not yet appeared in translated KD text). KD 3.11 (p. 117): श्रम-गति-परिणाम triad → "effort, motion, and result" — aligned with MVD/SB "Effort – Motion – Result"; effort \= grandeur of the existent-state, motion \= spreading of effect, result \= grandeur of a different existent-state</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>मध्यस्थीयकरण</t>
+          <t>परिश्रम</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>madhyasthiyakaran</t>
+          <t>pariśram</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>mediation</t>
+          <t>diligence (refined effort)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>KD 3.11: what modern force/power studies are said to deny</t>
+          <t>KD 2 p. 30 explicitly supplies परिश्रम (परिमार्जित श्रम). Source-image review (2026-10-04) restored the definition refined effort alongside the established diligence label. This is a local source gloss, not a replacement of प्रयास / प्रयत्न = endeavour or श्रम = effort.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>चुम्बकीय धारा</t>
+          <t>उत्सव</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>chumbakiya dhara</t>
+          <t>utsav</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>magnetic current</t>
+          <t>"festival" (literal, provisional)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>KD 3.13: electricity = flow from its fragmentation</t>
+          <t>KD 3.16 p. 137 visibly reads दो प्रजाति के प्राणकोषों का उत्सव. Source-image review (2026-10-04) retained the unusual wording and two species without inferring fusion, fertilisation, gametes, or the two sexes. The same provisional reading is retained for उत्सव विधि on p.142. Its technical or figurative intent remains unestablished; the source expression is preserved rather than silently repaired.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>विखंडन</t>
+          <t>पोषण</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>vikhandan</t>
+          <t>poshan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>fragmentation</t>
+          <t>nourishment</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>KD 3.13: of magnetic current (dynamo principle)</t>
+          <t>Settled per Raghava (2026-08-23). Use **nourishment** for the noun, including relational uses ("provides nourishment to"); ordinary grammatical derivatives such as "nourishing" remain available where the Hindi is adjectival. This deliberately prefers the KD source's nourishment sense over MD-Mapping's bare "nurturing" row; पोषक remains "nourisher" and is not collapsed into this noun.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>विद्युतवाहिता</t>
+          <t>अनुकूल</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>vidyutvahita</t>
+          <t>anukul</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>electric conduction</t>
+          <t>aligned / favourable (contextual)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>KD 3.13: radio/TV waves as electricity-borne word/sound</t>
+          <t>Settled per Raghava (2026-08-23): **aligned** when one faculty, activity, or result functions in relation to another. KD 1 p.15 therefore reads "endeavour aligned with knowledge, work aligned with endeavour, result aligned with work, realisation aligned with result, and knowledge aligned with realisation." Keep **favourable** for environmental/circumstantial uses such as अनुकूल वातावरण. Supersedes the opaque "consonant with" chain; MD-Mapping's bare row is "conducive."</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>चुम्बकीयता</t>
+          <t>प्रयास, प्रयत्न</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>chumbakiyata</t>
+          <t>prayas, prayatna</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>magnetism</t>
+          <t>endeavour</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Aligned with MVD/JV/SB usage; KD 3.13 abstract noun</t>
+          <t>Settled per Raghava (2026-08-23), with the standard British spelling **endeavour**. Reserve **effort** for श्रम in the श्रम–गति–परिणाम / Effort–Motion–Result sense. Where यत्न and प्रयत्न occur together (KD 3.16 p.143), distinguish them as "attempt and endeavour." Matches MD-Mapping's प्रयास = "endeavour."</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>प्रभाव क्षेत्र</t>
+          <t>प्रयोग</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>prabhav kshetra</t>
+          <t>prayog</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>field</t>
+          <t>application / apply</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Aligned with MVD/JV/SB usage; KD 3.13 field analogue</t>
+          <t>Settled per Raghava (2026-08-23). Use **application** as the noun and **apply** as the verb, including scientific passages; supersedes "experiment / experimentation." This is an explicit KD terminology choice differing from MD-Mapping and Rakesh's frequent "experiment / experimentation" rendering.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>संकोचन प्रसारण</t>
+          <t>द्वेष</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>sankochan prasaran</t>
+          <t>dvesh</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>contraction-expansion</t>
+          <t>malice</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>KD 3.13: mechanism of flow/pressure in a medium</t>
+          <t>Aligned 2026-08-23 with MVD's direct definition: "Malice (*dvesh*)" is imagining one's happiness only in the destruction of others. Use **malice** in राग–द्वेष and ईर्ष्या–द्वेष contexts too. Keep घृणा = **hatred** where the two occur separately in the same list (KD 2 p.41), and विद्वेष = **hostility**. Supersedes both "hatred" and "aversion" for द्वेष.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>सम विषम आवेश</t>
+          <t>भोग</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>sam-visham avesh</t>
+          <t>bhog</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>generative-degenerative excitation</t>
+          <t>enjoyment</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Settled per Raghava (July 2026); KD 3.13 pressure definition; sam=generative, visham=degenerative per MD-Mapping</t>
+          <t>Confirmed per Raghava (2026-08-23) for bare भोग in KD (e.g. भोग एवं बहुभोगवादी जीवन; भोग परिणाम). Contextual distinctions remain: फल भोगना = **experience consequences/results**; भोक्ता = **enjoyer**; उपभोग = **consumption**. Rakesh's MVD often uses "indulgence" or "sensory enjoyments" for bare/compound भोग, while JV commonly uses "consumption" for उपभोग; KD deliberately retains **enjoyment** for bare भोग.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>रस द्रव्य</t>
+          <t>योगाभ्यास, योग्याभ्यास</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ras dravya</t>
+          <t>yogabhyas, yogyabhyas</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>fluid matter</t>
+          <t>study of yoga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>KD 3.13 flow definition</t>
+          <t>Settled per Raghava (2026-08-23) for both forms on KD 1 p.18. Keep **yoga** transliterated in English rather than translating the technical term as "union"; render the full term as **study of yoga**. Supersedes "yoga-practice" and "union-worthy practice." The following source explanation मिलन का अभ्यास remains translated compositionally as "the study of meeting."</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>अण्डाकार</t>
+          <t>सत्यान्वेषण, ऐषणान्वेषण, विषयान्वेषण</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>andakar</t>
+          <t>satyanveshan, eshananveshan, vishayanveshan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>elliptic</t>
+          <t>truth-oriented exploration, motive-oriented exploration, instincts-oriented exploration</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Settled per Raghava (July 2026); KD 3.7: Earth's orbital path</t>
+          <t>Settled 2026-08-23 after source-image review of KD 1 pp.4–6. The exact compounds do not occur in MVD/JV; the rendering is compositional and aligns their established base vocabulary: सत्य = truth, ऐषणा = motive, विषय = instincts, अन्वेषण = exploration. Supersedes truth-/desire-/object-investigation. Their collective अन्वेषण-त्रय is **exploration-trio**.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ससम्मुखता</t>
+          <t>अच्छी दूरी</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>sasammukhta</t>
+          <t>acchi doori</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>facing-ness</t>
+          <t>good distance</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>KD 3.7: Earth's face toward the Sun</t>
+          <t>KD: equilibrium separation maintained by the nucleus / between bodies</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>सौर व्यूह</t>
+          <t>विन्यास</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>saur vyuh</t>
+          <t>vinyas</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>solar system (solar array)</t>
+          <t>*vinyas* (contextual gloss: arrangement; unresolved)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>KD 3.7/3.11</t>
+          <t>Source-image review (2026-10-04): KD printed pp. 103–104 describe weight, falling, running, flying, rain and flow; p. 104 explicitly defines विन्यास as activity in evidencing coexistence. A solely static layout is too narrow. MD-Mapping Sheet1 row 1352 gives demeanour/design with arrangement/manifestation alternatives in a behavioural context; SB PDF positions 78 and 228 use functional arrangements and configuration in different contexts. Retain *vinyas* and contextual arrangement without treating either precedent as a settled KD technical equivalent.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ग्रह-गोल</t>
+          <t>मध्यस्थीयकरण</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>grah-gol</t>
+          <t>madhyasthiyakaran</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>planet-orb</t>
+          <t>mediation</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>KD 3.7</t>
+          <t>KD 3.11: what modern force/power studies are said to deny</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ब्रह्माण्डीय ऊष्मा</t>
+          <t>चुम्बकीय धारा</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>brahmandiya ushma</t>
+          <t>chumbakiya dhara</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>cosmic heat</t>
+          <t>magnetic current</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>KD 3.2: role in origin of prana-cells</t>
+          <t>KD 3.13: electricity = flow from its fragmentation</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ब्रह्माण्डीय किरण</t>
+          <t>विखंडन</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>brahmandiya kiran</t>
+          <t>vikhandan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>cosmic rays</t>
+          <t>fragmentation</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>KD 3.7</t>
+          <t>KD 3.13: of magnetic current (dynamo principle)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>काई</t>
+          <t>विद्युतवाहिता</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>kaai</t>
+          <t>vidyutvahita</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>algae</t>
+          <t>electric conduction</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>KD 3.2: root form of prana-cell compositions in water</t>
+          <t>KD 3.13: radio/TV waves as electricity-borne word/sound</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>अजीर्ण (परमाणु)</t>
+          <t>चुम्बकीयता</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ajeern</t>
+          <t>chumbakiyata</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>undigested (atom)</t>
+          <t>magnetism</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>KD 3.3: atom holding excess particles it seeks to expel</t>
+          <t>Aligned with MVD/JV/SB usage; KD 3.13 abstract noun</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>भूखा (परमाणु)</t>
+          <t>प्रभाव क्षेत्र</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>bhookha</t>
+          <t>prabhav kshetra</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>hungry (atom)</t>
+          <t>field</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>KD 3.3: atom capable of absorbing more particles</t>
+          <t>Aligned with MVD/JV/SB usage; KD 3.13 field analogue</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>तृप्त (परमाणु)</t>
+          <t>संकोचन प्रसारण</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>tript</t>
+          <t>sankochan prasaran</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>satisfied (atom)</t>
+          <t>contraction-expansion</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>KD 3.3: constitutionally complete atom</t>
+          <t>KD 3.13: mechanism of flow/pressure in a medium</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>गठन तृप्त पद</t>
+          <t>सम विषम आवेश</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>gathan tript pad</t>
+          <t>sam-visham avesh</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>constitution-satisfied status</t>
+          <t>generative-degenerative excitation</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>KD 3.3</t>
+          <t>Settled per Raghava (July 2026); KD 3.13 pressure definition; sam=generative, visham=degenerative per MD-Mapping</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>संक्रमण</t>
+          <t>रस द्रव्य</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>sankraman</t>
+          <t>ras dravya</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>irreversible transition</t>
+          <t>fluid matter</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Aligned to the full technical sense in KD 3.3: irreversible passage to constitutional completeness</t>
+          <t>KD 3.13 flow definition</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>संक्रमणीयता</t>
+          <t>अण्डाकार</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>sankramaniyata</t>
+          <t>andakar</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>irreversibility</t>
+          <t>elliptic</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Aligned to the full technical sense in KD 3.3</t>
+          <t>Settled per Raghava (July 2026); KD 3.7: Earth's orbital path</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>विकिरणीयता</t>
+          <t>ससम्मुखता</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>vikiraniyata</t>
+          <t>sasammukhta</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>radiativeness</t>
+          <t>facing-ness</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>KD 3.3: emission property of undigested atoms</t>
+          <t>KD 3.7: Earth's face toward the Sun</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>विकिरणीय द्रव्य</t>
+          <t>सौर व्यूह</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>vikiraniya dravya</t>
+          <t>saur vyuh</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>radiant (radioactive) materials</t>
+          <t>solar system (solar array)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>KD 3.11</t>
+          <t>KD 3.7/3.11</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ताप पाचन</t>
+          <t>ग्रह-गोल</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>taap pachan</t>
+          <t>grah-gol</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>heat-digestion</t>
+          <t>planet-orb</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>KD 3.7: absorption of heat (coal/petroleum passages)</t>
+          <t>KD 3.7</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>प्राण घातक वायु</t>
+          <t>ब्रह्माण्डीय ऊष्मा</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>pran ghatak vayu</t>
+          <t>brahmandiya ushma</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>life-fatal air (carbon monoxide)</t>
+          <t>cosmic heat</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>KD 3.7; pattern of pranvayu=oxygen</t>
+          <t>KD 3.2: role in origin of prana-cells</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>संतुलनीकरण</t>
+          <t>ब्रह्माण्डीय किरण</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>santulanikaran</t>
+          <t>brahmandiya kiran</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>equilibration</t>
+          <t>cosmic rays</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -61863,2770 +61863,3056 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>आवर्तनशीलता</t>
+          <t>काई</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>avartansheelta</t>
+          <t>kaai</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>cyclicality</t>
+          <t>algae</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>KD 3.7/3.15: water cycle; recurrence basis of time-reckoning</t>
+          <t>KD 3.2: root form of prana-cell compositions in water</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>तापोद्दीपन</t>
+          <t>अजीर्ण (परमाणु)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>tapoddipan</t>
+          <t>ajeern</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>heat-stimulation</t>
+          <t>undigested (atom)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>KD 3.7</t>
+          <t>KD 3.3: atom holding excess particles it seeks to expel</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>मानवेत्तर प्रकृति</t>
+          <t>भूखा (परमाणु)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>manavettar prakriti</t>
+          <t>bhookha</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>nature-other-than-human</t>
+          <t>hungry (atom)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>KD 3.7 recurring</t>
+          <t>KD 3.3: atom capable of absorbing more particles</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>त्राण-प्राण</t>
+          <t>तृप्त (परमाणु)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>tran-pran</t>
+          <t>tript</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>succour and *pran*</t>
+          <t>satisfied (atom)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>KD 3.12; the text itself glosses *tran* as state and *pran* as motion. Keep *pran* transliterated rather than rendering it as “life-breath”; this also avoids confusion with प्राणवायु, which remains *pranavayu*.</t>
+          <t>KD 3.3: constitutionally complete atom</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>गम्य स्थली</t>
+          <t>गठन तृप्त पद</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>gamya sthali</t>
+          <t>gathan tript pad</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>destination</t>
+          <t>constitution-satisfied status</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>KD 3.12/3.14</t>
+          <t>KD 3.3</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>अनुप्राणित</t>
+          <t>संक्रमण</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>anupranit</t>
+          <t>sankraman</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>propagated</t>
+          <t>irreversible transition</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>EXPLICIT DECISION (2026-08-23): in KD 3.13's molecule-to-molecule wave-transmission context, use **propagated**. MVD's "invigorated/inspired" does not fit this physical context</t>
+          <t>Aligned to the full technical sense in KD 3.3: irreversible passage to constitutional completeness</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>निष्पत्ति स्थली</t>
+          <t>संक्रमणीयता</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>nishpatti sthali</t>
+          <t>sankramaniyata</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>site of production</t>
+          <t>irreversibility</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>KD 3.13: origin of sound/word waves</t>
+          <t>Aligned to the full technical sense in KD 3.3</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>स्वयं स्फूर्त</t>
+          <t>विकिरणीयता</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>svayam sphoort</t>
+          <t>vikiraniyata</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>self-motivated / self-motivation (contextual)</t>
+          <t>radiativeness</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Settled per Raghava (2026-07-08), superseding the earlier "self-organised" (KD 3.1) and "self-spurred" (KD 3.4, 3.9, 3.13, 3.16-3.18) renderings — use "self-motivated" as adjective (e.g. "self-motivated method"), "self-motivation" where a noun reads better (e.g. "comes to be self-motivation" → "occurs through self-motivation"). Retroactively corrected across KD-Karm-Darshan-English.md §3.1–3.3, KD-Karm-Darshan-English.md §3.4–3.6, KD-Karm-Darshan-English.md §3.9–3.10, KD-Karm-Darshan-English.md §3.13–3.15, KD-Karm-Darshan-English.md §3.16–3.18 on 2026-07-08. **KD-Karm-Darshan-English.md §3.7–3.8 audit (2026-07-08 remediation):** all four former "self-inspired" instances verified against source images (pp. 76, 77, 81, 87) — each translates **स्वयं स्फूर्त**, corrected to "self-motivated." Distinct from **स्वयं प्रेरित** = "self-inspired" (SB usage; not found in KD 3.7-3.8)</t>
+          <t>KD 3.3: emission property of undigested atoms</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>साम्य ऊर्जा</t>
+          <t>विकिरणीय द्रव्य</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>samya oorja</t>
+          <t>vikiraniya dravya</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>uniform energy</t>
+          <t>radiant (radioactive) materials</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>per MD-Mapping; KD 3.13 "fundamental uniform energy"</t>
+          <t>KD 3.11</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ऊर्जा सम्पन्न, पूर्णतया ऊर्जा सम्पन्न</t>
+          <t>ताप पाचन</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>urja sampanna</t>
+          <t>taap pachan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>energised / fully energised</t>
+          <t>heat-digestion</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Aligned with MVD p.26 ("fully energised") and MD-Mapping ऊर्जित = Energised; supersedes earlier "energy-endowed". Retroactively corrected corpus-wide 2026-07-10</t>
+          <t>KD 3.7: absorption of heat (coal/petroleum passages)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ऊर्जा सम्पन्नता</t>
+          <t>प्राण घातक वायु</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>urja sampannata</t>
+          <t>pran ghatak vayu</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>energy-fullness</t>
+          <t>life-fatal air (carbon monoxide)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Per MD-Mapping; supersedes earlier "energy-endowment". Retroactively corrected corpus-wide 2026-07-10</t>
+          <t>KD 3.7; pattern of pranvayu=oxygen</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>बल सम्पन्न, बल सम्पन्नता</t>
+          <t>संतुलनीकरण</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>bal sampanna / bal sampannata</t>
+          <t>santulanikaran</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>forceful / forcefulness</t>
+          <t>equilibration</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Per MD-Mapping बल संपन्नता = Forcefulness; adjective parallel to energised. Supersedes earlier "force-endowed" / "force-endowment". Retroactively corrected corpus-wide 2026-07-10</t>
+          <t>KD 3.7</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>चुंबकीय बल सम्पन्न, चुंबकीय बल सम्पन्नता</t>
+          <t>आवर्तनशीलता</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>chumbakiya bal sampanna / sampannata</t>
+          <t>avartansheelta</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>magnetic-force-full / magnetic force-fullness</t>
+          <t>cyclicality</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Per MD-Mapping चुंबकीय बल सम्पन्नता = magnetic force-fullness. Supersedes earlier "endowed with magnetic force" / "magnetic-force endowment". Retroactively corrected corpus-wide 2026-07-10</t>
+          <t>KD 3.7/3.15: water cycle; recurrence basis of time-reckoning</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>बल (bare, general/ontological sense)</t>
+          <t>तापोद्दीपन</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>bal</t>
+          <t>tapoddipan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>strength (inherent strength; "capacity to apply force")</t>
+          <t>heat-stimulation</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>FINALISED per Raghava (2026-08-05), superseding "force" for बल's general/ontological sense — the standing, endowed capacity a unit or faculty has (KD 3.11's *sthiti*/state term, paired with *shakti*/power in *gati*/motion). Rationale: (1) बल is described as inherent, constant, and present in a unit's natural state independent of any interaction (SB pp. 60–61: "every entity has... inseparability of strength in state and power in motion"; SB p. 98: "forcefulness is existentially inherent in each atomic particle") — this fits a standing capacity/endowment better than the relational, interaction-tied physics sense of "force." (2) Direct precedent in the source itself: SB's own published translation renders अक्षय बल — the five *jeevan* faculties (mun/vritti/chitta/buddhi/atma) themselves — as "**Inexhaustible Strength**" in the Five Forces table header (SB p. 85/SB-Samadhanatmak-Bhautikvad.md line ~772-790), even though the same table's left column (विद्युत-चुम्बकीय बल, गुरुत्वाकर्षण बल, मध्यस्थ बल) is rendered "Electromagnetic/Gravitational/Mediative Force." (3) The mutual-necessity claim ("शक्ति के बिना बल का परिचय, बल के बिना शक्ति का परिचय नहीं होता," SB ~p. 61) reads coherently as strength/capacity requiring exercise (power) to be evidenced, and vice versa — not strictly true of physics-force, which can exist statically without power (P=Fv=0 at rest). **Contextual boundary:** bare बल, including KD 3.11's opening and closing बल-शक्ति question, is **strength**; specific named physical or interaction categories such as दबाव को बल (pressure as force), विद्युत-चुम्बकीय बल, गुरुत्वाकर्षण बल, and मध्यस्थ बल remain **force**. शक्ति stays **power** throughout. Cross-ref: बल सम्पन्न / चुंबकीय बल सम्पन्न rows above (compounds, already settled as "forceful"/"forcefulness" — unaffected). **Applied corpus-wide on 2026-08-23 and completed in the editorial pilot on 2026-08-23**, including the chapter title, state–motion formulations, the five strengths of *jeevan*, and KD 3.11 p.102. **Translation-policy note:** Rakesh Gupta’s published MVD/SB/JV terminology and `MD-Mapping.xlsx` remain the project’s default authority; this rendering is a deliberate, narrowly scoped exception approved by Raghava where the standing-capacity sense is clearer as "strength." Do not generalise the override: named physical/interaction categories remain "force," and बल सम्पन्न / बल सम्पन्नता remain "forceful" / "forcefulness." Full reasoning trail: chat discussion preserved in *The Ontology of Coexistence* project history; see `Studies/The-Ontology-of-Coexistence/Research-Note-Physics-Of-Satta-Unit-Interaction.md` §4 and §7.1 for the surrounding argument (research note itself not yet updated to match — its "What MD says" claims still say "force" for बल's general sense, and its verbatim SB quotes correctly keep SB's own published wording regardless of this decision)</t>
+          <t>KD 3.7</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ग्राही</t>
+          <t>मानवेत्तर प्रकृति</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>grahi</t>
+          <t>manavettar prakriti</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>receptive</t>
+          <t>nature-other-than-human</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>KD 3.13: all nature electricity-receptive</t>
+          <t>KD 3.7 recurring</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>विस्तार आयाम</t>
+          <t>त्राण-प्राण</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>vistār āyām</t>
+          <t>tran-pran</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>area</t>
+          <t>succour and *pran*</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>KD 3.14 chapter title; confirmed by Raghava (July 2026)</t>
+          <t>KD 3.12; the text itself glosses *tran* as state and *pran* as motion. Keep *pran* transliterated rather than rendering it as “life-breath”; this also avoids confusion with प्राणवायु, which remains *pranavayu*.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>विस्तार</t>
+          <t>गम्य स्थली</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>vistār</t>
+          <t>gamya sthali</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>expanse</t>
+          <t>destination</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Aligned with MVD/JV/SB usage. KD 3.14: "whatever length, breadth, and height a composition is spread over"; distinct from the compound विस्तार आयाम \= area</t>
+          <t>KD 3.12/3.14</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>दृष्टि पाट</t>
+          <t>अनुप्राणित</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>drishti pat</t>
+          <t>anupranit</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>span of vision</t>
+          <t>propagated</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>KD 3.14: 90-degree binocular field</t>
+          <t>EXPLICIT DECISION (2026-08-23): in KD 3.13's molecule-to-molecule wave-transmission context, use **propagated**. MVD's "invigorated/inspired" does not fit this physical context</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>दृग बिन्दु</t>
+          <t>निष्पत्ति स्थली</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>drig bindu</t>
+          <t>nishpatti sthali</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>sight-point</t>
+          <t>site of production</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>KD 3.14</t>
+          <t>KD 3.13: origin of sound/word waves</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>चक्षु तंत्र</t>
+          <t>स्वयं स्फूर्त</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>chakshu tantra</t>
+          <t>svayam sphoort</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>visual system</t>
+          <t>self-motivated / self-motivation (contextual)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>KD 3.14</t>
+          <t>Settled per Raghava (2026-07-08), superseding the earlier "self-organised" (KD 3.1) and "self-spurred" (KD 3.4, 3.9, 3.13, 3.16-3.18) renderings — use "self-motivated" as adjective (e.g. "self-motivated method"), "self-motivation" where a noun reads better (e.g. "comes to be self-motivation" → "occurs through self-motivation"). Retroactively corrected across KD-Karm-Darshan-English.md §3.1–3.3, KD-Karm-Darshan-English.md §3.4–3.6, KD-Karm-Darshan-English.md §3.9–3.10, KD-Karm-Darshan-English.md §3.13–3.15, KD-Karm-Darshan-English.md §3.16–3.18 on 2026-07-08. **KD-Karm-Darshan-English.md §3.7–3.8 audit (2026-07-08 remediation):** all four former "self-inspired" instances verified against source images (pp. 76, 77, 81, 87) — each translates **स्वयं स्फूर्त**, corrected to "self-motivated." Distinct from **स्वयं प्रेरित** = "self-inspired" (SB usage; not found in KD 3.7-3.8)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>अंश (कोण में)</t>
+          <t>साम्य ऊर्जा</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ansh</t>
+          <t>samya oorja</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>degree (angle)</t>
+          <t>uniform energy</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>KD 3.14 — same word as ansh=particle; sense depends on context</t>
+          <t>per MD-Mapping; KD 3.13 "fundamental uniform energy"</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>समकेन्द्रीय रेखा</t>
+          <t>ऊर्जा सम्पन्न, पूर्णतया ऊर्जा सम्पन्न</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>samkendriya rekha</t>
+          <t>urja sampanna</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>concentric line</t>
+          <t>energised / fully energised</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>KD 3.14</t>
+          <t>Aligned with MVD p.26 ("fully energised") and MD-Mapping ऊर्जित = Energised; supersedes earlier "energy-endowed". Retroactively corrected corpus-wide 2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>काल शून्य</t>
+          <t>ऊर्जा सम्पन्नता</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>kaal shoonya</t>
+          <t>urja sampannata</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>time-zero</t>
+          <t>energy-fullness</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>KD 3.15</t>
+          <t>Per MD-Mapping; supersedes earlier "energy-endowment". Retroactively corrected corpus-wide 2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>घटी, पल</t>
+          <t>बल सम्पन्न, बल सम्पन्नता</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ghati, pal</t>
+          <t>bal sampanna / bal sampannata</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ghati, pal (time units)</t>
+          <t>forceful / forcefulness</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>KD 3.15, left transliterated</t>
+          <t>Per MD-Mapping बल संपन्नता = Forcefulness; adjective parallel to energised. Supersedes earlier "force-endowed" / "force-endowment". Retroactively corrected corpus-wide 2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>फलन</t>
+          <t>चुंबकीय बल सम्पन्न, चुंबकीय बल सम्पन्नता</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>phalan</t>
+          <t>chumbakiya bal sampanna / sampannata</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>outcome</t>
+          <t>magnetic-force-full / magnetic force-fullness</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Aligned with MVD/JV/SB usage. KD 3.15: evaluation on the basis of activity and outcome</t>
+          <t>Per MD-Mapping चुंबकीय बल सम्पन्नता = magnetic force-fullness. Supersedes earlier "endowed with magnetic force" / "magnetic-force endowment". Retroactively corrected corpus-wide 2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>नित्य वर्तमान</t>
+          <t>बल (bare, general/ontological sense)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>nitya vartman</t>
+          <t>bal</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ever-present</t>
+          <t>strength (inherent strength; "capacity to apply force")</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Settled per Raghava (July 2026); KD 3.15 predicate of kaal</t>
+          <t>FINALISED per Raghava (2026-08-05), superseding "force" for बल's general/ontological sense — the standing, endowed capacity a unit or faculty has (KD 3.11's *sthiti*/state term, paired with *shakti*/power in *gati*/motion). Rationale: (1) बल is described as inherent, constant, and present in a unit's natural state independent of any interaction (SB pp. 60–61: "every entity has... inseparability of strength in state and power in motion"; SB p. 98: "forcefulness is existentially inherent in each atomic particle") — this fits a standing capacity/endowment better than the relational, interaction-tied physics sense of "force." (2) Direct precedent in the source itself: SB's own published translation renders अक्षय बल — the five *jeevan* faculties (mun/vritti/chitta/buddhi/atma) themselves — as "**Inexhaustible Strength**" in the Five Forces table header (SB p. 85/SB-Samadhanatmak-Bhautikvad.md line ~772-790), even though the same table's left column (विद्युत-चुम्बकीय बल, गुरुत्वाकर्षण बल, मध्यस्थ बल) is rendered "Electromagnetic/Gravitational/Mediative Force." (3) The mutual-necessity claim ("शक्ति के बिना बल का परिचय, बल के बिना शक्ति का परिचय नहीं होता," SB ~p. 61) reads coherently as strength/capacity requiring exercise (power) to be evidenced, and vice versa — not strictly true of physics-force, which can exist statically without power (P=Fv=0 at rest). **Contextual boundary:** bare बल, including KD 3.11's opening and closing बल-शक्ति question, is **strength**; specific named physical or interaction categories such as दबाव को बल (pressure as force), विद्युत-चुम्बकीय बल, गुरुत्वाकर्षण बल, and मध्यस्थ बल remain **force**. शक्ति stays **power** throughout. Cross-ref: बल सम्पन्न / चुंबकीय बल सम्पन्न rows above (compounds, already settled as "forceful"/"forcefulness" — unaffected). **Applied corpus-wide on 2026-08-23 and completed in the editorial pilot on 2026-08-23**, including the chapter title, state–motion formulations, the five strengths of *jeevan*, and KD 3.11 p.102. **Translation-policy note:** Rakesh Gupta’s published MVD/SB/JV terminology and `MD-Mapping.xlsx` remain the project’s default authority; this rendering is a deliberate, narrowly scoped exception approved by Raghava where the standing-capacity sense is clearer as "strength." Do not generalise the override: named physical/interaction categories remain "force," and बल सम्पन्न / बल सम्पन्नता remain "forceful" / "forcefulness." Full reasoning trail: chat discussion preserved in *The Ontology of Coexistence* project history; see `Studies/The-Ontology-of-Coexistence/Research-Note-Physics-Of-Satta-Unit-Interaction.md` §4 and §7.1 for the surrounding argument (research note itself not yet updated to match — its "What MD says" claims still say "force" for बल's general sense, and its verbatim SB quotes correctly keep SB's own published wording regardless of this decision)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>मेधस</t>
+          <t>ग्राही</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>medhas</t>
+          <t>grahi</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>brain</t>
+          <t>receptive</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Aligned with MVD/JV usage. Retain *medhas* only as a first-use parenthetical where useful; KD 3.3 uses brain composition/system</t>
+          <t>KD 3.13: all nature electricity-receptive</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>शून्याकर्षण</t>
+          <t>विस्तार आयाम</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>shunyakarshan</t>
+          <t>vistār āyām</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>zero-attraction</t>
+          <t>area</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>per MD-Mapping; KD 3.14</t>
+          <t>KD 3.14 chapter title; confirmed by Raghava (July 2026)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>परावर्तन</t>
+          <t>विस्तार</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>paravartan</t>
+          <t>vistār</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>projection</t>
+          <t>expanse</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Re-settled per Raghava (2026-07-08), superseding the July 2026 KD-specific choice, to align with MD-Mapping's row, independently confirmed by MVD (MVD p.328). Ch. 3.12 retitled "Projection–Reflection"; all instances across KD-Karm-Darshan-English.md §3.11–3.12 and the confirmed paravartan instances in KD-Karm-Darshan-English.md §3.7–3.8 (heat-reflection passages, e.g. "the sun's heat is being projected equally in all directions") were swapped 2026-07-08</t>
+          <t>Aligned with MVD/JV/SB usage. KD 3.14: "whatever length, breadth, and height a composition is spread over"; distinct from the compound विस्तार आयाम \= area</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>प्रत्यावर्तन</t>
+          <t>दृष्टि पाट</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>pratyavartan</t>
+          <t>drishti pat</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>reflection</t>
+          <t>span of vision</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Re-settled per Raghava (2026-07-08), aligned with MD-Mapping/MVD (MVD p.286). See परावर्तन row above; swapped together as a pair 2026-07-08</t>
+          <t>KD 3.14: 90-degree binocular field</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>संसार (पशु/वनस्पति/खनिज-)</t>
+          <t>दृग बिन्दु</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>sansar</t>
+          <t>drig bindu</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>order (animal order, plant order, mineral order, human order)</t>
+          <t>sight-point</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Per Raghava (July 2026): render -संसार compounds with "order," aligning with the four-orders vocabulary, not literal "world"</t>
+          <t>KD 3.14</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>आत्मा, बुद्धि, चित्त, वृत्ति, मन</t>
+          <t>चक्षु तंत्र</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>atma, buddhi, chitta, vritti, mun</t>
+          <t>chakshu tantra</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>left transliterated (atma, buddhi, chitta, vritti, mun/"mind")</t>
+          <t>visual system</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>KD 3.6: the five jeevan faculties (pūrvānukram), each carrying one of the five *sthiti* (state) activities — anubhav/atma (realisation), bodh/buddhi (enlightenment), chintan/chitta (contemplation), tulan/vritti (comparison), aswadan/mun (tasting) — and one of the five *gati* (motion) activities — praman/atma (evidence), ṛtambharā/buddhi (resoluteness), ichha/chitta (desire), vishleshan/vritti (analysis), chayan/mun (selection). MD-Mapping leaves all five untranslated; matches its own note under अंतर्नियामन ("पूर्वानुक्रम = वरीयता क्रम याने आत्मा, बुद्धि, चित्त, वृत्ति, मन")</t>
+          <t>KD 3.14</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ऋतम्भरा, ऋतंभरा</t>
+          <t>अंश (कोण में)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ṛtambharā</t>
+          <t>ansh</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>resoluteness</t>
+          <t>degree (angle)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Per MD-Mapping; KD 3.4/3.6: buddhi's *gati* (motion) activity — putting justice, dharma, and truth to purpose and into practice</t>
+          <t>KD 3.14 — same word as ansh=particle; sense depends on context</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>गठनपूर्णता, क्रियापूर्णता, आचरणपूर्णता</t>
+          <t>समकेन्द्रीय रेखा</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>gathan-purnata, kriya-purnata, acharan-purnata</t>
+          <t>samkendriya rekha</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>constitutional completeness, activity-completeness, conduct-completeness</t>
+          <t>concentric line</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>KD 3.3/3.4: the atom's three stages of development. गठनपूर्णता = "constitutional completeness" per MD-Mapping; क्रियापूर्णता and आचरणपूर्णता are parallel KD coinages (not in MD-Mapping), rendered analogously</t>
+          <t>KD 3.14</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>अखण्ड समाज</t>
+          <t>काल शून्य</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>akhand samaj</t>
+          <t>kaal shoonya</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>undivided society</t>
+          <t>time-zero</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>KD 3.4: not in MD-Mapping; compositional rendering of अखण्ड (undivided) + समाज (society)</t>
+          <t>KD 3.15</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>चिराकांक्षा, चिराकाँक्षा</t>
+          <t>घटी, पल</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>chira-akanksha</t>
+          <t>ghati, pal</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>abiding aspiration</t>
+          <t>ghati, pal (time units)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>KD 3.6: not in MD-Mapping; judgment call — चिर (lasting/eternal) + आकांक्षा (aspiration/longing)</t>
+          <t>KD 3.15, left transliterated</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>सचेष्ट</t>
+          <t>फलन</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>sachesht</t>
+          <t>phalan</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>earnestly active</t>
+          <t>outcome</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>KD 3.6: not in MD-Mapping; judgment call for the state of alert, diligent striving toward the human goal</t>
+          <t>Aligned with MVD/JV/SB usage. KD 3.15: evaluation on the basis of activity and outcome</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>यथास्थिति</t>
+          <t>नित्य वर्तमान</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>yatha-sthiti</t>
+          <t>nitya vartman</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>existent state</t>
+          <t>ever-present</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Aligned with MVD/JV/SB usage. KD 3.4/3.5: distinct from अस्तित्व (existence) — the concrete, as-is state of a thing/person, not "status quo" in the political sense</t>
+          <t>Settled per Raghava (July 2026); KD 3.15 predicate of kaal</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>तृप्ति</t>
+          <t>मेधस</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>tripti</t>
+          <t>medhas</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>satisfaction</t>
+          <t>brain</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Aligned with MVD/JV/SB usage. KD 3.6: jeevan's fulfilment through realisation (*anubhav*), recognised in human tradition as happiness, peace, and contentment</t>
+          <t>Aligned with MVD/JV usage. Retain *medhas* only as a first-use parenthetical where useful; KD 3.3 uses brain composition/system</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>परम</t>
+          <t>शून्याकर्षण</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>param</t>
+          <t>shunyakarshan</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ultimate</t>
+          <t>zero-attraction</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>KD 3.6: predicate of अनुभव (realisation) — "never more than realisation; jeevan remains incomplete in anything less"</t>
+          <t>per MD-Mapping; KD 3.14</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ध्रुवीकरण</t>
+          <t>परावर्तन</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>dhruvikaran</t>
+          <t>paravartan</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>anchoring</t>
+          <t>projection</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Per MD-Mapping ("संतुलन स्वभाव गति"); KD 3.4: resolution becoming the fixed reference point of jeevan activity</t>
+          <t>Re-settled per Raghava (2026-07-08), superseding the July 2026 KD-specific choice, to align with MD-Mapping's row, independently confirmed by MVD (MVD p.328). Ch. 3.12 retitled "Projection–Reflection"; all instances across KD-Karm-Darshan-English.md §3.11–3.12 and the confirmed paravartan instances in KD-Karm-Darshan-English.md §3.7–3.8 (heat-reflection passages, e.g. "the sun's heat is being projected equally in all directions") were swapped 2026-07-08</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>गुण</t>
+          <t>प्रत्यावर्तन</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>guna</t>
+          <t>pratyavartan</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>property</t>
+          <t>reflection</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Settled per Raghava (2026-07-08): "property," NOT "quality." MD-Mapping carries both readings (गुण = "properties" as a noun; गुण = "qualitative" as an adjective) — for KD's recurring रूप/गुण/स्वभाव/धर्म (form/property/essential nature/dharma) list of the four orders' predominant traits, and for chapter 3.10's title, गुण is a noun and takes "property." Retroactively corrected in KD-Karm-Darshan-English.md §3.4–3.6, KD-Karm-Darshan-English.md §3.11–3.12, and KD-Karm-Darshan-English.md §3.13–3.15 (previously translated "quality") on 2026-07-08. Exception: the adjectival compound गुणात्मक परिवर्तन keeps MD-Mapping's own established "qualitative change/transformation" (KD 3.9) — "property-al" does not read in English, and MD-Mapping treats this compound as a separate row from bare गुण</t>
+          <t>Re-settled per Raghava (2026-07-08), aligned with MD-Mapping/MVD (MVD p.286). See परावर्तन row above; swapped together as a pair 2026-07-08</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>सम, विषम, मध्यस्थ (गुण के रूप में)</t>
+          <t>संसार (पशु/वनस्पति/खनिज-)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>sam, visham, madhyastha</t>
+          <t>sansar</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>generative, degenerative, mediating</t>
+          <t>order (animal order, plant order, mineral order, human order)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Per MD-Mapping (सम=generative, विषम=degenerative) and MVD running prose ("generative, degenerative, and mediative"). **Do not leave bare सम/विषम transliterated in analytical prose** — use generative / degenerative (MVD spelling: "degenerative", not "de-generative"). Optional (*sam*) / (*visham*) gloss only on first compound use if helpful (e.g. generative-degenerative (*sam-visham*)). Retroactively corrected in KD 1 (pp. 15–16, 25) on 2026-07-10 where *sam*/*visham* had been left italic-transliterated. मध्यस्थ here is an adjective describing the property that maintains a composition once formed ("mediating" in KD; MVD often "mediative"), distinct from मध्यस्थीयकरण (mediation, KD 3.11)</t>
+          <t>Per Raghava (July 2026): render -संसार compounds with "order," aligning with the four-orders vocabulary, not literal "world"</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>जागृति क्रम</t>
+          <t>आत्मा, बुद्धि, चित्त, वृत्ति, मन</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>jagriti kram</t>
+          <t>atma, buddhi, chitta, vritti, mun</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>awakening progression</t>
+          <t>left transliterated (atma, buddhi, chitta, vritti, mun/"mind")</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Per MD-Mapping and MVD (not "awakening sequence"). Paired with विकास क्रम = development progression. Retroactively corrected corpus-wide 2026-07-10</t>
+          <t>KD 3.6: the five jeevan faculties (pūrvānukram), each carrying one of the five *sthiti* (state) activities — anubhav/atma (realisation), bodh/buddhi (enlightenment), chintan/chitta (contemplation), tulan/vritti (comparison), aswadan/mun (tasting) — and one of the five *gati* (motion) activities — praman/atma (evidence), ṛtambharā/buddhi (resoluteness), ichha/chitta (desire), vishleshan/vritti (analysis), chayan/mun (selection). MD-Mapping leaves all five untranslated; matches its own note under अंतर्नियामन ("पूर्वानुक्रम = वरीयता क्रम याने आत्मा, बुद्धि, चित्त, वृत्ति, मन")</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>विकास क्रम, विकासक्रम</t>
+          <t>ऋतम्भरा, ऋतंभरा</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>vikas kram</t>
+          <t>ṛtambharā</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>development progression</t>
+          <t>resoluteness</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Per MD-Mapping and MVD (not "developmental sequence"). Retroactively corrected remaining "developmental sequence" instances corpus-wide 2026-07-10</t>
+          <t>Per MD-Mapping; KD 3.4/3.6: buddhi's *gati* (motion) activity — putting justice, dharma, and truth to purpose and into practice</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>सदुपयोग</t>
+          <t>गठनपूर्णता, क्रियापूर्णता, आचरणपूर्णता</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>sadupyog</t>
+          <t>gathan-purnata, kriya-purnata, acharan-purnata</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>right-use</t>
+          <t>constitutional completeness, activity-completeness, conduct-completeness</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Aligned 2026-08-23 with Rakesh Gupta's MVD/JV/SB terminology and MD-Mapping. Replaces the former KD variants "proper use," "good use," "good-use," and unhyphenated "right use."</t>
+          <t>KD 3.3/3.4: the atom's three stages of development. गठनपूर्णता = "constitutional completeness" per MD-Mapping; क्रियापूर्णता and आचरणपूर्णता are parallel KD coinages (not in MD-Mapping), rendered analogously</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>पदार्थावस्था, प्राणावस्था, जीवावस्था, ज्ञानावस्था</t>
+          <t>अखण्ड समाज</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>padarthavastha, pranavastha, jeevavastha, gyanavastha</t>
+          <t>akhand samaj</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>material order, biological order, animal order, knowledge order</t>
+          <t>undivided society</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Aligned 2026-08-23 with Rakesh Gupta's four-orders terminology. Here अवस्था names an ontological order, not a generic "state"; ordinary state/status usages of अवस्था or स्थिति remain context-sensitive.</t>
+          <t>KD 3.4: not in MD-Mapping; compositional rendering of अखण्ड (undivided) + समाज (society)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>प्राणकोष</t>
+          <t>चिराकांक्षा, चिराकाँक्षा</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>pranakosh</t>
+          <t>chira-akanksha</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>biological cell</t>
+          <t>abiding aspiration</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Aligned 2026-08-23 with MVD/JV. Replaces "prana cell," "prana-cell," and their plurals.</t>
+          <t>KD 3.6: not in MD-Mapping; judgment call — चिर (lasting/eternal) + आकांक्षा (aspiration/longing)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>व्यापक, व्यापक वस्तु</t>
+          <t>सचेष्ट</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>vyapak, vyapak vastu</t>
+          <t>sachesht</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Omnipresence; omnipresent reality</t>
+          <t>earnestly active</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Aligned 2026-08-23 with Rakesh Gupta. Use **Omnipresence** when व्यापक functions as the substantive reality and **omnipresent reality** for व्यापक वस्तु; adjectival predicate uses such as "God is omnipresent" remain grammatical. Distinct from सत्ता = Omnipotence.</t>
+          <t>KD 3.6: not in MD-Mapping; judgment call for the state of alert, diligent striving toward the human goal</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>व्यवसाय</t>
+          <t>यथास्थिति</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>vyavasay</t>
+          <t>yatha-sthiti</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>vocation</t>
+          <t>existent state</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Aligned 2026-08-23 with MVD/JV. Replaces "occupation" in the vocation/work-domain sense.</t>
+          <t>Aligned with MVD/JV/SB usage. KD 3.4/3.5: distinct from अस्तित्व (existence) — the concrete, as-is state of a thing/person, not "status quo" in the political sense</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>दया, कृपा, करुणा</t>
+          <t>तृप्ति</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>daya, kripa, karuna</t>
+          <t>tripti</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>kindness, grace, compassion</t>
+          <t>satisfaction</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Aligned 2026-08-23 with Rakesh Gupta's consistent technical trio. The former KD compassion/grace/mercy wording was corrected throughout; दया in the associated social-value passages is kindness, and करुणा is compassion.</t>
+          <t>Aligned with MVD/JV/SB usage. KD 3.6: jeevan's fulfilment through realisation (*anubhav*), recognised in human tradition as happiness, peace, and contentment</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>सारक, मारक</t>
+          <t>परम</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>sarak(ta), marak(ta)</t>
+          <t>param</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>vitalising, devitalising</t>
+          <t>ultimate</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Aligned with MVD/JV/SB usage. KD 3.10: the two modes of स्वभाव (essential nature) in the biological order — vitalising (*sarakta*) means being abundant in itself and useful to the animal order; devitalising (*marakta*) means obstructing one's own seed-abundance and being disease/death-causing to the animal order</t>
+          <t>KD 3.6: predicate of अनुभव (realisation) — "never more than realisation; jeevan remains incomplete in anything less"</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>पात्रता</t>
+          <t>ध्रुवीकरण</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>patrata</t>
+          <t>dhruvikaran</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>receptivity / worthiness (contextual)</t>
+          <t>anchoring</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>EXPLICIT CONTEXTUAL RULE (confirmed 2026-08-23): preserve the technical क्षमता/योग्यता/पात्रता trio as **capacity / ability / receptivity**. These qualities are used when units recognise relationships and evaluate. Use **worthiness** only in KD 3.10's reciprocal दया/कृपा/करुणा (kindness/grace/compassion) definition, where substances are made available "in accordance with worthiness (*patrata*)"</t>
+          <t>Per MD-Mapping ("संतुलन स्वभाव गति"); KD 3.4: resolution becoming the fixed reference point of jeevan activity</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>देव मानव, दिव्य मानव</t>
+          <t>गुण</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>dev manav, divya manav</t>
+          <t>guna</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>deific human, divine human</t>
+          <t>property</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Aligned 2026-08-23 with Rakesh Gupta's MVD terminology; supersedes the former KD "god-human" / "godly human" judgment call.</t>
+          <t>Settled per Raghava (2026-07-08): "property," NOT "quality." MD-Mapping carries both readings (गुण = "properties" as a noun; गुण = "qualitative" as an adjective) — for KD's recurring रूप/गुण/स्वभाव/धर्म (form/property/essential nature/dharma) list of the four orders' predominant traits, and for chapter 3.10's title, गुण is a noun and takes "property." Retroactively corrected in KD-Karm-Darshan-English.md §3.4–3.6, KD-Karm-Darshan-English.md §3.11–3.12, and KD-Karm-Darshan-English.md §3.13–3.15 (previously translated "quality") on 2026-07-08. Exception: the adjectival compound गुणात्मक परिवर्तन keeps MD-Mapping's own established "qualitative change/transformation" (KD 3.9) — "property-al" does not read in English, and MD-Mapping treats this compound as a separate row from bare गुण</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>पशु मानव, राक्षस मानव</t>
+          <t>सम, विषम, मध्यस्थ (गुण के रूप में)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>pashu manav, rakshas manav</t>
+          <t>sam, visham, madhyastha</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>the animalistic human, the demonic human</t>
+          <t>generative, degenerative, mediating</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Per MD-Mapping ("animalistic human," "demonic human"). Retroactively corrected in KD-Karm-Darshan-English.md §3.9–3.10 on 2026-07-08 (previously "animal-human"/"demon-human") to match MD-Mapping exactly and align with KD 1's usage of the same pair</t>
+          <t>Per MD-Mapping (सम=generative, विषम=degenerative) and MVD running prose ("generative, degenerative, and mediative"). **Do not leave bare सम/विषम transliterated in analytical prose** — use generative / degenerative (MVD spelling: "degenerative", not "de-generative"). Optional (*sam*) / (*visham*) gloss only on first compound use if helpful (e.g. generative-degenerative (*sam-visham*)). Retroactively corrected in KD 1 (pp. 15–16, 25) on 2026-07-10 where *sam*/*visham* had been left italic-transliterated. मध्यस्थ here is an adjective describing the property that maintains a composition once formed ("mediating" in KD; MVD often "mediative"), distinct from मध्यस्थीयकरण (mediation, KD 3.11)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>राशि विधि</t>
+          <t>जागृति क्रम</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>rashi vidhi</t>
+          <t>jagriti kram</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>the arrangement of quantity</t>
+          <t>awakening progression</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>KD 3.9/3.10 closing line; not in MD-Mapping, compositional rendering (राशि = quantity/aggregate, विधि = method/arrangement)</t>
+          <t>Per MD-Mapping and MVD (not "awakening sequence"). Paired with विकास क्रम = development progression. Retroactively corrected corpus-wide 2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>दृष्टा, ज्ञाता, ज्ञेय</t>
+          <t>प्रबुद्धता, अप्रबुद्धता</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>drishta, gyata, gyeya</t>
+          <t>prabuddhatā, aprabuddhatā</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>seer, knower, object of knowledge</t>
+          <t>full awareness; absence of full awareness</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Aligned with MVD/JV usage: ज्ञेय names the object-pole of ज्ञान/ज्ञाता (knowledge/knower)</t>
+          <t>Settled per Raghava (2026-08-31) after comparison with MVD and JV. This intentionally supersedes MVD's “enlightenment” for प्रबुद्धता because JV and the KD terminology already use “enlightenment” for बोध, the state activity of *buddhi*. Applied to the KD front matter and KD pp. 3, 18, 23, 31, 36, and 41–42. जागृति remains “awakening”; बोध remains “enlightenment.”</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>कर्त्ता, भोक्ता</t>
+          <t>विकास क्रम, विकासक्रम</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>karta, bhokta</t>
+          <t>vikas kram</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>doer, enjoyer</t>
+          <t>development progression</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Compositional; कर्त्ता=doer (agent), भोक्ता=enjoyer (experiencer of result). KD 3.18 title</t>
+          <t>Per MD-Mapping and MVD (not "developmental sequence"). Retroactively corrected remaining "developmental sequence" instances corpus-wide 2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>दृश, दृश्य, दर्शन</t>
+          <t>सदुपयोग</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>drish, drishya, darshan</t>
+          <t>sadupyog</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>seer, scene, worldview</t>
+          <t>right-use</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Aligned with MVD/JV usage and confirmed from the MVD source table: दृश = human life (the seer), दृश्य = coexistence (the scene), दर्शन = justice/dharma/truth (worldview)</t>
+          <t>Aligned 2026-08-23 with Rakesh Gupta's MVD/JV/SB terminology and MD-Mapping. Replaces the former KD variants "proper use," "good use," "good-use," and unhyphenated "right use."</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ध्यान, ध्याता, ध्येय</t>
+          <t>पदार्थावस्था, प्राणावस्था, जीवावस्था, ज्ञानावस्था</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>dhyan, dhyata, dhyeya</t>
+          <t>padarthavastha, pranavastha, jeevavastha, gyanavastha</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>concentration, one who concentrates, object of concentration</t>
+          <t>material order, biological order, animal order, knowledge order</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Aligned with MVD/JV usage and the parallel structure of ज्ञान/ज्ञाता/ज्ञेय</t>
+          <t>Aligned 2026-08-23 with Rakesh Gupta's four-orders terminology. Here अवस्था names an ontological order, not a generic "state"; ordinary state/status usages of अवस्था or स्थिति remain context-sensitive.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>साध्य, साधक, साधन</t>
+          <t>प्राणकोष</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>sadhya, sadhak, sadhan</t>
+          <t>pranakosh</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>aim, seeker, means</t>
+          <t>biological cell</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Per MD-Mapping: साध्य=aim, साधक=the seeker, साधन=the means. KD 3.17 triad</t>
+          <t>Aligned 2026-08-23 with MVD/JV. Replaces "prana cell," "prana-cell," and their plurals.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>अध्यात्मवाद, अधिदैवीवाद, अधिभौतिकवाद</t>
+          <t>व्यापक, व्यापक वस्तु</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>adhyatmavad, adhidaivikvad, adhibhautikvad</t>
+          <t>vyapak, vyapak vastu</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>*Adhyatma-vada*, *Adhidaivika-vada*, *Adhibhautika-vada*</t>
+          <t>Omnipresence; omnipresent reality</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Aligned with MVD/JV usage. KD 3.17 names the three classical schools collectively subsumed under आदर्शवाद (idealism)</t>
+          <t>Aligned 2026-08-23 with Rakesh Gupta. Use **Omnipresence** when व्यापक functions as the substantive reality and **omnipresent reality** for व्यापक वस्तु; adjectival predicate uses such as "God is omnipresent" remain grammatical. Distinct from सत्ता = Omnipotence.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ब्रह्मवाद, आत्मवाद, जातिवाद, नस्लवाद, वंशवाद</t>
+          <t>व्यवसाय</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>brahmavad, atmavad, jativad, naslvad, vanshvad</t>
+          <t>vyavasay</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Brahma-doctrine, self-doctrine, casteism, racism, lineage-ism</t>
+          <t>vocation</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>KD 3.16: not in MD-Mapping, compositional renderings of the "-वाद" (doctrine/ism) compounds</t>
+          <t>Aligned 2026-08-23 with MVD/JV. Replaces "occupation" in the vocation/work-domain sense.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>उद्घाता</t>
+          <t>दया, कृपा, करुणा</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>udghata</t>
+          <t>daya, kripa, karuna</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>herald</t>
+          <t>kindness, grace, compassion</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>KD 3.18: not in MD-Mapping, judgment call — the human being as the one who announces/evidences the awakened status</t>
+          <t>Aligned 2026-08-23 with Rakesh Gupta's consistent technical trio. The former KD compassion/grace/mercy wording was corrected throughout; दया in the associated social-value passages is kindness, and करुणा is compassion.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>कर्म अभ्यास</t>
+          <t>सारक, मारक</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>karma abhyas</t>
+          <t>sarak(ta), marak(ta)</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>practical-experiential method</t>
+          <t>vitalising, devitalising</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>KD 3.16: not in MD-Mapping under this compound; describes the Ayurveda/Unani diagnostic-treatment cycle (recognise disease → recognise medicine → treat, repeated until trust is earned)</t>
+          <t>Aligned with MVD/JV/SB usage. KD 3.10: the two modes of स्वभाव (essential nature) in the biological order — vitalising (*sarakta*) means being abundant in itself and useful to the animal order; devitalising (*marakta*) means obstructing one's own seed-abundance and being disease/death-causing to the animal order</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>औकात</t>
+          <t>पात्रता</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>aukat</t>
+          <t>patrata</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>standing</t>
+          <t>receptivity / worthiness (contextual)</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>KD 3.16: colloquial Hindi/Urdu term for capacity/standing, not in MD-Mapping; KD uses it for the fixed capacity of human body-composition across generations</t>
+          <t>EXPLICIT CONTEXTUAL RULE (confirmed 2026-08-23): preserve the technical क्षमता/योग्यता/पात्रता trio as **capacity / ability / receptivity**. These qualities are used when units recognise relationships and evaluate. Use **worthiness** only in KD 3.10's reciprocal दया/कृपा/करुणा (kindness/grace/compassion) definition, where substances are made available "in accordance with worthiness (*patrata*)"</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>वेदना</t>
+          <t>देव मानव, दिव्य मानव</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>vedana</t>
+          <t>dev manav, divya manav</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>pain</t>
+          <t>deific human, divine human</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>KD 1: "the pressure of accepting the unacceptable — that itself is vedana." Not the same word as संवेदना (sensation/sensitivity, already established); matches MVD's own usage ("दूसरों के कष्ट, दुःख, वेदना... सुख" → "suffering, misery, pain... of others")</t>
+          <t>Aligned 2026-08-23 with Rakesh Gupta's MVD terminology; supersedes the former KD "god-human" / "godly human" judgment call.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>संचेतना</t>
+          <t>पशु मानव, राक्षस मानव</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>sanchetana</t>
+          <t>pashu manav, rakshas manav</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>awareness</t>
+          <t>the animalistic human, the demonic human</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Settled per Raghava (2026-07-08), OVERRIDING MD-Mapping/SB's "Humane Consciousness" (SB Ch7 title) — "awareness" avoids collision with चेतना/जीव चेतना ("consciousness," e.g. "animal consciousness," KD 1) and चैतन्य ("conscious," e.g. "conscious activity," "material-conscious nature"), which stay untouched. Applies to संचेतनशील too ("awareness-endowed"). **Audit rule (2026-07-08 remediation):** grep for "human consciousness" / "higher-human consciousness" — replace with awareness / higher-awareness wherever the Hindi source is संचेतना; keep "consciousness" only for चेतना (e.g. "social consciousness" = सामाजिक चेतना, "consciousness-development" = चेतना विकास)</t>
+          <t>Per MD-Mapping ("animalistic human," "demonic human"). Retroactively corrected in KD-Karm-Darshan-English.md §3.9–3.10 on 2026-07-08 (previously "animal-human"/"demon-human") to match MD-Mapping exactly and align with KD 1's usage of the same pair</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>अभीष्ट</t>
+          <t>राशि विधि</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>abhīṣṭa</t>
+          <t>rashi vidhi</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>desire</t>
+          <t>the arrangement of quantity</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Settled per Raghava (2026-07-08), superseding this project's earlier "desideratum" (itself an override of MD-Mapping's "Aim," chosen to avoid colliding with साध्य=aim). Note: this reintroduces a collision with इच्छा (the general term for desire throughout KD) — अभीष्ट and इच्छा are now both "desire" in English; distinguish by context if needed (अभीष्ट is the wished-for/happiness-directed sense, इच्छा the general faculty/act of desiring). साध्य keeps "aim." Where the source explicitly glosses one with the other ("साध्य (अभीष्ट)"), rendered as "the aim (the desire)"</t>
+          <t>KD 3.9/3.10 closing line; not in MD-Mapping, compositional rendering (राशि = quantity/aggregate, विधि = method/arrangement)</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>कायिक</t>
+          <t>दृष्टा, ज्ञाता, ज्ञेय</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>kāyik</t>
+          <t>drishta, gyata, gyeya</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>physical</t>
+          <t>seer, knower, object of knowledge</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Settled per Raghava (2026-07-08), aligning with MD-Mapping's own value ("physical," glossed "duty/responsibility carried out through the body together with mentality"), superseding this project's earlier "bodily" (chosen to avoid colliding with भौतिक=physical). Note: this reintroduces that collision — कायिक and भौतिक are now both "physical" in English; भौतिक is the material/physical-world sense (e.g. "physical substances," "physical science"), कायिक specifically the bodily-action sense in the कायिक/वाचिक/मानसिक (physical/vocal/mental) and "triad of behaviour" groupings — distinguish by context if needed</t>
+          <t>Aligned with MVD/JV usage: ज्ञेय names the object-pole of ज्ञान/ज्ञाता (knowledge/knower)</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>कृत, कारित, अनुमोदित</t>
+          <t>कर्त्ता, भोक्ता</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>krit, karit, anumodit</t>
+          <t>karta, bhokta</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>done, caused, intended</t>
+          <t>doer, enjoyer</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Settled per Raghava (2026-07-08), superseding this project's earlier "done, caused-to-be-done, and approved"/"consented-to." MD-Mapping's कृत="doing," कारित="getting done," अनुमोदित="consenting" — kept close but simplified; अनुमोदित specifically rendered "intended" rather than "approved"/"consenting" per this decision. Retrofitted in KD-Karm-Darshan-English.md §3.11–3.12 (3 instances, including the related noun अनुमोदन→"intention") and KD-Karm-Darshan-English.md §3.16–3.18 (1 instance) on 2026-07-08</t>
+          <t>Compositional; कर्त्ता=doer (agent), भोक्ता=enjoyer (experiencer of result). KD 3.18 title</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>फल</t>
+          <t>दृश, दृश्य, दर्शन</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>phal</t>
+          <t>drish, drishya, darshan</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>result</t>
+          <t>seer, scene, worldview</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Settled per Raghava (2026-07-08), superseding this project's earlier "fruit" — "phal means result of the action (karma)." Retrofitted in KD-Karm-Darshan-English.md on 2026-07-08 wherever फल stood alone (not फलन=fruition, not a फल-परिणाम compound, not literal fruit as food). See परिणाम for the resolved collision and the फल-परिणाम compound convention</t>
+          <t>Aligned with MVD/JV usage and confirmed from the MVD source table: दृश = human life (the seer), दृश्य = coexistence (the scene), दर्शन = justice/dharma/truth (worldview)</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>परिणाम</t>
+          <t>ध्यान, ध्याता, ध्येय</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>parinam</t>
+          <t>dhyan, dhyata, dhyeya</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>result</t>
+          <t>concentration, one who concentrates, object of concentration</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>REALIGNED 2026-07-08 with MVD/SB: श्रम-गति-परिणाम → "Effort – Motion – Result" (MVD/SB title-page Principle; MVD p.11). Both फल and bare परिणाम render as "result" in English — acceptable overlap where Hindi also overlaps (फल-परिणाम compounds collapse to "result" rather than "result-consequence"). Idiomatic connectors ("as a result of X") unchanged. Retrofitted corpus-wide across all 9 translation files on 2026-07-08 remediation pass</t>
+          <t>Aligned with MVD/JV usage and the parallel structure of ज्ञान/ज्ञाता/ज्ञेय</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>अनुभूति</t>
+          <t>साध्य, साधक, साधन</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>anubhūti</t>
+          <t>sadhya, sadhak, sadhan</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>experiencing</t>
+          <t>aim, seeker, means</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Settled per Raghava (2026-08-23): **experiencing** is the activity at the lower-faculty / *chitta* level and remains distinct from अनुभव = **realisation**, which is established in *atma*. Do not collapse the two terms even where MVD/JV uses "realisation" more broadly.</t>
+          <t>Per MD-Mapping: साध्य=aim, साधक=the seeker, साधन=the means. KD 3.17 triad</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>सत्ता</t>
+          <t>अध्यात्मवाद, अधिदैवीवाद, अधिभौतिकवाद</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>sattā</t>
+          <t>adhyatmavad, adhidaivikvad, adhibhautikvad</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Omnipotence</t>
+          <t>*Adhyatma-vada*, *Adhidaivika-vada*, *Adhibhautika-vada*</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Per MD-Mapping. KD 1: the foundational basis of balance for all of nature ("अशेष प्रकृति का संतुलनाधार सत्ता ही है"); equated with अध्यात्म ("अध्यात्म (सत्ता) निरपेक्ष ज्ञान है")</t>
+          <t>Aligned with MVD/JV usage. KD 3.17 names the three classical schools collectively subsumed under आदर्शवाद (idealism)</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>अध्यात्म</t>
+          <t>ब्रह्मवाद, आत्मवाद, जातिवाद, नस्लवाद, वंशवाद</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>adhyātma</t>
+          <t>brahmavad, atmavad, jativad, naslvad, vanshvad</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>the Spirit</t>
+          <t>Brahma-doctrine, self-doctrine, casteism, racism, lineage-ism</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Per MD-Mapping ("The Spirit"). KD 1: "जड़-चैतन्यात्मक प्रकृति की आधारपूर्ण सत्ता ही अध्यात्म है" — glossed in-text as equivalent to सत्ता (Omnipotence), rendered "the Spirit (Omnipotence)" on first use</t>
+          <t>KD 3.16: not in MD-Mapping, compositional renderings of the "-वाद" (doctrine/ism) compounds</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>संस्कार</t>
+          <t>उद्घाता</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>sanskar</t>
+          <t>udghata</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>*sanskar* (left transliterated)</t>
+          <t>herald</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Per MD-Mapping (kept as "Sanskar," not translated). Settled per this project (2026-07-08): KD 1 uses संस्कार and संस्कृति together constantly (e.g. "संस्कार, संस्कृति व सभ्यता") — collapsing both to "culture" erases the distinction. संस्कार = the individual's cultural conditioning/refinement (kept as *sanskar*); संस्कृति = the collective/civilizational achievement (kept as "culture"); सभ्यता = "civilisation"</t>
+          <t>KD 3.18: not in MD-Mapping, judgment call — the human being as the one who announces/evidences the awakened status</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>संस्कृति</t>
+          <t>कर्म अभ्यास</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>sanskriti</t>
+          <t>karma abhyas</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>culture</t>
+          <t>practical-experiential method</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>See संस्कार above — kept distinct from it. सुसंस्कृति = "wholesome culture," विकृत संस्कृति = "corrupted culture"</t>
+          <t>KD 3.16: not in MD-Mapping under this compound; describes the Ayurveda/Unani diagnostic-treatment cycle (recognise disease → recognise medicine → treat, repeated until trust is earned)</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>सभ्यता</t>
+          <t>औकात</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>sabhyata</t>
+          <t>aukat</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>civilisation</t>
+          <t>standing</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Per MD-Mapping ("civilization, civility")</t>
+          <t>KD 3.16: colloquial Hindi/Urdu term for capacity/standing, not in MD-Mapping; KD uses it for the fixed capacity of human body-composition across generations</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>काम</t>
+          <t>वेदना</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>kama</t>
+          <t>vedana</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>lust / *kama* (contextual)</t>
+          <t>pain</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Settled per Raghava (2026-08-23): **lust** is acceptable where काम has that unambiguous sense. All current KD occurrences belong to the classical moksha–dharma–kama–artha life-aim listing, where "lust" would narrow the source; under the conflict rule these remain transliterated as ***kama***, glossed as desire on first use.</t>
+          <t>KD 1: "the pressure of accepting the unacceptable — that itself is vedana." Not the same word as संवेदना (sensation/sensitivity, already established); matches MVD's own usage ("दूसरों के कष्ट, दुःख, वेदना... सुख" → "suffering, misery, pain... of others")</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>अर्थ</t>
+          <t>संचेतना</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>artha</t>
+          <t>sanchetana</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>wealth / resources / meaning (contextual)</t>
+          <t>awareness</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Settled per Raghava (2026-08-23): use **wealth** in acquisition, economic, and धन-related contexts; **resources** where अर्थ denotes the means available as body, mind, and wealth; and **meaning** where the text explains the significance or sense of a concept.</t>
+          <t>Settled per Raghava (2026-07-08), OVERRIDING MD-Mapping/SB's "Humane Consciousness" (SB Ch7 title) — "awareness" avoids collision with चेतना/जीव चेतना ("consciousness," e.g. "animal consciousness," KD 1) and चैतन्य ("conscious," e.g. "conscious activity," "material-conscious nature"), which stay untouched. Applies to संचेतनशील too ("awareness-endowed"). **Audit rule (2026-07-08 remediation):** grep for "human consciousness" / "higher-human consciousness" — replace with awareness / higher-awareness wherever the Hindi source is संचेतना; keep "consciousness" only for चेतना (e.g. "social consciousness" = सामाजिक चेतना, "consciousness-development" = चेतना विकास)</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>कासा, आकूति, मेधा</t>
+          <t>अभीष्ट</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>kāsā, ākūti, medhā</t>
+          <t>abhīṣṭa</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>left transliterated</t>
+          <t>desire</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>DEFERRED REVIEW (2026-08-23): retain transliteration and the current first-use glosses pending explicit lexical review of this obscure योग-जन्य-बुद्धि triad</t>
+          <t>Settled per Raghava (2026-07-08), superseding this project's earlier "desideratum" (itself an override of MD-Mapping's "Aim," chosen to avoid colliding with साध्य=aim). Note: this reintroduces a collision with इच्छा (the general term for desire throughout KD) — अभीष्ट and इच्छा are now both "desire" in English; distinguish by context if needed (अभीष्ट is the wished-for/happiness-directed sense, इच्छा the general faculty/act of desiring). साध्य keeps "aim." Where the source explicitly glosses one with the other ("साध्य (अभीष्ट)"), rendered idiomatically as "the aim—the desired end".</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>मति, सुमति, अनुमति</t>
+          <t>कायिक</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>mati, sumati, anumati</t>
+          <t>kāyik</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>left transliterated</t>
+          <t>physical</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>KD 1: triad of "righteous-action-born intellect" (सुकर्म-जन्य-बुद्धि), not in MD-Mapping; left transliterated, glossed in-text</t>
+          <t>Settled per Raghava (2026-07-08), aligning with MD-Mapping's own value ("physical," glossed "duty/responsibility carried out through the body together with mentality"), superseding this project's earlier "bodily" (chosen to avoid colliding with भौतिक=physical). Note: this reintroduces that collision — कायिक and भौतिक are now both "physical" in English; भौतिक is the material/physical-world sense (e.g. "physical substances," "physical science"), कायिक specifically the bodily-action sense in the कायिक/वाचिक/मानसिक (physical/vocal/mental) and "triad of behaviour" groupings — distinguish by context if needed</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>अमति, कुमति, दुर्मति</t>
+          <t>कृत, कारित, अनुमोदित</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>amati, kumati, durmati</t>
+          <t>krit, karit, anumodit</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>left transliterated</t>
+          <t>done, caused, intended</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>KD 1: triad of "unrighteous-action-born tendency" (दुष्कर्म-जन्य-प्रवृत्ति), parallel to मति/सुमति/अनुमति; not in MD-Mapping</t>
+          <t>Settled per Raghava (2026-07-08), superseding this project's earlier "done, caused-to-be-done, and approved"/"consented-to." MD-Mapping's कृत="doing," कारित="getting done," अनुमोदित="consenting" — kept close but simplified; अनुमोदित specifically rendered "intended" rather than "approved"/"consenting" per this decision. Retrofitted in KD-Karm-Darshan-English.md §3.11–3.12 (3 instances, including the related noun अनुमोदन→"intention") and KD-Karm-Darshan-English.md §3.16–3.18 (1 instance) on 2026-07-08</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>निवृत्ति</t>
+          <t>फल</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>nivṛtti</t>
+          <t>phal</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>disencumberance</t>
+          <t>result</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Per MD-Mapping ("Disencumberance, Disinclination" — freedom from delusion, fear, bondage). KD 1: one link in a definitional chain (ascertainment → disencumberance → impetus/wisdom → ...)</t>
+          <t>Settled per Raghava (2026-07-08), superseding this project's earlier "fruit" — "phal means result of the action (karma)." Retrofitted in KD-Karm-Darshan-English.md on 2026-07-08 wherever फल stood alone (not फलन=fruition, not a फल-परिणाम compound, not literal fruit as food). See परिणाम for the resolved collision and the फल-परिणाम compound convention</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>संवेग</t>
+          <t>परिणाम</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>samveg</t>
+          <t>parinam</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>impetus</t>
+          <t>result</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Per MD-Mapping</t>
+          <t>REALIGNED 2026-07-08 with MVD/SB: श्रम-गति-परिणाम → "Effort – Motion – Result" (MVD/SB title-page Principle; MVD p.11). Both फल and bare परिणाम render as "result" in English — acceptable overlap where Hindi also overlaps (फल-परिणाम compounds collapse to "result" rather than "result-consequence"). Idiomatic connectors ("as a result of X") unchanged. Retrofitted corpus-wide across all 9 translation files on 2026-07-08 remediation pass</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>पुण्यात्मा, पापात्मा</t>
+          <t>अनुभूति</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>punyatma, papatma</t>
+          <t>anubhūti</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>the meritorious soul, the sinful soul</t>
+          <t>experiencing</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>KD 1: not in MD-Mapping as a pair; compositional (पुण्य=merit, पाप=sin, आत्मा=soul), paired with सुखी/दुखी (happy/unhappy) across the five states (individual/family/society/nation/international)</t>
+          <t>Settled per Raghava (2026-08-23): **experiencing** is the activity at the lower-faculty / *chitta* level and remains distinct from अनुभव = **realisation**, which is established in *atma*. Do not collapse the two terms even where MVD/JV uses "realisation" more broadly.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>स्थूल, सूक्ष्म, कारण</t>
+          <t>सत्ता</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>sthula, sukshma, karana</t>
+          <t>sattā</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>gross, subtle, causal</t>
+          <t>Omnipotence</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>KD 1: classical triad (not in MD-Mapping under this exact grouping) for the three levels at which direct-perception, inference, and testimony-activity, and independent/imitative/adherent tendency, all operate</t>
+          <t>Per MD-Mapping. KD 1: the foundational basis of balance for all of nature ("अशेष प्रकृति का संतुलनाधार सत्ता ही है"); equated with अध्यात्म ("अध्यात्म (सत्ता) निरपेक्ष ज्ञान है")</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>रजोगुण, तमोगुण, सत्वगुण</t>
+          <t>अध्यात्म</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>rajoguna, tamoguna, sattvaguna</t>
+          <t>adhyātma</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>left transliterated</t>
+          <t>the Spirit</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>KD 1: the classical three गुण (property-modes), mapped onto sam/visham/mediating (see सम-विषम-मध्यस्थ row above: sam=rajoguna, visham=tamoguna, mediating=sattvaguna); not in MD-Mapping, kept transliterated per standard practice for this well-known Sanskrit triad</t>
+          <t>Per MD-Mapping ("The Spirit"). KD 1: "जड़-चैतन्यात्मक प्रकृति की आधारपूर्ण सत्ता ही अध्यात्म है" — glossed in-text as equivalent to सत्ता (Omnipotence), rendered "the Spirit (Omnipotence)" on first use</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>नियम-त्रय, व्यवहार-त्रय, अन्वेषण-त्रय</t>
+          <t>संस्कार</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>niyam-tray, vyavahar-tray, anveshan-tray</t>
+          <t>sanskar</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>rule-trio, behaviour-trio, exploration-trio</t>
+          <t>*sanskar* (left transliterated)</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>KD 1: aligned with MVD/SB's fixed X-trio pattern; niyam-tray = intellectual/social/natural rule, vyavahar-tray = physical/vocal/mental behaviour, anveshan-tray = instincts-/motive-/truth-oriented exploration.</t>
+          <t>Per MD-Mapping (kept as "Sanskar," not translated). Settled per this project (2026-07-08): KD 1 uses संस्कार and संस्कृति together constantly (e.g. "संस्कार, संस्कृति व सभ्यता") — collapsing both to "culture" erases the distinction. संस्कार = the individual's cultural conditioning/refinement (kept as *sanskar*); संस्कृति = the collective/civilizational achievement (kept as "culture"); सभ्यता = "civilisation"</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>मानवीयतापूर्ण (X) / अतिमानवीयतापूर्ण (X)</t>
+          <t>संस्कृति</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>manviyatapurna, atimanviyatapurna</t>
+          <t>sanskriti</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>humane (X) / higher-humane (X)</t>
+          <t>culture</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>CORRECTION, 2026-07-08: MD-Mapping has direct rows मानवीयता पूर्ण आचरण = "Humane Conduct" and मानवीयता पूर्ण आचरण ज्ञान = "knowledge of humane conduct." MVD independently confirms in running prose: "...जीवन ज्ञान व मानवीयतापूर्ण आचरण ज्ञान..." → "...knowledge of jeevan and humane conduct" (MVD p.3); MVD also has a dedicated glossary entry "मानवीयतापूर्ण व्यवहार" → "Humane Behaviour" (MVD p.34). The "X-पूर्ण" suffix (X-filled/X-replete) is therefore a plain adjective in English ("humane"), not "conduct filled with humaneness" or "humaneness-replete conduct." Retrofitted in KD-Karm-Darshan-English.md (ch. 2) (7 instances) and KD-Karm-Darshan-English.md (ch. 1) (~15 instances, verified against source images pp.8, 9, 10, 11, 16, 18, 24, 28) on 2026-07-08, wherever मानवीयतापूर्ण/अतिमानवीयतापूर्ण directly modified a noun (आचरण, व्यवहार, स्वभाव, मानव, कार्यक्रम, पद्धति, etc.). Not touched: bare मानवीयता/अतिमानवीयता used as nouns ("in humaneness and higher-humaneness"), and unrelated "-पूर्ण" compounds on other roots (e.g. सत्यतापूर्ण = "truthfulness-replete," सहअस्तित्व-replete, ज्ञान-/विवेक-/विज्ञान-पूर्ण = "knowledge-/wisdom-/science-filled" — different words, out of scope for this correction). **CHAPTER 3 SWEEP, 2026-07-08:** the same "X-replete-with-humaneness"/"humanity-replete X" error (variant wordings of the same underlying मानवीयतापूर्ण mistranslation) was also found and fixed across chapter 3: KD-Karm-Darshan-English.md §3.4–3.6 (2 instances, including one inside the recurring three-part knowledge formula — see जीवन ज्ञान row), KD-Karm-Darshan-English.md §3.9–3.10 (4 instances, using "humanity-replete" rather than "humaneness-replete"), and KD-Karm-Darshan-English.md §3.16–3.18 (1 instance, inside the same three-part formula). KD-Karm-Darshan-English.md §3.1–3.3, KD-Karm-Darshan-English.md §3.7–3.8, and KD-Karm-Darshan-English.md §3.13–3.15 had no instances of this error</t>
+          <t>See संस्कार above — kept distinct from it. सुसंस्कृति = "wholesome culture," विकृत संस्कृति = "corrupted culture"</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>जीवन ज्ञान</t>
+          <t>सभ्यता</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>jeevan gyan</t>
+          <t>sabhyata</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>knowledge of jeevan</t>
+          <t>civilisation</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>CORRECTION, 2026-07-08: MVD confirms "जीवन ज्ञान" → "knowledge of jeevan" in both instances of the recurring three-part formula (अस्तित्व दर्शन ज्ञान / जीवन ज्ञान / मानवीयतापूर्ण आचरण ज्ञान): "...जीवन ज्ञान व मानवीयतापूर्ण आचरण ज्ञान..." → "...knowledge of jeevan and humane conduct" (MVD p.3), and "...चैतन्य प्रकृति रूपी जीवन ज्ञान..." → "...knowledge of jeevan in the form of sentient nature..." (MVD p.259). Keeps the "knowledge of X" pattern parallel across all three terms, matching the established renderings of the other two (see दर्शन and मानवीयतापूर्ण rows above/below). Retrofitted in KD-Karm-Darshan-English.md (ch. 2)'s opening line (had "jeevan knowledge") on 2026-07-08. Also retrofitted across all of chapter 3 on 2026-07-08 (see चैप्टर 3 sweep note under the मानवीयतापूर्ण row): "jeevan-knowledge"/"jeevan knowledge" → "the knowledge of jeevan" in KD-Karm-Darshan-English.md §3.4–3.6, KD-Karm-Darshan-English.md §3.11–3.12 (×2), and KD-Karm-Darshan-English.md §3.16–3.18 (×2); "darshan-knowledge" and bare "darshan" (in the same non-triad, non-proper-noun sense) → "the knowledge of the holistic view"/"the holistic view" in KD-Karm-Darshan-English.md §3.11–3.12 (3 instances)</t>
+          <t>Per MD-Mapping ("civilization, civility")</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>गम्यता</t>
+          <t>काम</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>gamyata</t>
+          <t>kama</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>the destination</t>
+          <t>lust / *kama* (contextual)</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>KD 1: abstract-noun form of गम्य/गन्तव्य (already "destination" per KD 3.12/3.14 glossary row); not in MD-Mapping, treated as the same concept</t>
+          <t>Settled per Raghava (2026-08-23): **lust** is acceptable where काम has that unambiguous sense. All current KD occurrences belong to the classical moksha–dharma–kama–artha life-aim listing, where "lust" would narrow the source; under the conflict rule these remain transliterated as ***kama***, glossed as desire on first use.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>दर्शन (bare, or in "X दर्शन ज्ञान" / "X दर्शन" / "दर्शन-क्षमता" compounds)</t>
+          <t>अर्थ</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>darshan</t>
+          <t>artha</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>the holistic view (of X)</t>
+          <t>wealth / resources / meaning (contextual)</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>CORRECTION, 2026-07-08: MD-Mapping has a direct row for bare दर्शन = "Holistic view, Worldview, Philosophy," plus confirmed compound rows सह-अस्तित्व दर्शन ज्ञान = "knowledge of holistic view of coexistence" and मानव कर्म दर्शन (this book's own title) = "Holistic view of Human Action." MVD independently confirms the exact KD 2 phrase: "अस्तित्व दर्शन ज्ञान" → "knowledge of the holistic view of existence" (MVD p.259, near-verbatim to KD 2's opening line). Retrofitted in KD-Karm-Darshan-English.md (ch. 2) (4 instances: the opening "अस्तित्व दर्शन ज्ञान," "(पूर्ण-दर्शन)," and two "दर्शन-क्षमता" instances) and in KD-Karm-Darshan-English.md (ch. 1) (10 instances, verified page-by-page against the source images: pp.1, 3, 13, 14, 15 (×2), 16 (×2 continuing to 17), 17 (×2)) on 2026-07-08. Excluded from this correction (kept as-is): the proper noun "Madhyasth Darshan" (book/philosophy name, p.19, always transliterated); the दृश/दृश्य/दर्शन seer-triad sense (KD 3.17, see separate row below, a distinct established convention); and the verbal usage "X का दर्शन करना" = "to behold X" (KD 1 p.24, four instances, e.g. "vritti... beholds the mind" — this is the common devotional-register verb "to behold/have sight of," not the noun "holistic view," and one redundant instance ("beholds the darshan of the less-awakened") was simplified to "beholds the less-awakened" accordingly</t>
+          <t>Settled per Raghava (2026-08-23): use **wealth** in acquisition, economic, and धन-related contexts; **resources** where अर्थ denotes the means available as body, mind, and wealth; and **meaning** where the text explains the significance or sense of a concept. Source-image review (2026-10-04) retains a close literal rendering of the compressed complete-meaning statements on pp.3 and 23; these do not settle every contextual sense of अर्थ.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>उपासना</t>
+          <t>कासा, आकूति, मेधा</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>upāsanā</t>
+          <t>kāsā, ākūti, medhā</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Upasana (worship)</t>
+          <t>left transliterated</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>KD 2 chapter title. Per MD-Mapping ("worship, upasana") and SB's own English rendering (SB p.23: "worship, archana, yoga, sadhana, and upasana" — SB itself leaves उपासना transliterated rather than translating it). Kept transliterated as "upasana" throughout, glossed "(worship)" on first use, per this project's practice for the book's central chapter-2 term</t>
+          <t>Source-image review (2026-10-04): KD p. 5 lists these as योग-जन्य-बुद्धि and visibly varies आकूति / आकृति between enumeration and explanation. P. 47 explicitly associates the three with activity-, desire-, and knowledge-power. MVD printed/PDF pp. 324 and 330 and MD-Mapping row 1215 give a medha/intellect precedent but do not establish English names for the complete KD trio. Retain all three transliterations; do not collapse मेधा into मेधस = brain or silently normalise the p. 5 variation.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>विवेक</t>
+          <t>मति, सुमति, अनुमति</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>vivek</t>
+          <t>mati, sumati, anumati</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>wisdom</t>
+          <t>left transliterated</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Per MD-Mapping ("wisdom"); KD 2 chapter subtitle ("उपासना – विवेक" → "Upasana – Wisdom"). Remaining "discretion" variants in the KD body were corrected 2026-08-23.</t>
+          <t>KD 1: triad of "righteous-action-born intellect" (सुकर्म-जन्य-बुद्धि), not in MD-Mapping; left transliterated, glossed in-text</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>नश्वरत्व</t>
+          <t>अमति, कुमति, दुर्मति</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>nashwaratva</t>
+          <t>amati, kumati, durmati</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>mortality</t>
+          <t>left transliterated</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Aligned with MVD/JV usage. KD 2 opening line contrasts the immortality of jeevan with the mortality of the body</t>
+          <t>KD 1: triad of "unrighteous-action-born tendency" (दुष्कर्म-जन्य-प्रवृत्ति), parallel to मति/सुमति/अनुमति; not in MD-Mapping</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>कूटस्थ, रूपस्थ, आत्मस्थ (उपासना के रूप में)</t>
+          <t>निवृत्ति</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>kutastha, rupastha, atmastha</t>
+          <t>nivṛtti</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>kutastha upasana (abiding in the immutable), rupastha upasana (abiding in form), atmastha upasana (abiding in the self)</t>
+          <t>disencumberance</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>KD 2: the three loci/modes of upasana (undertaken respectively for complete realisation; for proximity to a form together with magnificence; and as the process of reflection/*pratyavartan*). Not in MD-Mapping; left transliterated with compositional glosses, judgment call</t>
+          <t>Per MD-Mapping ("Disencumberance, Disinclination" — freedom from delusion, fear, bondage). KD 1: one link in a definitional chain (ascertainment → disencumberance → impetus/wisdom → ...)</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>देवात्मा, भूतात्मा, दिव्यात्मा</t>
+          <t>संवेग</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>devatma, bhootatma, divyatma</t>
+          <t>samveg</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>deific self, elemental self, divine self</t>
+          <t>impetus</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Aligned with MVD/JV usage and the established आत्मा = self rendering; the three states are tied to absolute-oneness (*tadatmya*) with adhidaivik facts, adhibhautik elements, and adhyatma respectively</t>
+          <t>Per MD-Mapping</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>जीवन-पुंज</t>
+          <t>पुण्यात्मा, पापात्मा</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>jeevan-punj</t>
+          <t>punyatma, papatma</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>jeevan-cloud</t>
+          <t>the meritorious soul, the sinful soul</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Aligned 2026-08-23 with Rakesh Gupta's explicit MVD rendering, **Jeevan-cloud (*punj*)**. MVD defines पुंज as the shape created by the limits of a sentient unit's activity. Supersedes the former KD-specific **jeevan-cluster**</t>
+          <t>KD 1: not in MD-Mapping as a pair; compositional (पुण्य=merit, पाप=sin, आत्मा=soul), paired with सुखी/दुखी (happy/unhappy) across the five states (individual/family/society/nation/international)</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>प्राण वायु, प्राणवायु</t>
+          <t>स्थूल, सूक्ष्म, कारण</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>pranavayu</t>
+          <t>sthula, sukshma, karana</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>*pranavayu* (left transliterated)</t>
+          <t>gross, subtle, causal</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>EXPLICIT DECISION (2026-08-23): retain the technical term as **pranavayu**, without translating it as "life-breath" or separating it as *pran vayu*. In KD 2 p.31, pranavayu controls the gross body. This is a deliberate KD choice differing from MVD's "prana-air"</t>
+          <t>KD 1: classical triad (not in MD-Mapping under this exact grouping) for the three levels at which direct-perception, inference, and testimony-activity, and independent/imitative/adherent tendency, all operate</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>विषय-चतुष्टय, चतुर्विषय</t>
+          <t>रजोगुण, तमोगुण, सत्वगुण</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>vishaya-chatushtaya</t>
+          <t>rajoguna, tamoguna, sattvaguna</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>instincts-quad / the four-object domain</t>
+          <t>left transliterated</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Per MD-Mapping ("विषय चतुष्टय = instincts-quad"). KD 2 uses both विषय-चतुष्टय and the equivalent चतुर्विषय; both rendered with the same established English</t>
+          <t>KD 1: the classical three गुण (property-modes), mapped onto sam/visham/mediating (see सम-विषम-मध्यस्थ row above: sam=rajoguna, visham=tamoguna, mediating=sattvaguna); not in MD-Mapping, kept transliterated per standard practice for this well-known Sanskrit triad</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ऐषणा-त्रय</t>
+          <t>नियम-त्रय, व्यवहार-त्रय, अन्वेषण-त्रय</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>eshana-traya</t>
+          <t>niyam-tray, vyavahar-tray, anveshan-tray</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>the "motive-trio"</t>
+          <t>rule-trio, behaviour-trio, exploration-trio</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>KD 2: paired with विषय-चतुष्टय, tied to adhidaivik (social/behavioural) values. Aligned 2026-08-23 with MD-Mapping and MVD's fixed **motive-trio**, superseding this project's former "desires-trio." Left transliterated (*eshana-traya*) on first use.</t>
+          <t>KD 1: aligned with MVD/SB's fixed X-trio pattern; niyam-tray = intellectual/social/natural rule, vyavahar-tray = physical/vocal/mental behaviour, anveshan-tray = instincts-/motive-/truth-oriented exploration.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>विद्या, उपविद्या, क्षुद्र विद्या</t>
+          <t>मानवीयतापूर्ण (X) / अतिमानवीयतापूर्ण (X)</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>vidya, upavidya, kshudra vidya</t>
+          <t>manviyatapurna, atimanviyatapurna</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>learning, sub-learning, base learning</t>
+          <t>humane (X) / higher-humane (X)</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>KD 2: the three qualities of upasana outcome, tied respectively to divine, deific, and elemental souls. विद्या = "learning" per MD-Mapping; उपविद्या and क्षुद्र विद्या are KD coinages not in MD-Mapping, compositional (उप- = sub-, क्षुद्र = base/petty)</t>
+          <t>CORRECTION, 2026-07-08: MD-Mapping has direct rows मानवीयता पूर्ण आचरण = "Humane Conduct" and मानवीयता पूर्ण आचरण ज्ञान = "knowledge of humane conduct." MVD independently confirms in running prose: "...जीवन ज्ञान व मानवीयतापूर्ण आचरण ज्ञान..." → "...knowledge of jeevan and humane conduct" (MVD p.3); MVD also has a dedicated glossary entry "मानवीयतापूर्ण व्यवहार" → "Humane Behaviour" (MVD p.34). The "X-पूर्ण" suffix (X-filled/X-replete) is therefore a plain adjective in English ("humane"), not "conduct filled with humaneness" or "humaneness-replete conduct." Retrofitted in KD-Karm-Darshan-English.md (ch. 2) (7 instances) and KD-Karm-Darshan-English.md (ch. 1) (~15 instances, verified against source images pp.8, 9, 10, 11, 16, 18, 24, 28) on 2026-07-08, wherever मानवीयतापूर्ण/अतिमानवीयतापूर्ण directly modified a noun (आचरण, व्यवहार, स्वभाव, मानव, कार्यक्रम, पद्धति, etc.). Not touched: bare मानवीयता/अतिमानवीयता used as nouns ("in humaneness and higher-humaneness"), and unrelated "-पूर्ण" compounds on other roots (e.g. सत्यतापूर्ण = "truthfulness-replete," सहअस्तित्व-replete, ज्ञान-/विवेक-/विज्ञान-पूर्ण = "knowledge-/wisdom-/science-filled" — different words, out of scope for this correction). **CHAPTER 3 SWEEP, 2026-07-08:** the same "X-replete-with-humaneness"/"humanity-replete X" error (variant wordings of the same underlying मानवीयतापूर्ण mistranslation) was also found and fixed across chapter 3: KD-Karm-Darshan-English.md §3.4–3.6 (2 instances, including one inside the recurring three-part knowledge formula — see जीवन ज्ञान row), KD-Karm-Darshan-English.md §3.9–3.10 (4 instances, using "humanity-replete" rather than "humaneness-replete"), and KD-Karm-Darshan-English.md §3.16–3.18 (1 instance, inside the same three-part formula). KD-Karm-Darshan-English.md §3.1–3.3, KD-Karm-Darshan-English.md §3.7–3.8, and KD-Karm-Darshan-English.md §3.13–3.15 had no instances of this error</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>नियम-त्रय</t>
+          <t>जीवन ज्ञान</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>niyam-tray</t>
+          <t>jeevan gyan</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>the "rule-trio"</t>
+          <t>knowledge of jeevan</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Reused from KD 1; KD 2 explicitly glosses it as "बौद्धिक, सामाजिक एवं प्राकृतिक" (intellectual, social, and natural), confirming the KD 1 gloss.</t>
+          <t>CORRECTION, 2026-07-08: MVD confirms "जीवन ज्ञान" → "knowledge of jeevan" in both instances of the recurring three-part formula (अस्तित्व दर्शन ज्ञान / जीवन ज्ञान / मानवीयतापूर्ण आचरण ज्ञान): "...जीवन ज्ञान व मानवीयतापूर्ण आचरण ज्ञान..." → "...knowledge of jeevan and humane conduct" (MVD p.3), and "...चैतन्य प्रकृति रूपी जीवन ज्ञान..." → "...knowledge of jeevan in the form of sentient nature..." (MVD p.259). Keeps the "knowledge of X" pattern parallel across all three terms, matching the established renderings of the other two (see दर्शन and मानवीयतापूर्ण rows above/below). Retrofitted in KD-Karm-Darshan-English.md (ch. 2)'s opening line (had "jeevan knowledge") on 2026-07-08. Also retrofitted across all of chapter 3 on 2026-07-08 (see चैप्टर 3 sweep note under the मानवीयतापूर्ण row): "jeevan-knowledge"/"jeevan knowledge" → "the knowledge of jeevan" in KD-Karm-Darshan-English.md §3.4–3.6, KD-Karm-Darshan-English.md §3.11–3.12 (×2), and KD-Karm-Darshan-English.md §3.16–3.18 (×2); "darshan-knowledge" and bare "darshan" (in the same non-triad, non-proper-noun sense) → "the knowledge of the holistic view"/"the holistic view" in KD-Karm-Darshan-English.md §3.11–3.12 (3 instances)</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>जागृति-त्रय, शक्ति-त्रय</t>
+          <t>गम्यता</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>jagriti-traya, shakti-traya</t>
+          <t>gamyata</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>the "awakening-trio", the "powers-trio"</t>
+          <t>the destination</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>KD 2: parallel formations on the established "X-trio" pattern (see नियम-त्रय, व्यवहार-त्रय, अन्वेषण-त्रय). जागृति-त्रय = awakening of इच्छा/क्रिया/ज्ञान शक्ति (desire-, activity-, and knowledge-power); शक्ति-त्रय = the same three powers named directly.</t>
+          <t>KD 1: abstract-noun form of गम्य/गन्तव्य (already "destination" per KD 3.12/3.14 glossary row); not in MD-Mapping, treated as the same concept</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>इच्छा शक्ति, क्रिया शक्ति, ज्ञान शक्ति</t>
+          <t>दर्शन (bare, or in "X दर्शन ज्ञान" / "X दर्शन" / "दर्शन-क्षमता" compounds)</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>ichha shakti, kriya shakti, gyan shakti</t>
+          <t>darshan</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>desire-power, activity-power, knowledge-power</t>
+          <t>the holistic view (of X)</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>KD 2: classical triad (kriya-shakti/iccha-shakti/jnana-shakti); not in MD-Mapping under this grouping, compositional</t>
+          <t>CORRECTION, 2026-07-08: MD-Mapping has a direct row for bare दर्शन = "Holistic view, Worldview, Philosophy," plus confirmed compound rows सह-अस्तित्व दर्शन ज्ञान = "knowledge of holistic view of coexistence" and मानव कर्म दर्शन (this book's own title) = "Holistic view of Human Action." MVD independently confirms the exact KD 2 phrase: "अस्तित्व दर्शन ज्ञान" → "knowledge of the holistic view of existence" (MVD p.259, near-verbatim to KD 2's opening line). Retrofitted in KD-Karm-Darshan-English.md (ch. 2) (4 instances: the opening "अस्तित्व दर्शन ज्ञान," "(पूर्ण-दर्शन)," and two "दर्शन-क्षमता" instances) and in KD-Karm-Darshan-English.md (ch. 1) (10 instances, verified page-by-page against the source images: pp.1, 3, 13, 14, 15 (×2), 16 (×2 continuing to 17), 17 (×2)) on 2026-07-08. Excluded from this correction (kept as-is): the proper noun "Madhyasth Darshan" (book/philosophy name, p.19, always transliterated); the दृश/दृश्य/दर्शन seer-triad sense (KD 3.17, see separate row below, a distinct established convention); and the verbal usage "X का दर्शन करना" = "to behold X" (KD 1 p.24, four instances, e.g. "vritti... beholds the mind" — this is the common devotional-register verb "to behold/have sight of," not the noun "holistic view," and one redundant instance ("beholds the darshan of the less-awakened") was simplified to "beholds the less-awakened" accordingly</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ता-त्रय</t>
+          <t>उपासना</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>tā-traya</t>
+          <t>upāsanā</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>the "*-tā*-trio"</t>
+          <t>Upasana (worship)</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>KD 2 p.44: "स्वयं का मूल्यांकन 'ता-त्रय' की सीमा में होता है" (self-evaluation occurs within the domain of the tā-traya). UNCERTAIN — not in MD-Mapping; the surrounding text repeatedly pairs क्षमता/योग्यता/पात्रता (capacity/ability/receptivity), which is the likeliest referent, but the source does not gloss the compound explicitly here. Left transliterated and flagged for human review rather than asserted</t>
+          <t>KD 2 chapter title. Per MD-Mapping ("worship, upasana") and SB's own English rendering (SB p.23: "worship, archana, yoga, sadhana, and upasana" — SB itself leaves उपासना transliterated rather than translating it). Kept transliterated as "upasana" throughout, glossed "(worship)" on first use, per this project's practice for the book's central chapter-2 term</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>अनुक्षण-विक्षण-वृत्ति, सहजावृत्ति</t>
+          <t>विवेक</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>anukshan-vikshan-vritti, sahajavritti</t>
+          <t>vivek</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>the moment-to-moment unbroken tendency; natural-recurrence</t>
+          <t>wisdom</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>KD 2 p.43/45: defined in-text as "the disappearance of moment-to-moment mediating obstruction." Not in MD-Mapping; compositional, glossed in-text on first use</t>
+          <t>Per MD-Mapping ("wisdom"); KD 2 chapter subtitle ("उपासना – विवेक" → "Upasana – Wisdom"). Remaining "discretion" variants in the KD body were corrected 2026-08-23.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>तदाकार</t>
+          <t>नश्वरत्व</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>tadakar</t>
+          <t>nashwaratva</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>absolute-resonance</t>
+          <t>mortality</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Aligned with Rakesh Gupta's MVD and MD-Mapping row 929 on 2026-08-23. MVD renders तदाकार as **absolute-resonance** both in its definition (p.80) and in the relational construction "achieving absolute-resonance ... with understanding" (Hindi p.149 / English p.150). KD 2 pp.40–41 applies the same construction to the *antahkarana* and to water, fire, air, and light; render it grammatically as "brought into absolute-resonance with" or "attaining absolute-resonance with." Supersedes the former literal **take-/taking-the-form-of** rendering. JV and SB contain no competing precedent.</t>
+          <t>Aligned with MVD/JV usage. KD 2 opening line contrasts the immortality of jeevan with the mortality of the body</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>सम्यक्-बोध, सम्यक् संकल्प</t>
+          <t>कूटस्थ, रूपस्थ, आत्मस्थ (उपासना के रूप में)</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>samyak-bodh, samyak sankalp</t>
+          <t>kutastha, rupastha, atmastha</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>right-enlightenment, right resolve</t>
+          <t>kutastha upasana (abiding in the immutable), rupastha upasana (abiding in form), atmastha upasana (abiding in the self)</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>KD 2: सम्यक् = classical "right/proper" prefix + established बोध (enlightenment) and संकल्प (resolve); not in MD-Mapping under this compound, compositional</t>
+          <t>KD 2: the three loci/modes of upasana (undertaken respectively for complete realisation; for proximity to a form together with magnificence; and as the process of reflection/*pratyavartan*). Not in MD-Mapping; left transliterated with compositional glosses, judgment call</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>सद्विवेक</t>
+          <t>देवात्मा, भूतात्मा, दिव्यात्मा</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>sad-vivek</t>
+          <t>devatma, bhootatma, divyatma</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>right-wisdom</t>
+          <t>deific self, elemental self, divine self</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>KD 2 p.46: सत् (right) + विवेक (wisdom); not in MD-Mapping, compositional, parallel to सम्यक्-बोध</t>
+          <t>Aligned with MVD/JV usage and the established आत्मा = self rendering; the three states are tied to absolute-oneness (*tadatmya*) with adhidaivik facts, adhibhautik elements, and adhyatma respectively</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>साध्य, साधक, साधन (उपासना में)</t>
+          <t>जीवन-पुंज</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>sadhya, sadhak, sadhan</t>
+          <t>jeevan-punj</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>the aim, the seeker, the means</t>
+          <t>jeevan-cloud</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Reused from KD 3.17 (see row above) — KD 2 p.38 requires the same triad to remain integrated within upasana for it to succeed</t>
+          <t>Aligned 2026-08-23 with Rakesh Gupta's explicit MVD rendering, **Jeevan-cloud (*punj*)**. MVD defines पुंज as the shape created by the limits of a sentient unit's activity. Supersedes the former KD-specific **jeevan-cluster**</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>मत, सम्प्रदाय, वर्ग</t>
+          <t>प्राण वायु, प्राणवायु</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>mat, sampradaya, varga</t>
+          <t>pranavayu</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>creed, sect, class</t>
+          <t>*pranavayu* (left transliterated)</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>KD 2 p.38: "मानव के स्वधर्म में ही मत, सम्प्रदाय, वर्ग तिरोहित हो जाते हैं" — not in MD-Mapping under this triad, compositional</t>
+          <t>EXPLICIT DECISION (2026-08-23): retain the technical term as **pranavayu**, without translating it as "life-breath" or separating it as *pran vayu*. In KD 2 p.31, pranavayu controls the gross body. This is a deliberate KD choice differing from MVD's "prana-air"</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>वर्ग-भावना</t>
+          <t>विषय-चतुष्टय, चतुर्विषय</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>varga-bhavana</t>
+          <t>vishaya-chatushtaya</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>class-sentiment</t>
+          <t>instincts-quad / the four-object domain</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>KD 2 p.35: not in MD-Mapping, compositional (वर्ग = class/group + भावना = sentiment)</t>
+          <t>Per MD-Mapping ("विषय चतुष्टय = instincts-quad"). KD 2 uses both विषय-चतुष्टय and the equivalent चतुर्विषय; both rendered with the same established English</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>सर्वमंगल, मांगल्य</t>
+          <t>ऐषणा-त्रय</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>sarva mangal, mangalya</t>
+          <t>eshana-traya</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>universal welfare, welfare</t>
+          <t>the "motive-trio"</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>KD 2: सर्व मंगल (universal welfare) is the shared aim underlying all upasanas; मांगल्य is its abstract-noun cognate. Not in MD-Mapping, compositional</t>
+          <t>KD 2: paired with विषय-चतुष्टय, tied to adhidaivik (social/behavioural) values. Aligned 2026-08-23 with MD-Mapping and MVD's fixed **motive-trio**, superseding this project's former "desires-trio." Left transliterated (*eshana-traya*) on first use.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>अभ्युदय</t>
+          <t>विद्या, उपविद्या, क्षुद्र विद्या</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>abhyudaya</t>
+          <t>vidya, upavidya, kshudra vidya</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>comprehensive resolution</t>
+          <t>learning, sub-learning, base learning</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Settled per Raghava (2026-07-08), aligned with MVD p.23 (supersedes "well-being" / "rise"); KD 2 p.35 and KD 3.12 p.116 in KD-Karm-Darshan-English.md</t>
+          <t>KD 2: the three qualities of upasana outcome, tied respectively to divine, deific, and elemental souls. विद्या = "learning" per MD-Mapping; उपविद्या and क्षुद्र विद्या are KD coinages not in MD-Mapping, compositional (उप- = sub-, क्षुद्र = base/petty) Source-image review of p. 146 (2026-10-04) likewise retains विद्या = learning in the three named forms Shakti-vidya, Shiva-vidya and Vishnu-vidya, replacing the former ambiguous Shakti-/Shiva-/Vishnu-knowledge labels.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>न्यूनातिरेक</t>
+          <t>नियम-त्रय</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>nyoonatirek</t>
+          <t>niyam-tray</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>deficiency-or-excess</t>
+          <t>the "rule-trio"</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>KD 2 p.44: न्यून (deficient) + अतिरेक (excess); describes faulty (imposed) self-evaluation. Not in MD-Mapping, compositional</t>
+          <t>Reused from KD 1; KD 2 explicitly glosses it as "बौद्धिक, सामाजिक एवं प्राकृतिक" (intellectual, social, and natural), confirming the KD 1 gloss.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>प्रभुसत्ता</t>
+          <t>जागृति-त्रय, शक्ति-त्रय</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>prabhusatta</t>
+          <t>jagriti-traya, shakti-traya</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>supreme order</t>
+          <t>the "awakening-trio", the "powers-trio"</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Aligned with MVD/JV usage; kept distinct from संप्रभुता = sovereignty and साम्राज्य = empire</t>
+          <t>KD 2: parallel formations on the established "X-trio" pattern (see नियम-त्रय, व्यवहार-त्रय, अन्वेषण-त्रय). जागृति-त्रय = awakening of इच्छा/क्रिया/ज्ञान शक्ति (desire-, activity-, and knowledge-power); शक्ति-त्रय = the same three powers named directly.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>साम्राज्य</t>
+          <t>इच्छा शक्ति, क्रिया शक्ति, ज्ञान शक्ति</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>samrajya</t>
+          <t>ichha shakti, kriya shakti, gyan shakti</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>dominion</t>
+          <t>desire-power, activity-power, knowledge-power</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>KD 2 p.48: kept as "dominion" rather than "sovereignty" specifically to avoid collision with प्रभुसत्ता above — both appear in this chapter as distinct stages in a causal chain</t>
+          <t>KD 2: classical triad (kriya-shakti/iccha-shakti/jnana-shakti); not in MD-Mapping under this grouping, compositional</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>मानवेतर प्राणी</t>
+          <t>ता-त्रय</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>manavetar prani</t>
+          <t>tā-traya</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>beings other than human</t>
+          <t>the "*-tā*-trio"</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>KD 2 p.48: parallel to the already-established मानवेत्तर प्रकृति = "nature-other-than-human" (KD 3.7 glossary row)</t>
+          <t>KD 2 p. 44 places self-evaluation within the domain of this compound but does not identify its members. Direct contextual review of pp. 41–47 and bounded searches of MVD/SB/JV and MD-Mapping (2026-10-04) did not establish a definition. Capacity/ability/receptivity remains a candidate only; suffix similarity does not prove the referent. Retain the transliteration.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>विराग, वैराग्य</t>
+          <t>अनुक्षण-विक्षण-वृत्ति, सहजावृत्ति</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>virag, vairagya</t>
+          <t>anukshan-vikshan-vritti, sahajavritti</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>dispassion / detachment</t>
+          <t>the moment-to-moment unbroken tendency; natural-recurrence</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Aligned with MVD/JV usage: विराग = dispassion; वैराग्य = detachment; पर-वैराग्य = supreme-detachment</t>
+          <t>KD 2 p.43/45: defined in-text as "the disappearance of moment-to-moment mediating obstruction." Not in MD-Mapping; compositional, glossed in-text on first use</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>आत्म-दीपन</t>
+          <t>तदाकार</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>atma-deepan</t>
+          <t>tadakar</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>self-illumination</t>
+          <t>absolute-resonance</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>KD 2 p.48: दीपन = illumination/kindling; not in MD-Mapping, compositional, part of the आत्म-बोध → आत्म-दीपन → आत्म-विश्वास → ... causal chain</t>
+          <t>Aligned with Rakesh Gupta's MVD and MD-Mapping row 929 on 2026-08-23. MVD renders तदाकार as **absolute-resonance** both in its definition (p.80) and in the relational construction "achieving absolute-resonance ... with understanding" (Hindi p.149 / English p.150). KD 2 pp.40–41 applies the same construction to the *antahkarana* and to water, fire, air, and light; render it grammatically as "brought into absolute-resonance with" or "attaining absolute-resonance with." Supersedes the former literal **take-/taking-the-form-of** rendering. JV and SB contain no competing precedent.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>पाण्डित्य</t>
+          <t>सम्यक्-बोध, सम्यक् संकल्प</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>panditya</t>
+          <t>samyak-bodh, samyak sankalp</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>scholarliness</t>
+          <t>right-enlightenment, right resolve</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Per MD-Mapping; first appearance in the KD corpus at KD 2 p.31 ("परिमार्जनशीलता ही निपुणता एवं कुशलता, पाण्डित्य है")</t>
+          <t>KD 2: सम्यक् = classical "right/proper" prefix + established बोध (enlightenment) and संकल्प (resolve); not in MD-Mapping under this compound, compositional</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>कासा, आकूति, मेधा (क्रिया/इच्छा/ज्ञान शक्ति के रूप में)</t>
+          <t>सद्विवेक</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>kāsā, ākūti, medhā</t>
+          <t>sad-vivek</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>activity-power (kāsā), desire-power (ākūti), knowledge-power (medhā)</t>
+          <t>right-wisdom</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>DEFERRED REVIEW (2026-08-23): retain the current mapping pending explicit lexical review. KD 2 p.47 re-invokes the KD 1 triad, now explicitly mapped onto क्रिया/इच्छा/ज्ञान शक्ति</t>
+          <t>KD 2 p.46: सत् (right) + विवेक (wisdom); not in MD-Mapping, compositional, parallel to सम्यक्-बोध</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
+          <t>साध्य, साधक, साधन (उपासना में)</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>sadhya, sadhak, sadhan</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>the aim, the seeker, the means</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Reused from KD 3.17 (see row above) — KD 2 p.38 requires the same triad to remain integrated within upasana for it to succeed</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>मत, सम्प्रदाय, वर्ग</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>mat, sampradaya, varga</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>creed, sect, class</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>KD 2 p.38: "मानव के स्वधर्म में ही मत, सम्प्रदाय, वर्ग तिरोहित हो जाते हैं" — not in MD-Mapping under this triad, compositional</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>वर्ग-भावना</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>varga-bhavana</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>class-sentiment</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>KD 2 p.35: not in MD-Mapping, compositional (वर्ग = class/group + भावना = sentiment)</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>सर्वमंगल, मांगल्य</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>sarva mangal, mangalya</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>universal welfare, welfare</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>KD 2: सर्व मंगल (universal welfare) is the shared aim underlying all upasanas; मांगल्य is its abstract-noun cognate. Not in MD-Mapping, compositional</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>अभ्युदय</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>abhyudaya</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>comprehensive resolution</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Settled per Raghava (2026-07-08), aligned with MVD p.23 (supersedes "well-being" / "rise"); KD 2 p.35 and KD 3.12 p.116 in KD-Karm-Darshan-English.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>न्यूनातिरेक</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>nyoonatirek</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>deficiency-or-excess</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>KD 2 p.44: न्यून (deficient) + अतिरेक (excess); describes faulty (imposed) self-evaluation. Not in MD-Mapping, compositional</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>प्रभुसत्ता</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>prabhusatta</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>supreme order</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Aligned with MVD/JV usage; kept distinct from संप्रभुता = sovereignty and साम्राज्य = empire</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>साम्राज्य</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>samrajya</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>dominion</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>KD 2 p.48: kept as "dominion" rather than "sovereignty" specifically to avoid collision with प्रभुसत्ता above — both appear in this chapter as distinct stages in a causal chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>मानवेतर प्राणी</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>manavetar prani</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>beings other than human</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>KD 2 p.48: parallel to the already-established मानवेत्तर प्रकृति = "nature-other-than-human" (KD 3.7 glossary row)</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>विराग, वैराग्य</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>virag, vairagya</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>dispassion / detachment</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Aligned with MVD/JV usage: विराग = dispassion; वैराग्य = detachment; पर-वैराग्य = supreme-detachment</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>आत्म-दीपन</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>atma-deepan</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>self-illumination</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>KD 2 p.48: दीपन = illumination/kindling; not in MD-Mapping, compositional, part of the आत्म-बोध → आत्म-दीपन → आत्म-विश्वास → ... causal chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>पाण्डित्य</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>panditya</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>scholarliness</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Per MD-Mapping; first appearance in the KD corpus at KD 2 p.31 ("परिमार्जनशीलता ही निपुणता एवं कुशलता, पाण्डित्य है")</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>कासा, आकूति, मेधा (क्रिया/इच्छा/ज्ञान शक्ति के रूप में)</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>kāsā, ākūti, medhā</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>activity-power (kāsā), desire-power (ākūti), knowledge-power (medhā)</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>CONFIRMED FUNCTIONAL MAPPING (source image, 2026-10-04): KD 2 p. 47 explicitly associates क्रिया शक्ति with कासा, इच्छा शक्ति with आकूति, and ज्ञान शक्ति with मेधा. This confirms the local functional glosses, not settled English lexical names for the three terms. Retain the p. 5 spelling-variation note.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
           <t>अवकाश</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr">
+      <c r="B186" t="inlineStr">
         <is>
           <t>avakash</t>
         </is>
       </c>
-      <c r="C173" t="inlineStr">
+      <c r="C186" t="inlineStr">
         <is>
           <t>opportunity</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr">
+      <c r="D186" t="inlineStr">
         <is>
           <t>Settled per Raghava (2026-07-09): **not** "leisure." KD 1 p.14 (PDF p.39) glosses अवकाश (सम्भावना) → "opportunity (possibility)"; body/mind/wealth as means is itself opportunity; paired with अवसर ("occasion") in "necessity, occasion, and opportunity." Distinct from MD-Mapping's आकाश, अवकाश = "void" (space sense). MVD renders अवकाश एवम् अवसर as "opportunity and scope"</t>
         </is>
@@ -64643,7 +64929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:D97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="114" min="1" max="1"/>
@@ -64677,1684 +64963,1684 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>प्रस्थापन</t>
+          <t>वस्तुस्थिति सत्य</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>insertion</t>
+          <t>Relative Truth</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>absorption (absorbed)</t>
+          <t>relative truth, objective truth, absolute truth</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Settled per Raghava (July 2026); KD 3.1: particle absorbed into an atom (paired with visthapan)</t>
+          <t>Base-alignment correction (2026-10-04): KD p.3 distributes the shared सत्य across these three terms. MD-Mapping Sheet1 rows103/102/101 give these equivalents; the former existent-state/objective/context rendering lost the established triad.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>विस्थापन</t>
+          <t>वस्तुगत सत्य</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>expulsion</t>
+          <t>Objective Truth</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>displacement (displaced/shed)</t>
+          <t>relative truth, objective truth, absolute truth</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Settled per Raghava (July 2026); KD 3.1: particle shed from an excited atom</t>
+          <t>Base-alignment correction (2026-10-04): KD p.3 distributes the shared सत्य across these three terms. MD-Mapping Sheet1 rows103/102/101 give these equivalents; the former existent-state/objective/context rendering lost the established triad.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>सत्यता</t>
+          <t>स्थिति सत्य</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>verity</t>
+          <t>Absolute Truth</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>truthfulness</t>
+          <t>relative truth, objective truth, absolute truth</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Settled per Raghava (July 2026): "truthfulness", overriding MD-Mapping's "verity". Aligns with JV and KD usage; distinguishes सत्य = truth from सत्यता = truthfulness.</t>
+          <t>Base-alignment correction (2026-10-04): KD p.3 distributes the shared सत्य across these three terms. MD-Mapping Sheet1 rows103/102/101 give these equivalents; the former existent-state/objective/context rendering lost the established triad.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>प्रसन्नता</t>
+          <t>तिरोभाव</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>happiness / gladly</t>
+          <t>disappearance, annihilation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>happiness</t>
+          <t>disappearance (contextual)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Settled per Raghava (July 2026): "happiness" (noun), "happily" (adverb for प्रसन्नतापूर्वक). Aligns with MVD, JV, and MD-Mapping (overriding legacy "gladness").</t>
+          <t>MD-Mapping Sheet1 row1305 gives disappearance/annihilation. Source-image review (2026-10-04) uses disappearance for the absence/presence passage on p.23 and retains tirobhav alongside it on p.139. Do not merge with प्रलय = dissolution or supply a death/salvation mechanism.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>श्रम</t>
+          <t>प्रस्थापन</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>effort, physical labour</t>
+          <t>insertion</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>effort</t>
+          <t>absorption (absorbed)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Per MD-Mapping ("effort, physical labour"), whose notes state: "We are using 'effort' for shram in the sense of shram-gati-parinam." "Labour" only in economic compounds (श्रम मूल्य \= evaluation of labour, श्रम विनिमय \= exchange of labour, श्रम नियोजन \= utilisation of labour — updated 2026-07-08 per MVD; these compounds have not yet appeared in translated KD text). KD 3.11 (p. 117): श्रम-गति-परिणाम triad → "effort, motion, and result" — aligned with MVD/SB "Effort – Motion – Result"; effort \= grandeur of the existent-state, motion \= spreading of effect, result \= grandeur of a different existent-state</t>
+          <t>Settled per Raghava (July 2026); KD 3.1: particle absorbed into an atom (paired with visthapan)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>पोषण</t>
+          <t>विस्थापन</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nurturing</t>
+          <t>expulsion</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nourishment</t>
+          <t>displacement (displaced/shed)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Settled per Raghava (2026-08-23). Use **nourishment** for the noun, including relational uses ("provides nourishment to"); ordinary grammatical derivatives such as "nourishing" remain available where the Hindi is adjectival. This deliberately prefers the KD source's nourishment sense over MD-Mapping's bare "nurturing" row; पोषक remains "nourisher" and is not collapsed into this noun.</t>
+          <t>Settled per Raghava (July 2026); KD 3.1: particle shed from an excited atom</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>अनुकूल</t>
+          <t>सत्यता</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>conducive</t>
+          <t>verity</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>aligned / favourable (contextual)</t>
+          <t>truthfulness</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Settled per Raghava (2026-08-23): **aligned** when one faculty, activity, or result functions in relation to another. KD 1 p.15 therefore reads "endeavour aligned with knowledge, work aligned with endeavour, result aligned with work, realisation aligned with result, and knowledge aligned with realisation." Keep **favourable** for environmental/circumstantial uses such as अनुकूल वातावरण. Supersedes the opaque "consonant with" chain; MD-Mapping's bare row is "conducive."</t>
+          <t>Settled per Raghava (July 2026): "truthfulness", overriding MD-Mapping's "verity". Aligns with JV and KD usage; distinguishes सत्य = truth from सत्यता = truthfulness.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>प्रयोग</t>
+          <t>सत्यानुभूति</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>experimentation</t>
+          <t>realisation in truth</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>application / apply</t>
+          <t>Experiencing Truth</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Settled per Raghava (2026-08-23). Use **application** as the noun and **apply** as the verb, including scientific passages; supersedes "experiment / experimentation." This is an explicit KD terminology choice differing from MD-Mapping and Rakesh's frequent "experiment / experimentation" rendering.</t>
+          <t>Settled per Raghava (2026-08-31) for KD 1 p.3; supersedes "true experiencing" and renders the compound as an active experiential attainment. Source-image review (2026-10-04) also restored this rendering for सत्यानुभूति on p.29, replacing true realisation.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>भोग</t>
+          <t>प्रसन्नता</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>indulgence</t>
+          <t>happiness / gladly</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>enjoyment</t>
+          <t>happiness</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Confirmed per Raghava (2026-08-23) for bare भोग in KD (e.g. भोग एवं बहुभोगवादी जीवन; भोग परिणाम). Contextual distinctions remain: फल भोगना = **experience consequences/results**; भोक्ता = **enjoyer**; उपभोग = **consumption**. Rakesh's MVD often uses "indulgence" or "sensory enjoyments" for bare/compound भोग, while JV commonly uses "consumption" for उपभोग; KD deliberately retains **enjoyment** for bare भोग.</t>
+          <t>Settled per Raghava (July 2026): "happiness" (noun), "happily" (adverb for प्रसन्नतापूर्वक). Aligns with MVD, JV, and MD-Mapping (overriding legacy "gladness").</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>विन्यास</t>
+          <t>श्रम</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>demeanour, design</t>
+          <t>effort, physical labour</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>*vinyas* (contextual gloss: arrangement; unresolved)</t>
+          <t>effort</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DEFERRED REVIEW (2026-08-23): retain the transliteration and current contextual gloss pending explicit review of its technical physical sense. KD 3.11 presents weight/falling as *vinyas* evidencing coexistence; do not promote **arrangement** to a settled technical equivalent.</t>
+          <t>Per MD-Mapping ("effort, physical labour"), whose notes state: "We are using 'effort' for shram in the sense of shram-gati-parinam." "Labour" only in economic compounds (श्रम मूल्य \= evaluation of labour, श्रम विनिमय \= exchange of labour, श्रम नियोजन \= utilisation of labour — updated 2026-07-08 per MVD; these compounds have not yet appeared in translated KD text). KD 3.11 (p. 117): श्रम-गति-परिणाम triad → "effort, motion, and result" — aligned with MVD/SB "Effort – Motion – Result"; effort \= grandeur of the existent-state, motion \= spreading of effect, result \= grandeur of a different existent-state</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>चुम्बकीयता</t>
+          <t>उत्सव</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>magnestism</t>
+          <t>celebration, festival</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>magnetism</t>
+          <t>"festival" (literal, provisional)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Aligned with MVD/JV/SB usage; KD 3.13 abstract noun</t>
+          <t>KD 3.16 p. 137 visibly reads दो प्रजाति के प्राणकोषों का उत्सव. Source-image review (2026-10-04) retained the unusual wording and two species without inferring fusion, fertilisation, gametes, or the two sexes. The same provisional reading is retained for उत्सव विधि on p.142. Its technical or figurative intent remains unestablished; the source expression is preserved rather than silently repaired.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>संक्रमण</t>
+          <t>पोषण</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>irrversible transition</t>
+          <t>nurturing</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>irreversible transition</t>
+          <t>nourishment</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Aligned to the full technical sense in KD 3.3: irreversible passage to constitutional completeness</t>
+          <t>Settled per Raghava (2026-08-23). Use **nourishment** for the noun, including relational uses ("provides nourishment to"); ordinary grammatical derivatives such as "nourishing" remain available where the Hindi is adjectival. This deliberately prefers the KD source's nourishment sense over MD-Mapping's bare "nurturing" row; पोषक remains "nourisher" and is not collapsed into this noun.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>संक्रमणीयता</t>
+          <t>अनुकूल</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>transition-ness</t>
+          <t>conducive</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>irreversibility</t>
+          <t>aligned / favourable (contextual)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Aligned to the full technical sense in KD 3.3</t>
+          <t>Settled per Raghava (2026-08-23): **aligned** when one faculty, activity, or result functions in relation to another. KD 1 p.15 therefore reads "endeavour aligned with knowledge, work aligned with endeavour, result aligned with work, realisation aligned with result, and knowledge aligned with realisation." Keep **favourable** for environmental/circumstantial uses such as अनुकूल वातावरण. Supersedes the opaque "consonant with" chain; MD-Mapping's bare row is "conducive."</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>अनुप्राणित</t>
+          <t>प्रयोग</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>invigorated, inspired</t>
+          <t>experimentation</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>propagated</t>
+          <t>application / apply</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>EXPLICIT DECISION (2026-08-23): in KD 3.13's molecule-to-molecule wave-transmission context, use **propagated**. MVD's "invigorated/inspired" does not fit this physical context</t>
+          <t>Settled per Raghava (2026-08-23). Use **application** as the noun and **apply** as the verb, including scientific passages; supersedes "experiment / experimentation." This is an explicit KD terminology choice differing from MD-Mapping and Rakesh's frequent "experiment / experimentation" rendering.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>स्वयं स्फूर्त</t>
+          <t>भोग</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>spontaneity/spontaneous</t>
+          <t>indulgence</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>self-motivated / self-motivation (contextual)</t>
+          <t>enjoyment</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Settled per Raghava (2026-07-08), superseding the earlier "self-organised" (KD 3.1) and "self-spurred" (KD 3.4, 3.9, 3.13, 3.16-3.18) renderings — use "self-motivated" as adjective (e.g. "self-motivated method"), "self-motivation" where a noun reads better (e.g. "comes to be self-motivation" → "occurs through self-motivation"). Retroactively corrected across KD-Karm-Darshan-English.md §3.1–3.3, KD-Karm-Darshan-English.md §3.4–3.6, KD-Karm-Darshan-English.md §3.9–3.10, KD-Karm-Darshan-English.md §3.13–3.15, KD-Karm-Darshan-English.md §3.16–3.18 on 2026-07-08. **KD-Karm-Darshan-English.md §3.7–3.8 audit (2026-07-08 remediation):** all four former "self-inspired" instances verified against source images (pp. 76, 77, 81, 87) — each translates **स्वयं स्फूर्त**, corrected to "self-motivated." Distinct from **स्वयं प्रेरित** = "self-inspired" (SB usage; not found in KD 3.7-3.8)</t>
+          <t>Confirmed per Raghava (2026-08-23) for bare भोग in KD (e.g. भोग एवं बहुभोगवादी जीवन; भोग परिणाम). Contextual distinctions remain: फल भोगना = **experience consequences/results**; भोक्ता = **enjoyer**; उपभोग = **consumption**. Rakesh's MVD often uses "indulgence" or "sensory enjoyments" for bare/compound भोग, while JV commonly uses "consumption" for उपभोग; KD deliberately retains **enjoyment** for bare भोग.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>चुंबकीय बल सम्पन्नता</t>
+          <t>विन्यास</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>magnetic force-fullness</t>
+          <t>demeanour, design</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>magnetic-force-full / magnetic force-fullness</t>
+          <t>*vinyas* (contextual gloss: arrangement; unresolved)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Per MD-Mapping चुंबकीय बल सम्पन्नता = magnetic force-fullness. Supersedes earlier "endowed with magnetic force" / "magnetic-force endowment". Retroactively corrected corpus-wide 2026-07-10</t>
+          <t>Source-image review (2026-10-04): KD printed pp. 103–104 describe weight, falling, running, flying, rain and flow; p. 104 explicitly defines विन्यास as activity in evidencing coexistence. A solely static layout is too narrow. MD-Mapping Sheet1 row 1352 gives demeanour/design with arrangement/manifestation alternatives in a behavioural context; SB PDF positions 78 and 228 use functional arrangements and configuration in different contexts. Retain *vinyas* and contextual arrangement without treating either precedent as a settled KD technical equivalent.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>फलन</t>
+          <t>चुम्बकीयता</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>function/outcome</t>
+          <t>magnestism</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>outcome</t>
+          <t>magnetism</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Aligned with MVD/JV/SB usage. KD 3.15: evaluation on the basis of activity and outcome</t>
+          <t>Aligned with MVD/JV/SB usage; KD 3.13 abstract noun</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>नित्य वर्तमान</t>
+          <t>संक्रमण</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>eternal presence</t>
+          <t>irrversible transition</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ever-present</t>
+          <t>irreversible transition</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Settled per Raghava (July 2026); KD 3.15 predicate of kaal</t>
+          <t>Aligned to the full technical sense in KD 3.3: irreversible passage to constitutional completeness</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>आत्मा</t>
+          <t>संक्रमणीयता</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>atma</t>
+          <t>transition-ness</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>left transliterated (atma, buddhi, chitta, vritti, mun/"mind")</t>
+          <t>irreversibility</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>KD 3.6: the five jeevan faculties (pūrvānukram), each carrying one of the five *sthiti* (state) activities — anubhav/atma (realisation), bodh/buddhi (enlightenment), chintan/chitta (contemplation), tulan/vritti (comparison), aswadan/mun (tasting) — and one of the five *gati* (motion) activities — praman/atma (evidence), ṛtambharā/buddhi (resoluteness), ichha/chitta (desire), vishleshan/vritti (analysis), chayan/mun (selection). MD-Mapping leaves all five untranslated; matches its own note under अंतर्नियामन ("पूर्वानुक्रम = वरीयता क्रम याने आत्मा, बुद्धि, चित्त, वृत्ति, मन")</t>
+          <t>Aligned to the full technical sense in KD 3.3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>बुद्धि</t>
+          <t>अनुप्राणित</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>buddhi</t>
+          <t>invigorated, inspired</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>left transliterated (atma, buddhi, chitta, vritti, mun/"mind")</t>
+          <t>propagated</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>KD 3.6: the five jeevan faculties (pūrvānukram), each carrying one of the five *sthiti* (state) activities — anubhav/atma (realisation), bodh/buddhi (enlightenment), chintan/chitta (contemplation), tulan/vritti (comparison), aswadan/mun (tasting) — and one of the five *gati* (motion) activities — praman/atma (evidence), ṛtambharā/buddhi (resoluteness), ichha/chitta (desire), vishleshan/vritti (analysis), chayan/mun (selection). MD-Mapping leaves all five untranslated; matches its own note under अंतर्नियामन ("पूर्वानुक्रम = वरीयता क्रम याने आत्मा, बुद्धि, चित्त, वृत्ति, मन")</t>
+          <t>EXPLICIT DECISION (2026-08-23): in KD 3.13's molecule-to-molecule wave-transmission context, use **propagated**. MVD's "invigorated/inspired" does not fit this physical context</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>चित्त</t>
+          <t>स्वयं स्फूर्त</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>chitta</t>
+          <t>spontaneity/spontaneous</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>left transliterated (atma, buddhi, chitta, vritti, mun/"mind")</t>
+          <t>self-motivated / self-motivation (contextual)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>KD 3.6: the five jeevan faculties (pūrvānukram), each carrying one of the five *sthiti* (state) activities — anubhav/atma (realisation), bodh/buddhi (enlightenment), chintan/chitta (contemplation), tulan/vritti (comparison), aswadan/mun (tasting) — and one of the five *gati* (motion) activities — praman/atma (evidence), ṛtambharā/buddhi (resoluteness), ichha/chitta (desire), vishleshan/vritti (analysis), chayan/mun (selection). MD-Mapping leaves all five untranslated; matches its own note under अंतर्नियामन ("पूर्वानुक्रम = वरीयता क्रम याने आत्मा, बुद्धि, चित्त, वृत्ति, मन")</t>
+          <t>Settled per Raghava (2026-07-08), superseding the earlier "self-organised" (KD 3.1) and "self-spurred" (KD 3.4, 3.9, 3.13, 3.16-3.18) renderings — use "self-motivated" as adjective (e.g. "self-motivated method"), "self-motivation" where a noun reads better (e.g. "comes to be self-motivation" → "occurs through self-motivation"). Retroactively corrected across KD-Karm-Darshan-English.md §3.1–3.3, KD-Karm-Darshan-English.md §3.4–3.6, KD-Karm-Darshan-English.md §3.9–3.10, KD-Karm-Darshan-English.md §3.13–3.15, KD-Karm-Darshan-English.md §3.16–3.18 on 2026-07-08. **KD-Karm-Darshan-English.md §3.7–3.8 audit (2026-07-08 remediation):** all four former "self-inspired" instances verified against source images (pp. 76, 77, 81, 87) — each translates **स्वयं स्फूर्त**, corrected to "self-motivated." Distinct from **स्वयं प्रेरित** = "self-inspired" (SB usage; not found in KD 3.7-3.8)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>वृत्ति</t>
+          <t>चुंबकीय बल सम्पन्नता</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>vritti</t>
+          <t>magnetic force-fullness</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>left transliterated (atma, buddhi, chitta, vritti, mun/"mind")</t>
+          <t>magnetic-force-full / magnetic force-fullness</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>KD 3.6: the five jeevan faculties (pūrvānukram), each carrying one of the five *sthiti* (state) activities — anubhav/atma (realisation), bodh/buddhi (enlightenment), chintan/chitta (contemplation), tulan/vritti (comparison), aswadan/mun (tasting) — and one of the five *gati* (motion) activities — praman/atma (evidence), ṛtambharā/buddhi (resoluteness), ichha/chitta (desire), vishleshan/vritti (analysis), chayan/mun (selection). MD-Mapping leaves all five untranslated; matches its own note under अंतर्नियामन ("पूर्वानुक्रम = वरीयता क्रम याने आत्मा, बुद्धि, चित्त, वृत्ति, मन")</t>
+          <t>Per MD-Mapping चुंबकीय बल सम्पन्नता = magnetic force-fullness. Supersedes earlier "endowed with magnetic force" / "magnetic-force endowment". Retroactively corrected corpus-wide 2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>मन</t>
+          <t>फलन</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>mun</t>
+          <t>function/outcome</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>left transliterated (atma, buddhi, chitta, vritti, mun/"mind")</t>
+          <t>outcome</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>KD 3.6: the five jeevan faculties (pūrvānukram), each carrying one of the five *sthiti* (state) activities — anubhav/atma (realisation), bodh/buddhi (enlightenment), chintan/chitta (contemplation), tulan/vritti (comparison), aswadan/mun (tasting) — and one of the five *gati* (motion) activities — praman/atma (evidence), ṛtambharā/buddhi (resoluteness), ichha/chitta (desire), vishleshan/vritti (analysis), chayan/mun (selection). MD-Mapping leaves all five untranslated; matches its own note under अंतर्नियामन ("पूर्वानुक्रम = वरीयता क्रम याने आत्मा, बुद्धि, चित्त, वृत्ति, मन")</t>
+          <t>Aligned with MVD/JV/SB usage. KD 3.15: evaluation on the basis of activity and outcome</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>गठनपूर्णता</t>
+          <t>नित्य वर्तमान</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>constitutional completeness</t>
+          <t>eternal presence</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>constitutional completeness, activity-completeness, conduct-completeness</t>
+          <t>ever-present</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>KD 3.3/3.4: the atom's three stages of development. गठनपूर्णता = "constitutional completeness" per MD-Mapping; क्रियापूर्णता and आचरणपूर्णता are parallel KD coinages (not in MD-Mapping), rendered analogously</t>
+          <t>Settled per Raghava (July 2026); KD 3.15 predicate of kaal</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>गुण</t>
+          <t>आत्मा</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>properties</t>
+          <t>atma</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>property</t>
+          <t>left transliterated (atma, buddhi, chitta, vritti, mun/"mind")</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Settled per Raghava (2026-07-08): "property," NOT "quality." MD-Mapping carries both readings (गुण = "properties" as a noun; गुण = "qualitative" as an adjective) — for KD's recurring रूप/गुण/स्वभाव/धर्म (form/property/essential nature/dharma) list of the four orders' predominant traits, and for chapter 3.10's title, गुण is a noun and takes "property." Retroactively corrected in KD-Karm-Darshan-English.md §3.4–3.6, KD-Karm-Darshan-English.md §3.11–3.12, and KD-Karm-Darshan-English.md §3.13–3.15 (previously translated "quality") on 2026-07-08. Exception: the adjectival compound गुणात्मक परिवर्तन keeps MD-Mapping's own established "qualitative change/transformation" (KD 3.9) — "property-al" does not read in English, and MD-Mapping treats this compound as a separate row from bare गुण</t>
+          <t>KD 3.6: the five jeevan faculties (pūrvānukram), each carrying one of the five *sthiti* (state) activities — anubhav/atma (realisation), bodh/buddhi (enlightenment), chintan/chitta (contemplation), tulan/vritti (comparison), aswadan/mun (tasting) — and one of the five *gati* (motion) activities — praman/atma (evidence), ṛtambharā/buddhi (resoluteness), ichha/chitta (desire), vishleshan/vritti (analysis), chayan/mun (selection). MD-Mapping leaves all five untranslated; matches its own note under अंतर्नियामन ("पूर्वानुक्रम = वरीयता क्रम याने आत्मा, बुद्धि, चित्त, वृत्ति, मन")</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>सम</t>
+          <t>बुद्धि</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>generative</t>
+          <t>buddhi</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>generative, degenerative, mediating</t>
+          <t>left transliterated (atma, buddhi, chitta, vritti, mun/"mind")</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Per MD-Mapping (सम=generative, विषम=degenerative) and MVD running prose ("generative, degenerative, and mediative"). **Do not leave bare सम/विषम transliterated in analytical prose** — use generative / degenerative (MVD spelling: "degenerative", not "de-generative"). Optional (*sam*) / (*visham*) gloss only on first compound use if helpful (e.g. generative-degenerative (*sam-visham*)). Retroactively corrected in KD 1 (pp. 15–16, 25) on 2026-07-10 where *sam*/*visham* had been left italic-transliterated. मध्यस्थ here is an adjective describing the property that maintains a composition once formed ("mediating" in KD; MVD often "mediative"), distinct from मध्यस्थीयकरण (mediation, KD 3.11)</t>
+          <t>KD 3.6: the five jeevan faculties (pūrvānukram), each carrying one of the five *sthiti* (state) activities — anubhav/atma (realisation), bodh/buddhi (enlightenment), chintan/chitta (contemplation), tulan/vritti (comparison), aswadan/mun (tasting) — and one of the five *gati* (motion) activities — praman/atma (evidence), ṛtambharā/buddhi (resoluteness), ichha/chitta (desire), vishleshan/vritti (analysis), chayan/mun (selection). MD-Mapping leaves all five untranslated; matches its own note under अंतर्नियामन ("पूर्वानुक्रम = वरीयता क्रम याने आत्मा, बुद्धि, चित्त, वृत्ति, मन")</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>विषम</t>
+          <t>चित्त</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>degenerative</t>
+          <t>chitta</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>generative, degenerative, mediating</t>
+          <t>left transliterated (atma, buddhi, chitta, vritti, mun/"mind")</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Per MD-Mapping (सम=generative, विषम=degenerative) and MVD running prose ("generative, degenerative, and mediative"). **Do not leave bare सम/विषम transliterated in analytical prose** — use generative / degenerative (MVD spelling: "degenerative", not "de-generative"). Optional (*sam*) / (*visham*) gloss only on first compound use if helpful (e.g. generative-degenerative (*sam-visham*)). Retroactively corrected in KD 1 (pp. 15–16, 25) on 2026-07-10 where *sam*/*visham* had been left italic-transliterated. मध्यस्थ here is an adjective describing the property that maintains a composition once formed ("mediating" in KD; MVD often "mediative"), distinct from मध्यस्थीयकरण (mediation, KD 3.11)</t>
+          <t>KD 3.6: the five jeevan faculties (pūrvānukram), each carrying one of the five *sthiti* (state) activities — anubhav/atma (realisation), bodh/buddhi (enlightenment), chintan/chitta (contemplation), tulan/vritti (comparison), aswadan/mun (tasting) — and one of the five *gati* (motion) activities — praman/atma (evidence), ṛtambharā/buddhi (resoluteness), ichha/chitta (desire), vishleshan/vritti (analysis), chayan/mun (selection). MD-Mapping leaves all five untranslated; matches its own note under अंतर्नियामन ("पूर्वानुक्रम = वरीयता क्रम याने आत्मा, बुद्धि, चित्त, वृत्ति, मन")</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>पदार्थावस्था</t>
+          <t>वृत्ति</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Material order</t>
+          <t>vritti</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>material order, biological order, animal order, knowledge order</t>
+          <t>left transliterated (atma, buddhi, chitta, vritti, mun/"mind")</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Aligned 2026-08-23 with Rakesh Gupta's four-orders terminology. Here अवस्था names an ontological order, not a generic "state"; ordinary state/status usages of अवस्था or स्थिति remain context-sensitive.</t>
+          <t>KD 3.6: the five jeevan faculties (pūrvānukram), each carrying one of the five *sthiti* (state) activities — anubhav/atma (realisation), bodh/buddhi (enlightenment), chintan/chitta (contemplation), tulan/vritti (comparison), aswadan/mun (tasting) — and one of the five *gati* (motion) activities — praman/atma (evidence), ṛtambharā/buddhi (resoluteness), ichha/chitta (desire), vishleshan/vritti (analysis), chayan/mun (selection). MD-Mapping leaves all five untranslated; matches its own note under अंतर्नियामन ("पूर्वानुक्रम = वरीयता क्रम याने आत्मा, बुद्धि, चित्त, वृत्ति, मन")</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>प्राणावस्था</t>
+          <t>मन</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Biological order</t>
+          <t>mun</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>material order, biological order, animal order, knowledge order</t>
+          <t>left transliterated (atma, buddhi, chitta, vritti, mun/"mind")</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Aligned 2026-08-23 with Rakesh Gupta's four-orders terminology. Here अवस्था names an ontological order, not a generic "state"; ordinary state/status usages of अवस्था or स्थिति remain context-sensitive.</t>
+          <t>KD 3.6: the five jeevan faculties (pūrvānukram), each carrying one of the five *sthiti* (state) activities — anubhav/atma (realisation), bodh/buddhi (enlightenment), chintan/chitta (contemplation), tulan/vritti (comparison), aswadan/mun (tasting) — and one of the five *gati* (motion) activities — praman/atma (evidence), ṛtambharā/buddhi (resoluteness), ichha/chitta (desire), vishleshan/vritti (analysis), chayan/mun (selection). MD-Mapping leaves all five untranslated; matches its own note under अंतर्नियामन ("पूर्वानुक्रम = वरीयता क्रम याने आत्मा, बुद्धि, चित्त, वृत्ति, मन")</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>जीवावस्था</t>
+          <t>गठनपूर्णता</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Animal order</t>
+          <t>constitutional completeness</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>material order, biological order, animal order, knowledge order</t>
+          <t>constitutional completeness, activity-completeness, conduct-completeness</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Aligned 2026-08-23 with Rakesh Gupta's four-orders terminology. Here अवस्था names an ontological order, not a generic "state"; ordinary state/status usages of अवस्था or स्थिति remain context-sensitive.</t>
+          <t>KD 3.3/3.4: the atom's three stages of development. गठनपूर्णता = "constitutional completeness" per MD-Mapping; क्रियापूर्णता and आचरणपूर्णता are parallel KD coinages (not in MD-Mapping), rendered analogously</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ज्ञानावस्था</t>
+          <t>गुण</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Knowledge order</t>
+          <t>properties</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>material order, biological order, animal order, knowledge order</t>
+          <t>property</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Aligned 2026-08-23 with Rakesh Gupta's four-orders terminology. Here अवस्था names an ontological order, not a generic "state"; ordinary state/status usages of अवस्था or स्थिति remain context-sensitive.</t>
+          <t>Settled per Raghava (2026-07-08): "property," NOT "quality." MD-Mapping carries both readings (गुण = "properties" as a noun; गुण = "qualitative" as an adjective) — for KD's recurring रूप/गुण/स्वभाव/धर्म (form/property/essential nature/dharma) list of the four orders' predominant traits, and for chapter 3.10's title, गुण is a noun and takes "property." Retroactively corrected in KD-Karm-Darshan-English.md §3.4–3.6, KD-Karm-Darshan-English.md §3.11–3.12, and KD-Karm-Darshan-English.md §3.13–3.15 (previously translated "quality") on 2026-07-08. Exception: the adjectival compound गुणात्मक परिवर्तन keeps MD-Mapping's own established "qualitative change/transformation" (KD 3.9) — "property-al" does not read in English, and MD-Mapping treats this compound as a separate row from bare गुण</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>व्यापक</t>
+          <t>सम</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Omnipresent, Omnipresence</t>
+          <t>generative</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Omnipresence; omnipresent reality</t>
+          <t>generative, degenerative, mediating</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Aligned 2026-08-23 with Rakesh Gupta. Use **Omnipresence** when व्यापक functions as the substantive reality and **omnipresent reality** for व्यापक वस्तु; adjectival predicate uses such as "God is omnipresent" remain grammatical. Distinct from सत्ता = Omnipotence.</t>
+          <t>Per MD-Mapping (सम=generative, विषम=degenerative) and MVD running prose ("generative, degenerative, and mediative"). **Do not leave bare सम/विषम transliterated in analytical prose** — use generative / degenerative (MVD spelling: "degenerative", not "de-generative"). Optional (*sam*) / (*visham*) gloss only on first compound use if helpful (e.g. generative-degenerative (*sam-visham*)). Retroactively corrected in KD 1 (pp. 15–16, 25) on 2026-07-10 where *sam*/*visham* had been left italic-transliterated. मध्यस्थ here is an adjective describing the property that maintains a composition once formed ("mediating" in KD; MVD often "mediative"), distinct from मध्यस्थीयकरण (mediation, KD 3.11)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>दया</t>
+          <t>विषम</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>kindness</t>
+          <t>degenerative</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>kindness, grace, compassion</t>
+          <t>generative, degenerative, mediating</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Aligned 2026-08-23 with Rakesh Gupta's consistent technical trio. The former KD compassion/grace/mercy wording was corrected throughout; दया in the associated social-value passages is kindness, and करुणा is compassion.</t>
+          <t>Per MD-Mapping (सम=generative, विषम=degenerative) and MVD running prose ("generative, degenerative, and mediative"). **Do not leave bare सम/विषम transliterated in analytical prose** — use generative / degenerative (MVD spelling: "degenerative", not "de-generative"). Optional (*sam*) / (*visham*) gloss only on first compound use if helpful (e.g. generative-degenerative (*sam-visham*)). Retroactively corrected in KD 1 (pp. 15–16, 25) on 2026-07-10 where *sam*/*visham* had been left italic-transliterated. मध्यस्थ here is an adjective describing the property that maintains a composition once formed ("mediating" in KD; MVD often "mediative"), distinct from मध्यस्थीयकरण (mediation, KD 3.11)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>कृपा</t>
+          <t>प्रबुद्धता</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>grace</t>
+          <t>enlightenment</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>kindness, grace, compassion</t>
+          <t>full awareness; absence of full awareness</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Aligned 2026-08-23 with Rakesh Gupta's consistent technical trio. The former KD compassion/grace/mercy wording was corrected throughout; दया in the associated social-value passages is kindness, and करुणा is compassion.</t>
+          <t>Settled per Raghava (2026-08-31) after comparison with MVD and JV. This intentionally supersedes MVD's “enlightenment” for प्रबुद्धता because JV and the KD terminology already use “enlightenment” for बोध, the state activity of *buddhi*. Applied to the KD front matter and KD pp. 3, 18, 23, 31, 36, and 41–42. जागृति remains “awakening”; बोध remains “enlightenment.”</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>करुणा</t>
+          <t>पदार्थावस्था</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>compassion</t>
+          <t>Material order</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>kindness, grace, compassion</t>
+          <t>material order, biological order, animal order, knowledge order</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Aligned 2026-08-23 with Rakesh Gupta's consistent technical trio. The former KD compassion/grace/mercy wording was corrected throughout; दया in the associated social-value passages is kindness, and करुणा is compassion.</t>
+          <t>Aligned 2026-08-23 with Rakesh Gupta's four-orders terminology. Here अवस्था names an ontological order, not a generic "state"; ordinary state/status usages of अवस्था or स्थिति remain context-sensitive.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>सारक</t>
+          <t>प्राणावस्था</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Vitalising</t>
+          <t>Biological order</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>vitalising, devitalising</t>
+          <t>material order, biological order, animal order, knowledge order</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Aligned with MVD/JV/SB usage. KD 3.10: the two modes of स्वभाव (essential nature) in the biological order — vitalising (*sarakta*) means being abundant in itself and useful to the animal order; devitalising (*marakta*) means obstructing one's own seed-abundance and being disease/death-causing to the animal order</t>
+          <t>Aligned 2026-08-23 with Rakesh Gupta's four-orders terminology. Here अवस्था names an ontological order, not a generic "state"; ordinary state/status usages of अवस्था or स्थिति remain context-sensitive.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>मारक</t>
+          <t>जीवावस्था</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Devitalising</t>
+          <t>Animal order</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>vitalising, devitalising</t>
+          <t>material order, biological order, animal order, knowledge order</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Aligned with MVD/JV/SB usage. KD 3.10: the two modes of स्वभाव (essential nature) in the biological order — vitalising (*sarakta*) means being abundant in itself and useful to the animal order; devitalising (*marakta*) means obstructing one's own seed-abundance and being disease/death-causing to the animal order</t>
+          <t>Aligned 2026-08-23 with Rakesh Gupta's four-orders terminology. Here अवस्था names an ontological order, not a generic "state"; ordinary state/status usages of अवस्था or स्थिति remain context-sensitive.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>पात्रता</t>
+          <t>ज्ञानावस्था</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>receptivity</t>
+          <t>Knowledge order</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>receptivity / worthiness (contextual)</t>
+          <t>material order, biological order, animal order, knowledge order</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>EXPLICIT CONTEXTUAL RULE (confirmed 2026-08-23): preserve the technical क्षमता/योग्यता/पात्रता trio as **capacity / ability / receptivity**. These qualities are used when units recognise relationships and evaluate. Use **worthiness** only in KD 3.10's reciprocal दया/कृपा/करुणा (kindness/grace/compassion) definition, where substances are made available "in accordance with worthiness (*patrata*)"</t>
+          <t>Aligned 2026-08-23 with Rakesh Gupta's four-orders terminology. Here अवस्था names an ontological order, not a generic "state"; ordinary state/status usages of अवस्था or स्थिति remain context-sensitive.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>देव मानव</t>
+          <t>व्यापक</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>deific human</t>
+          <t>Omnipresent, Omnipresence</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>deific human, divine human</t>
+          <t>Omnipresence; omnipresent reality</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Aligned 2026-08-23 with Rakesh Gupta's MVD terminology; supersedes the former KD "god-human" / "godly human" judgment call.</t>
+          <t>Aligned 2026-08-23 with Rakesh Gupta. Use **Omnipresence** when व्यापक functions as the substantive reality and **omnipresent reality** for व्यापक वस्तु; adjectival predicate uses such as "God is omnipresent" remain grammatical. Distinct from सत्ता = Omnipotence.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>दिव्य मानव</t>
+          <t>दया</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>divine human</t>
+          <t>kindness</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>deific human, divine human</t>
+          <t>kindness, grace, compassion</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Aligned 2026-08-23 with Rakesh Gupta's MVD terminology; supersedes the former KD "god-human" / "godly human" judgment call.</t>
+          <t>Aligned 2026-08-23 with Rakesh Gupta's consistent technical trio. The former KD compassion/grace/mercy wording was corrected throughout; दया in the associated social-value passages is kindness, and करुणा is compassion.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>पशु मानव</t>
+          <t>कृपा</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>animalistic human</t>
+          <t>grace</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>the animalistic human, the demonic human</t>
+          <t>kindness, grace, compassion</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Per MD-Mapping ("animalistic human," "demonic human"). Retroactively corrected in KD-Karm-Darshan-English.md §3.9–3.10 on 2026-07-08 (previously "animal-human"/"demon-human") to match MD-Mapping exactly and align with KD 1's usage of the same pair</t>
+          <t>Aligned 2026-08-23 with Rakesh Gupta's consistent technical trio. The former KD compassion/grace/mercy wording was corrected throughout; दया in the associated social-value passages is kindness, and करुणा is compassion.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>राक्षस मानव</t>
+          <t>करुणा</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>demonic human</t>
+          <t>compassion</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>the animalistic human, the demonic human</t>
+          <t>kindness, grace, compassion</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Per MD-Mapping ("animalistic human," "demonic human"). Retroactively corrected in KD-Karm-Darshan-English.md §3.9–3.10 on 2026-07-08 (previously "animal-human"/"demon-human") to match MD-Mapping exactly and align with KD 1's usage of the same pair</t>
+          <t>Aligned 2026-08-23 with Rakesh Gupta's consistent technical trio. The former KD compassion/grace/mercy wording was corrected throughout; दया in the associated social-value passages is kindness, and करुणा is compassion.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>दृष्टा</t>
+          <t>सारक</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Seer</t>
+          <t>Vitalising</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>seer, knower, object of knowledge</t>
+          <t>vitalising, devitalising</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Aligned with MVD/JV usage: ज्ञेय names the object-pole of ज्ञान/ज्ञाता (knowledge/knower)</t>
+          <t>Aligned with MVD/JV/SB usage. KD 3.10: the two modes of स्वभाव (essential nature) in the biological order — vitalising (*sarakta*) means being abundant in itself and useful to the animal order; devitalising (*marakta*) means obstructing one's own seed-abundance and being disease/death-causing to the animal order</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ज्ञाता</t>
+          <t>मारक</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>knower</t>
+          <t>Devitalising</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>seer, knower, object of knowledge</t>
+          <t>vitalising, devitalising</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Aligned with MVD/JV usage: ज्ञेय names the object-pole of ज्ञान/ज्ञाता (knowledge/knower)</t>
+          <t>Aligned with MVD/JV/SB usage. KD 3.10: the two modes of स्वभाव (essential nature) in the biological order — vitalising (*sarakta*) means being abundant in itself and useful to the animal order; devitalising (*marakta*) means obstructing one's own seed-abundance and being disease/death-causing to the animal order</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ज्ञेय</t>
+          <t>पात्रता</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>knowable</t>
+          <t>receptivity</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>seer, knower, object of knowledge</t>
+          <t>receptivity / worthiness (contextual)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Aligned with MVD/JV usage: ज्ञेय names the object-pole of ज्ञान/ज्ञाता (knowledge/knower)</t>
+          <t>EXPLICIT CONTEXTUAL RULE (confirmed 2026-08-23): preserve the technical क्षमता/योग्यता/पात्रता trio as **capacity / ability / receptivity**. These qualities are used when units recognise relationships and evaluate. Use **worthiness** only in KD 3.10's reciprocal दया/कृपा/करुणा (kindness/grace/compassion) definition, where substances are made available "in accordance with worthiness (*patrata*)"</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>भोक्ता</t>
+          <t>देव मानव</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>enjoyer, experiencer</t>
+          <t>deific human</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>doer, enjoyer</t>
+          <t>deific human, divine human</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Compositional; कर्त्ता=doer (agent), भोक्ता=enjoyer (experiencer of result). KD 3.18 title</t>
+          <t>Aligned 2026-08-23 with Rakesh Gupta's MVD terminology; supersedes the former KD "god-human" / "godly human" judgment call.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>दृश्य</t>
+          <t>दिव्य मानव</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>scene</t>
+          <t>divine human</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>seer, scene, worldview</t>
+          <t>deific human, divine human</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Aligned with MVD/JV usage and confirmed from the MVD source table: दृश = human life (the seer), दृश्य = coexistence (the scene), दर्शन = justice/dharma/truth (worldview)</t>
+          <t>Aligned 2026-08-23 with Rakesh Gupta's MVD terminology; supersedes the former KD "god-human" / "godly human" judgment call.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>दर्शन</t>
+          <t>पशु मानव</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Holistic view, Worldview, Philosophy</t>
+          <t>animalistic human</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>seer, scene, worldview</t>
+          <t>the animalistic human, the demonic human</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Aligned with MVD/JV usage and confirmed from the MVD source table: दृश = human life (the seer), दृश्य = coexistence (the scene), दर्शन = justice/dharma/truth (worldview)</t>
+          <t>Per MD-Mapping ("animalistic human," "demonic human"). Retroactively corrected in KD-Karm-Darshan-English.md §3.9–3.10 on 2026-07-08 (previously "animal-human"/"demon-human") to match MD-Mapping exactly and align with KD 1's usage of the same pair</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ध्यान</t>
+          <t>राक्षस मानव</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>concentration</t>
+          <t>demonic human</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>concentration, one who concentrates, object of concentration</t>
+          <t>the animalistic human, the demonic human</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Aligned with MVD/JV usage and the parallel structure of ज्ञान/ज्ञाता/ज्ञेय</t>
+          <t>Per MD-Mapping ("animalistic human," "demonic human"). Retroactively corrected in KD-Karm-Darshan-English.md §3.9–3.10 on 2026-07-08 (previously "animal-human"/"demon-human") to match MD-Mapping exactly and align with KD 1's usage of the same pair</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ध्याता</t>
+          <t>दृष्टा</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>the one who concentrates</t>
+          <t>Seer</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>concentration, one who concentrates, object of concentration</t>
+          <t>seer, knower, object of knowledge</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Aligned with MVD/JV usage and the parallel structure of ज्ञान/ज्ञाता/ज्ञेय</t>
+          <t>Aligned with MVD/JV usage: ज्ञेय names the object-pole of ज्ञान/ज्ञाता (knowledge/knower)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ध्येय</t>
+          <t>ज्ञाता</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>object of concentration</t>
+          <t>knower</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>concentration, one who concentrates, object of concentration</t>
+          <t>seer, knower, object of knowledge</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Aligned with MVD/JV usage and the parallel structure of ज्ञान/ज्ञाता/ज्ञेय</t>
+          <t>Aligned with MVD/JV usage: ज्ञेय names the object-pole of ज्ञान/ज्ञाता (knowledge/knower)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>साध्य</t>
+          <t>ज्ञेय</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>aim</t>
+          <t>knowable</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>aim, seeker, means</t>
+          <t>seer, knower, object of knowledge</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Per MD-Mapping: साध्य=aim, साधक=the seeker, साधन=the means. KD 3.17 triad</t>
+          <t>Aligned with MVD/JV usage: ज्ञेय names the object-pole of ज्ञान/ज्ञाता (knowledge/knower)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>साधक</t>
+          <t>भोक्ता</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>the seeker</t>
+          <t>enjoyer, experiencer</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>aim, seeker, means</t>
+          <t>doer, enjoyer</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Per MD-Mapping: साध्य=aim, साधक=the seeker, साधन=the means. KD 3.17 triad</t>
+          <t>Compositional; कर्त्ता=doer (agent), भोक्ता=enjoyer (experiencer of result). KD 3.18 title</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>साधन</t>
+          <t>दृश्य</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>the means</t>
+          <t>scene</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>aim, seeker, means</t>
+          <t>seer, scene, worldview</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Per MD-Mapping: साध्य=aim, साधक=the seeker, साधन=the means. KD 3.17 triad</t>
+          <t>Aligned with MVD/JV usage and confirmed from the MVD source table: दृश = human life (the seer), दृश्य = coexistence (the scene), दर्शन = justice/dharma/truth (worldview)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>अध्यात्मवाद</t>
+          <t>दर्शन</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>spiritualism, adhyatma-vada</t>
+          <t>Holistic view, Worldview, Philosophy</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>*Adhyatma-vada*, *Adhidaivika-vada*, *Adhibhautika-vada*</t>
+          <t>seer, scene, worldview</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Aligned with MVD/JV usage. KD 3.17 names the three classical schools collectively subsumed under आदर्शवाद (idealism)</t>
+          <t>Aligned with MVD/JV usage and confirmed from the MVD source table: दृश = human life (the seer), दृश्य = coexistence (the scene), दर्शन = justice/dharma/truth (worldview)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>अधिदैवीवाद</t>
+          <t>ध्यान</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Adhidaivika-vada</t>
+          <t>concentration</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>*Adhyatma-vada*, *Adhidaivika-vada*, *Adhibhautika-vada*</t>
+          <t>concentration, one who concentrates, object of concentration</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Aligned with MVD/JV usage. KD 3.17 names the three classical schools collectively subsumed under आदर्शवाद (idealism)</t>
+          <t>Aligned with MVD/JV usage and the parallel structure of ज्ञान/ज्ञाता/ज्ञेय</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>अधिभौतिकवाद</t>
+          <t>ध्याता</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>adhi-bhautikvad</t>
+          <t>the one who concentrates</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>*Adhyatma-vada*, *Adhidaivika-vada*, *Adhibhautika-vada*</t>
+          <t>concentration, one who concentrates, object of concentration</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Aligned with MVD/JV usage. KD 3.17 names the three classical schools collectively subsumed under आदर्शवाद (idealism)</t>
+          <t>Aligned with MVD/JV usage and the parallel structure of ज्ञान/ज्ञाता/ज्ञेय</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>संचेतना</t>
+          <t>ध्येय</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>consciousness, human consciousness, humane consciousness</t>
+          <t>object of concentration</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>awareness</t>
+          <t>concentration, one who concentrates, object of concentration</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Settled per Raghava (2026-07-08), OVERRIDING MD-Mapping/SB's "Humane Consciousness" (SB Ch7 title) — "awareness" avoids collision with चेतना/जीव चेतना ("consciousness," e.g. "animal consciousness," KD 1) and चैतन्य ("conscious," e.g. "conscious activity," "material-conscious nature"), which stay untouched. Applies to संचेतनशील too ("awareness-endowed"). **Audit rule (2026-07-08 remediation):** grep for "human consciousness" / "higher-human consciousness" — replace with awareness / higher-awareness wherever the Hindi source is संचेतना; keep "consciousness" only for चेतना (e.g. "social consciousness" = सामाजिक चेतना, "consciousness-development" = चेतना विकास)</t>
+          <t>Aligned with MVD/JV usage and the parallel structure of ज्ञान/ज्ञाता/ज्ञेय</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>अभीष्ट</t>
+          <t>साध्य</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Aim</t>
+          <t>aim</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>desire</t>
+          <t>aim, seeker, means</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Settled per Raghava (2026-07-08), superseding this project's earlier "desideratum" (itself an override of MD-Mapping's "Aim," chosen to avoid colliding with साध्य=aim). Note: this reintroduces a collision with इच्छा (the general term for desire throughout KD) — अभीष्ट and इच्छा are now both "desire" in English; distinguish by context if needed (अभीष्ट is the wished-for/happiness-directed sense, इच्छा the general faculty/act of desiring). साध्य keeps "aim." Where the source explicitly glosses one with the other ("साध्य (अभीष्ट)"), rendered as "the aim (the desire)"</t>
+          <t>Per MD-Mapping: साध्य=aim, साधक=the seeker, साधन=the means. KD 3.17 triad</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>कृत</t>
+          <t>साधक</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>doing</t>
+          <t>the seeker</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>done, caused, intended</t>
+          <t>aim, seeker, means</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Settled per Raghava (2026-07-08), superseding this project's earlier "done, caused-to-be-done, and approved"/"consented-to." MD-Mapping's कृत="doing," कारित="getting done," अनुमोदित="consenting" — kept close but simplified; अनुमोदित specifically rendered "intended" rather than "approved"/"consenting" per this decision. Retrofitted in KD-Karm-Darshan-English.md §3.11–3.12 (3 instances, including the related noun अनुमोदन→"intention") and KD-Karm-Darshan-English.md §3.16–3.18 (1 instance) on 2026-07-08</t>
+          <t>Per MD-Mapping: साध्य=aim, साधक=the seeker, साधन=the means. KD 3.17 triad</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>कारित</t>
+          <t>साधन</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>getting done</t>
+          <t>the means</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>done, caused, intended</t>
+          <t>aim, seeker, means</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Settled per Raghava (2026-07-08), superseding this project's earlier "done, caused-to-be-done, and approved"/"consented-to." MD-Mapping's कृत="doing," कारित="getting done," अनुमोदित="consenting" — kept close but simplified; अनुमोदित specifically rendered "intended" rather than "approved"/"consenting" per this decision. Retrofitted in KD-Karm-Darshan-English.md §3.11–3.12 (3 instances, including the related noun अनुमोदन→"intention") and KD-Karm-Darshan-English.md §3.16–3.18 (1 instance) on 2026-07-08</t>
+          <t>Per MD-Mapping: साध्य=aim, साधक=the seeker, साधन=the means. KD 3.17 triad</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>अनुमोदित</t>
+          <t>अध्यात्मवाद</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>consenting</t>
+          <t>spiritualism, adhyatma-vada</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>done, caused, intended</t>
+          <t>*Adhyatma-vada*, *Adhidaivika-vada*, *Adhibhautika-vada*</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Settled per Raghava (2026-07-08), superseding this project's earlier "done, caused-to-be-done, and approved"/"consented-to." MD-Mapping's कृत="doing," कारित="getting done," अनुमोदित="consenting" — kept close but simplified; अनुमोदित specifically rendered "intended" rather than "approved"/"consenting" per this decision. Retrofitted in KD-Karm-Darshan-English.md §3.11–3.12 (3 instances, including the related noun अनुमोदन→"intention") and KD-Karm-Darshan-English.md §3.16–3.18 (1 instance) on 2026-07-08</t>
+          <t>Aligned with MVD/JV usage. KD 3.17 names the three classical schools collectively subsumed under आदर्शवाद (idealism)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>फल</t>
+          <t>अधिदैवीवाद</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>consequence</t>
+          <t>Adhidaivika-vada</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>result</t>
+          <t>*Adhyatma-vada*, *Adhidaivika-vada*, *Adhibhautika-vada*</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Settled per Raghava (2026-07-08), superseding this project's earlier "fruit" — "phal means result of the action (karma)." Retrofitted in KD-Karm-Darshan-English.md on 2026-07-08 wherever फल stood alone (not फलन=fruition, not a फल-परिणाम compound, not literal fruit as food). See परिणाम for the resolved collision and the फल-परिणाम compound convention</t>
+          <t>Aligned with MVD/JV usage. KD 3.17 names the three classical schools collectively subsumed under आदर्शवाद (idealism)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>संस्कार</t>
+          <t>अधिभौतिकवाद</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Sanskar</t>
+          <t>adhi-bhautikvad</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>*sanskar* (left transliterated)</t>
+          <t>*Adhyatma-vada*, *Adhidaivika-vada*, *Adhibhautika-vada*</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Per MD-Mapping (kept as "Sanskar," not translated). Settled per this project (2026-07-08): KD 1 uses संस्कार and संस्कृति together constantly (e.g. "संस्कार, संस्कृति व सभ्यता") — collapsing both to "culture" erases the distinction. संस्कार = the individual's cultural conditioning/refinement (kept as *sanskar*); संस्कृति = the collective/civilizational achievement (kept as "culture"); सभ्यता = "civilisation"</t>
+          <t>Aligned with MVD/JV usage. KD 3.17 names the three classical schools collectively subsumed under आदर्शवाद (idealism)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>सभ्यता</t>
+          <t>संचेतना</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>civilization, civility</t>
+          <t>consciousness, human consciousness, humane consciousness</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>civilisation</t>
+          <t>awareness</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Per MD-Mapping ("civilization, civility")</t>
+          <t>Settled per Raghava (2026-07-08), OVERRIDING MD-Mapping/SB's "Humane Consciousness" (SB Ch7 title) — "awareness" avoids collision with चेतना/जीव चेतना ("consciousness," e.g. "animal consciousness," KD 1) and चैतन्य ("conscious," e.g. "conscious activity," "material-conscious nature"), which stay untouched. Applies to संचेतनशील too ("awareness-endowed"). **Audit rule (2026-07-08 remediation):** grep for "human consciousness" / "higher-human consciousness" — replace with awareness / higher-awareness wherever the Hindi source is संचेतना; keep "consciousness" only for चेतना (e.g. "social consciousness" = सामाजिक चेतना, "consciousness-development" = चेतना विकास)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>काम</t>
+          <t>अभीष्ट</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>lust</t>
+          <t>Aim</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>lust / *kama* (contextual)</t>
+          <t>desire</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Settled per Raghava (2026-08-23): **lust** is acceptable where काम has that unambiguous sense. All current KD occurrences belong to the classical moksha–dharma–kama–artha life-aim listing, where "lust" would narrow the source; under the conflict rule these remain transliterated as ***kama***, glossed as desire on first use.</t>
+          <t>Settled per Raghava (2026-07-08), superseding this project's earlier "desideratum" (itself an override of MD-Mapping's "Aim," chosen to avoid colliding with साध्य=aim). Note: this reintroduces a collision with इच्छा (the general term for desire throughout KD) — अभीष्ट and इच्छा are now both "desire" in English; distinguish by context if needed (अभीष्ट is the wished-for/happiness-directed sense, इच्छा the general faculty/act of desiring). साध्य keeps "aim." Where the source explicitly glosses one with the other ("साध्य (अभीष्ट)"), rendered idiomatically as "the aim—the desired end".</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>अर्थ</t>
+          <t>कृत</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>resources</t>
+          <t>doing</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>wealth / resources / meaning (contextual)</t>
+          <t>done, caused, intended</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Settled per Raghava (2026-08-23): use **wealth** in acquisition, economic, and धन-related contexts; **resources** where अर्थ denotes the means available as body, mind, and wealth; and **meaning** where the text explains the significance or sense of a concept.</t>
+          <t>Settled per Raghava (2026-07-08), superseding this project's earlier "done, caused-to-be-done, and approved"/"consented-to." MD-Mapping's कृत="doing," कारित="getting done," अनुमोदित="consenting" — kept close but simplified; अनुमोदित specifically rendered "intended" rather than "approved"/"consenting" per this decision. Retrofitted in KD-Karm-Darshan-English.md §3.11–3.12 (3 instances, including the related noun अनुमोदन→"intention") and KD-Karm-Darshan-English.md §3.16–3.18 (1 instance) on 2026-07-08</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>मेधा</t>
+          <t>कारित</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>intellect</t>
+          <t>getting done</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>left transliterated</t>
+          <t>done, caused, intended</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>DEFERRED REVIEW (2026-08-23): retain transliteration and the current first-use glosses pending explicit lexical review of this obscure योग-जन्य-बुद्धि triad</t>
+          <t>Settled per Raghava (2026-07-08), superseding this project's earlier "done, caused-to-be-done, and approved"/"consented-to." MD-Mapping's कृत="doing," कारित="getting done," अनुमोदित="consenting" — kept close but simplified; अनुमोदित specifically rendered "intended" rather than "approved"/"consenting" per this decision. Retrofitted in KD-Karm-Darshan-English.md §3.11–3.12 (3 instances, including the related noun अनुमोदन→"intention") and KD-Karm-Darshan-English.md §3.16–3.18 (1 instance) on 2026-07-08</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>मति</t>
+          <t>अनुमोदित</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>mati, sumati, anumati (left transliterated)</t>
+          <t>consenting</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>left transliterated</t>
+          <t>done, caused, intended</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>KD 1: triad of "righteous-action-born intellect" (सुकर्म-जन्य-बुद्धि), not in MD-Mapping; left transliterated, glossed in-text</t>
+          <t>Settled per Raghava (2026-07-08), superseding this project's earlier "done, caused-to-be-done, and approved"/"consented-to." MD-Mapping's कृत="doing," कारित="getting done," अनुमोदित="consenting" — kept close but simplified; अनुमोदित specifically rendered "intended" rather than "approved"/"consenting" per this decision. Retrofitted in KD-Karm-Darshan-English.md §3.11–3.12 (3 instances, including the related noun अनुमोदन→"intention") and KD-Karm-Darshan-English.md §3.16–3.18 (1 instance) on 2026-07-08</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>सुमति</t>
+          <t>फल</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>mati, sumati, anumati (left transliterated)</t>
+          <t>consequence</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>left transliterated</t>
+          <t>result</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>KD 1: triad of "righteous-action-born intellect" (सुकर्म-जन्य-बुद्धि), not in MD-Mapping; left transliterated, glossed in-text</t>
+          <t>Settled per Raghava (2026-07-08), superseding this project's earlier "fruit" — "phal means result of the action (karma)." Retrofitted in KD-Karm-Darshan-English.md on 2026-07-08 wherever फल stood alone (not फलन=fruition, not a फल-परिणाम compound, not literal fruit as food). See परिणाम for the resolved collision and the फल-परिणाम compound convention</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>अनुमति</t>
+          <t>संस्कार</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>mati, sumati, anumati (left transliterated)</t>
+          <t>Sanskar</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>left transliterated</t>
+          <t>*sanskar* (left transliterated)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>KD 1: triad of "righteous-action-born intellect" (सुकर्म-जन्य-बुद्धि), not in MD-Mapping; left transliterated, glossed in-text</t>
+          <t>Per MD-Mapping (kept as "Sanskar," not translated). Settled per this project (2026-07-08): KD 1 uses संस्कार and संस्कृति together constantly (e.g. "संस्कार, संस्कृति व सभ्यता") — collapsing both to "culture" erases the distinction. संस्कार = the individual's cultural conditioning/refinement (kept as *sanskar*); संस्कृति = the collective/civilizational achievement (kept as "culture"); सभ्यता = "civilisation"</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>अमति</t>
+          <t>सभ्यता</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>amati, kumati, durmati (left transliterated)</t>
+          <t>civilization, civility</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>left transliterated</t>
+          <t>civilisation</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>KD 1: triad of "unrighteous-action-born tendency" (दुष्कर्म-जन्य-प्रवृत्ति), parallel to मति/सुमति/अनुमति; not in MD-Mapping</t>
+          <t>Per MD-Mapping ("civilization, civility")</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>कुमति</t>
+          <t>काम</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>amati, kumati, durmati (left transliterated)</t>
+          <t>lust</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>left transliterated</t>
+          <t>lust / *kama* (contextual)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>KD 1: triad of "unrighteous-action-born tendency" (दुष्कर्म-जन्य-प्रवृत्ति), parallel to मति/सुमति/अनुमति; not in MD-Mapping</t>
+          <t>Settled per Raghava (2026-08-23): **lust** is acceptable where काम has that unambiguous sense. All current KD occurrences belong to the classical moksha–dharma–kama–artha life-aim listing, where "lust" would narrow the source; under the conflict rule these remain transliterated as ***kama***, glossed as desire on first use.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>दुर्मति</t>
+          <t>अर्थ</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>amati, kumati, durmati (left transliterated)</t>
+          <t>resources</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>left transliterated</t>
+          <t>wealth / resources / meaning (contextual)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>KD 1: triad of "unrighteous-action-born tendency" (दुष्कर्म-जन्य-प्रवृत्ति), parallel to मति/सुमति/अनुमति; not in MD-Mapping</t>
+          <t>Settled per Raghava (2026-08-23): use **wealth** in acquisition, economic, and धन-related contexts; **resources** where अर्थ denotes the means available as body, mind, and wealth; and **meaning** where the text explains the significance or sense of a concept. Source-image review (2026-10-04) retains a close literal rendering of the compressed complete-meaning statements on pp.3 and 23; these do not settle every contextual sense of अर्थ.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>निवृत्ति</t>
+          <t>मेधा</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Disencumberance, Disinclination</t>
+          <t>intellect</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>disencumberance</t>
+          <t>left transliterated</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Per MD-Mapping ("Disencumberance, Disinclination" — freedom from delusion, fear, bondage). KD 1: one link in a definitional chain (ascertainment → disencumberance → impetus/wisdom → ...)</t>
+          <t>Source-image review (2026-10-04): KD p. 5 lists these as योग-जन्य-बुद्धि and visibly varies आकूति / आकृति between enumeration and explanation. P. 47 explicitly associates the three with activity-, desire-, and knowledge-power. MVD printed/PDF pp. 324 and 330 and MD-Mapping row 1215 give a medha/intellect precedent but do not establish English names for the complete KD trio. Retain all three transliterations; do not collapse मेधा into मेधस = brain or silently normalise the p. 5 variation.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>कारण</t>
+          <t>मति</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>cause</t>
+          <t>mati, sumati, anumati (left transliterated)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>gross, subtle, causal</t>
+          <t>left transliterated</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>KD 1: classical triad (not in MD-Mapping under this exact grouping) for the three levels at which direct-perception, inference, and testimony-activity, and independent/imitative/adherent tendency, all operate</t>
+          <t>KD 1: triad of "righteous-action-born intellect" (सुकर्म-जन्य-बुद्धि), not in MD-Mapping; left transliterated, glossed in-text</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>रजोगुण</t>
+          <t>सुमति</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>rajoguna, tamoguna, sattvaguna (left transliterated)</t>
+          <t>mati, sumati, anumati (left transliterated)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -66364,19 +66650,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>KD 1: the classical three गुण (property-modes), mapped onto sam/visham/mediating (see सम-विषम-मध्यस्थ row above: sam=rajoguna, visham=tamoguna, mediating=sattvaguna); not in MD-Mapping, kept transliterated per standard practice for this well-known Sanskrit triad</t>
+          <t>KD 1: triad of "righteous-action-born intellect" (सुकर्म-जन्य-बुद्धि), not in MD-Mapping; left transliterated, glossed in-text</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>तमोगुण</t>
+          <t>अनुमति</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>rajoguna, tamoguna, sattvaguna (left transliterated)</t>
+          <t>mati, sumati, anumati (left transliterated)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -66386,19 +66672,19 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>KD 1: the classical three गुण (property-modes), mapped onto sam/visham/mediating (see सम-विषम-मध्यस्थ row above: sam=rajoguna, visham=tamoguna, mediating=sattvaguna); not in MD-Mapping, kept transliterated per standard practice for this well-known Sanskrit triad</t>
+          <t>KD 1: triad of "righteous-action-born intellect" (सुकर्म-जन्य-बुद्धि), not in MD-Mapping; left transliterated, glossed in-text</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>सत्वगुण</t>
+          <t>अमति</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>rajoguna, tamoguna, sattvaguna (left transliterated)</t>
+          <t>amati, kumati, durmati (left transliterated)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -66408,225 +66694,379 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>KD 1: the classical three गुण (property-modes), mapped onto sam/visham/mediating (see सम-विषम-मध्यस्थ row above: sam=rajoguna, visham=tamoguna, mediating=sattvaguna); not in MD-Mapping, kept transliterated per standard practice for this well-known Sanskrit triad</t>
+          <t>KD 1: triad of "unrighteous-action-born tendency" (दुष्कर्म-जन्य-प्रवृत्ति), parallel to मति/सुमति/अनुमति; not in MD-Mapping</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>उपासना</t>
+          <t>कुमति</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>worship, upasana</t>
+          <t>amati, kumati, durmati (left transliterated)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Upasana (worship)</t>
+          <t>left transliterated</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>KD 2 chapter title. Per MD-Mapping ("worship, upasana") and SB's own English rendering (SB p.23: "worship, archana, yoga, sadhana, and upasana" — SB itself leaves उपासना transliterated rather than translating it). Kept transliterated as "upasana" throughout, glossed "(worship)" on first use, per this project's practice for the book's central chapter-2 term</t>
+          <t>KD 1: triad of "unrighteous-action-born tendency" (दुष्कर्म-जन्य-प्रवृत्ति), parallel to मति/सुमति/अनुमति; not in MD-Mapping</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>देवात्मा</t>
+          <t>दुर्मति</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>deific-self</t>
+          <t>amati, kumati, durmati (left transliterated)</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>deific self, elemental self, divine self</t>
+          <t>left transliterated</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Aligned with MVD/JV usage and the established आत्मा = self rendering; the three states are tied to absolute-oneness (*tadatmya*) with adhidaivik facts, adhibhautik elements, and adhyatma respectively</t>
+          <t>KD 1: triad of "unrighteous-action-born tendency" (दुष्कर्म-जन्य-प्रवृत्ति), parallel to मति/सुमति/अनुमति; not in MD-Mapping</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>दिव्यात्मा</t>
+          <t>निवृत्ति</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>divine-self</t>
+          <t>Disencumberance, Disinclination</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>deific self, elemental self, divine self</t>
+          <t>disencumberance</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Aligned with MVD/JV usage and the established आत्मा = self rendering; the three states are tied to absolute-oneness (*tadatmya*) with adhidaivik facts, adhibhautik elements, and adhyatma respectively</t>
+          <t>Per MD-Mapping ("Disencumberance, Disinclination" — freedom from delusion, fear, bondage). KD 1: one link in a definitional chain (ascertainment → disencumberance → impetus/wisdom → ...)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>प्राणवायु</t>
+          <t>कारण</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>oxygen, prana air</t>
+          <t>cause</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>*pranavayu* (left transliterated)</t>
+          <t>gross, subtle, causal</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>EXPLICIT DECISION (2026-08-23): retain the technical term as **pranavayu**, without translating it as "life-breath" or separating it as *pran vayu*. In KD 2 p.31, pranavayu controls the gross body. This is a deliberate KD choice differing from MVD's "prana-air"</t>
+          <t>KD 1: classical triad (not in MD-Mapping under this exact grouping) for the three levels at which direct-perception, inference, and testimony-activity, and independent/imitative/adherent tendency, all operate</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>विद्या</t>
+          <t>रजोगुण</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>learning</t>
+          <t>rajoguna, tamoguna, sattvaguna (left transliterated)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>learning, sub-learning, base learning</t>
+          <t>left transliterated</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>KD 2: the three qualities of upasana outcome, tied respectively to divine, deific, and elemental souls. विद्या = "learning" per MD-Mapping; उपविद्या and क्षुद्र विद्या are KD coinages not in MD-Mapping, compositional (उप- = sub-, क्षुद्र = base/petty)</t>
+          <t>KD 1: the classical three गुण (property-modes), mapped onto sam/visham/mediating (see सम-विषम-मध्यस्थ row above: sam=rajoguna, visham=tamoguna, mediating=sattvaguna); not in MD-Mapping, kept transliterated per standard practice for this well-known Sanskrit triad</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>वर्ग</t>
+          <t>तमोगुण</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>class</t>
+          <t>rajoguna, tamoguna, sattvaguna (left transliterated)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>creed, sect, class</t>
+          <t>left transliterated</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>KD 2 p.38: "मानव के स्वधर्म में ही मत, सम्प्रदाय, वर्ग तिरोहित हो जाते हैं" — not in MD-Mapping under this triad, compositional</t>
+          <t>KD 1: the classical three गुण (property-modes), mapped onto sam/visham/mediating (see सम-विषम-मध्यस्थ row above: sam=rajoguna, visham=tamoguna, mediating=sattvaguna); not in MD-Mapping, kept transliterated per standard practice for this well-known Sanskrit triad</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>अभ्युदय</t>
+          <t>सत्वगुण</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>comprehensive resolution (Abhyudaya)</t>
+          <t>rajoguna, tamoguna, sattvaguna (left transliterated)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>comprehensive resolution</t>
+          <t>left transliterated</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Settled per Raghava (2026-07-08), aligned with MVD p.23 (supersedes "well-being" / "rise"); KD 2 p.35 and KD 3.12 p.116 in KD-Karm-Darshan-English.md</t>
+          <t>KD 1: the classical three गुण (property-modes), mapped onto sam/visham/mediating (see सम-विषम-मध्यस्थ row above: sam=rajoguna, visham=tamoguna, mediating=sattvaguna); not in MD-Mapping, kept transliterated per standard practice for this well-known Sanskrit triad</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>विराग</t>
+          <t>उपासना</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>dispassion</t>
+          <t>worship, upasana</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>dispassion / detachment</t>
+          <t>Upasana (worship)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Aligned with MVD/JV usage: विराग = dispassion; वैराग्य = detachment; पर-वैराग्य = supreme-detachment</t>
+          <t>KD 2 chapter title. Per MD-Mapping ("worship, upasana") and SB's own English rendering (SB p.23: "worship, archana, yoga, sadhana, and upasana" — SB itself leaves उपासना transliterated rather than translating it). Kept transliterated as "upasana" throughout, glossed "(worship)" on first use, per this project's practice for the book's central chapter-2 term</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>वैराग्य</t>
+          <t>देवात्मा</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>detachment</t>
+          <t>deific-self</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>dispassion / detachment</t>
+          <t>deific self, elemental self, divine self</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Aligned with MVD/JV usage: विराग = dispassion; वैराग्य = detachment; पर-वैराग्य = supreme-detachment</t>
+          <t>Aligned with MVD/JV usage and the established आत्मा = self rendering; the three states are tied to absolute-oneness (*tadatmya*) with adhidaivik facts, adhibhautik elements, and adhyatma respectively</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
+          <t>दिव्यात्मा</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>divine-self</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>deific self, elemental self, divine self</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Aligned with MVD/JV usage and the established आत्मा = self rendering; the three states are tied to absolute-oneness (*tadatmya*) with adhidaivik facts, adhibhautik elements, and adhyatma respectively</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>प्राणवायु</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>oxygen, prana air</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>*pranavayu* (left transliterated)</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>EXPLICIT DECISION (2026-08-23): retain the technical term as **pranavayu**, without translating it as "life-breath" or separating it as *pran vayu*. In KD 2 p.31, pranavayu controls the gross body. This is a deliberate KD choice differing from MVD's "prana-air"</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>विद्या</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>learning</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>learning, sub-learning, base learning</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>KD 2: the three qualities of upasana outcome, tied respectively to divine, deific, and elemental souls. विद्या = "learning" per MD-Mapping; उपविद्या and क्षुद्र विद्या are KD coinages not in MD-Mapping, compositional (उप- = sub-, क्षुद्र = base/petty) Source-image review of p. 146 (2026-10-04) likewise retains विद्या = learning in the three named forms Shakti-vidya, Shiva-vidya and Vishnu-vidya, replacing the former ambiguous Shakti-/Shiva-/Vishnu-knowledge labels.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>वर्ग</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>class</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>creed, sect, class</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>KD 2 p.38: "मानव के स्वधर्म में ही मत, सम्प्रदाय, वर्ग तिरोहित हो जाते हैं" — not in MD-Mapping under this triad, compositional</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>अभ्युदय</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>comprehensive resolution (Abhyudaya)</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>comprehensive resolution</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Settled per Raghava (2026-07-08), aligned with MVD p.23 (supersedes "well-being" / "rise"); KD 2 p.35 and KD 3.12 p.116 in KD-Karm-Darshan-English.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>विराग</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>dispassion</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>dispassion / detachment</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Aligned with MVD/JV usage: विराग = dispassion; वैराग्य = detachment; पर-वैराग्य = supreme-detachment</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>वैराग्य</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>detachment</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>dispassion / detachment</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Aligned with MVD/JV usage: विराग = dispassion; वैराग्य = detachment; पर-वैराग्य = supreme-detachment</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
           <t>अवकाश</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B97" t="inlineStr">
         <is>
           <t>void</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>opportunity</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="D97" t="inlineStr">
         <is>
           <t>Settled per Raghava (2026-07-09): **not** "leisure." KD 1 p.14 (PDF p.39) glosses अवकाश (सम्भावना) → "opportunity (possibility)"; body/mind/wealth as means is itself opportunity; paired with अवसर ("occasion") in "necessity, occasion, and opportunity." Distinct from MD-Mapping's आकाश, अवकाश = "void" (space sense). MVD renders अवकाश एवम् अवसर as "opportunity and scope"</t>
         </is>

--- a/References/Madhyasth-Darshan/KD-Karm-Darshan-English/KD-Translation-Glossary.xlsx
+++ b/References/Madhyasth-Darshan/KD-Karm-Darshan-English/KD-Translation-Glossary.xlsx
@@ -911,7 +911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2245"/>
+  <dimension ref="A1:K2298"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="13.4399995803833" defaultRowHeight="15"/>
   <cols>
     <col width="23.21999931335449" customWidth="1" style="114" min="1" max="1"/>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="B76" s="37" t="inlineStr">
         <is>
-          <t>evaluation of labour</t>
+          <t>value of labour</t>
         </is>
       </c>
       <c r="C76" s="117" t="inlineStr">
@@ -3491,7 +3491,8 @@
       <c r="F76" s="121" t="inlineStr">
         <is>
           <t>labour value
-[Updated 'labour value' -&gt; 'evaluation of labour' per MVD priority rule, 2026-07-08. Existing says 'labour value'; MVD's sentence renders 'श्रम मूल्य...' as 'evaluation ... of human labour', i.e. 'evaluation' rather than 'value'.]</t>
+[Updated 'labour value' -&gt; 'evaluation of labour' per MVD priority rule, 2026-07-08. Existing says 'labour value'; MVD's sentence renders 'श्रम मूल्य...' as 'evaluation ... of human labour', i.e. 'evaluation' rather than 'value'.]
+[Updated 'evaluation of labour' -&gt; 'value of labour' by project-wide decision of 7 October 2026 (AA key term 5); 'valuing labour' where the text names the act.]</t>
         </is>
       </c>
       <c r="G76" s="121" t="n"/>
@@ -6389,7 +6390,7 @@
       </c>
       <c r="B163" s="116" t="inlineStr">
         <is>
-          <t>exploitation, depletion</t>
+          <t>exploitation</t>
         </is>
       </c>
       <c r="C163" s="117" t="inlineStr">
@@ -6399,7 +6400,11 @@
       </c>
       <c r="D163" s="118" t="n"/>
       <c r="E163" s="119" t="n"/>
-      <c r="F163" s="121" t="n"/>
+      <c r="F163" s="121" t="inlineStr">
+        <is>
+          <t>[Updated 'exploitation, depletion' -&gt; 'exploitation' by project-wide decision of 7 October 2026 (AA key term 24: exploitation throughout, of people and of the earth alike).]</t>
+        </is>
+      </c>
       <c r="G163" s="121" t="inlineStr">
         <is>
           <t>Cruel, aggressive,</t>
@@ -11138,7 +11143,7 @@
       </c>
       <c r="B314" s="116" t="inlineStr">
         <is>
-          <t>Satisfaction Point</t>
+          <t>satiation point</t>
         </is>
       </c>
       <c r="C314" s="123" t="inlineStr">
@@ -11154,7 +11159,8 @@
       <c r="E314" s="119" t="n"/>
       <c r="F314" s="120" t="inlineStr">
         <is>
-          <t>Point of Satisfaction</t>
+          <t>Point of Satisfaction
+[Updated 'Satisfaction Point' -&gt; 'satiation point' by project-wide decision of 7 October 2026 (AA key term 11).]</t>
         </is>
       </c>
       <c r="G314" s="121" t="n"/>
@@ -11402,7 +11408,7 @@
       </c>
       <c r="B322" s="116" t="inlineStr">
         <is>
-          <t>purposeful-use, purposefulness</t>
+          <t>purposeful use</t>
         </is>
       </c>
       <c r="C322" s="123" t="inlineStr">
@@ -11414,7 +11420,8 @@
       <c r="E322" s="119" t="n"/>
       <c r="F322" s="121" t="inlineStr">
         <is>
-          <t>Purposefulness</t>
+          <t>Purposefulness
+[Updated 'purposeful-use, purposefulness' -&gt; 'purposeful use' by project-wide decision of 7 October 2026 (AA key term 8).]</t>
         </is>
       </c>
       <c r="G322" s="121" t="n"/>
@@ -22393,12 +22400,12 @@
     <row r="669" ht="14.25" customHeight="1" s="114">
       <c r="A669" s="119" t="inlineStr">
         <is>
-          <t xml:space="preserve">दूर दर्शन </t>
+          <t>दूर दर्शन, दूरदर्शन</t>
         </is>
       </c>
       <c r="B669" s="116" t="inlineStr">
         <is>
-          <t>telecommunication</t>
+          <t>broadcasting</t>
         </is>
       </c>
       <c r="C669" s="117" t="inlineStr">
@@ -22411,7 +22418,8 @@
       <c r="F669" s="121" t="inlineStr">
         <is>
           <t>television
-[Unconfirmed MVD/SB evidence found (MVD ~p.171) — needs human review; see MD-Mapping-Sources. The English list ('(1) transportation and (2) telecommunication') collapses/renumbers the three Hindi items (दूरगमन, दूरश्रवण, दूर-दर्शन) inconsistently, so it isn't clear which English word specifically corresponds to दूर-दर्शन versus दूरश्रवण.]</t>
+[Unconfirmed MVD/SB evidence found (MVD ~p.171) — needs human review; see MD-Mapping-Sources. The English list ('(1) transportation and (2) telecommunication') collapses/renumbers the three Hindi items (दूरगमन, दूरश्रवण, दूर-दर्शन) inconsistently, so it isn't clear which English word specifically corresponds to दूर-दर्शन versus दूरश्रवण.]
+[Updated 'telecommunication' -&gt; 'broadcasting' by project-wide decision of 7 October 2026 (AA key term 12); दूरश्रवण, दूरदर्शन and दूरगमन take distinct terms.]</t>
         </is>
       </c>
       <c r="G669" s="121" t="n"/>
@@ -22423,12 +22431,12 @@
     <row r="670" ht="14.25" customHeight="1" s="114">
       <c r="A670" s="119" t="inlineStr">
         <is>
-          <t xml:space="preserve">दूर गमन </t>
+          <t>दूर गमन, दूरगमन</t>
         </is>
       </c>
       <c r="B670" s="116" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>transport</t>
         </is>
       </c>
       <c r="C670" s="117" t="inlineStr">
@@ -22440,7 +22448,8 @@
       <c r="E670" s="119" t="n"/>
       <c r="F670" s="121" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>transportation
+[Updated 'transportation' -&gt; 'transport' by project-wide decision of 7 October 2026 (AA key term 12).]</t>
         </is>
       </c>
       <c r="G670" s="121" t="n"/>
@@ -22452,12 +22461,12 @@
     <row r="671" ht="14.25" customHeight="1" s="114">
       <c r="A671" s="119" t="inlineStr">
         <is>
-          <t xml:space="preserve">दूर श्रवण </t>
+          <t>दूर श्रवण, दूरश्रवण</t>
         </is>
       </c>
       <c r="B671" s="116" t="inlineStr">
         <is>
-          <t>telecommunication</t>
+          <t>telephony</t>
         </is>
       </c>
       <c r="C671" s="117" t="inlineStr">
@@ -22469,7 +22478,8 @@
       <c r="E671" s="119" t="n"/>
       <c r="F671" s="121" t="inlineStr">
         <is>
-          <t>telephone, telephony</t>
+          <t>telephone, telephony
+[Updated 'telecommunication' -&gt; 'telephony' by project-wide decision of 7 October 2026 (AA key term 12).]</t>
         </is>
       </c>
       <c r="G671" s="121" t="n"/>
@@ -24015,7 +24025,7 @@
       </c>
       <c r="B719" s="37" t="inlineStr">
         <is>
-          <t>kosha</t>
+          <t>kosha (sheaths); reserve (economic sense)</t>
         </is>
       </c>
       <c r="C719" s="117" t="inlineStr">
@@ -24027,7 +24037,8 @@
       <c r="E719" s="119" t="n"/>
       <c r="F719" s="121" t="inlineStr">
         <is>
-          <t>repository, reserve, sheath</t>
+          <t>repository, reserve, sheath
+[Updated 'kosha' -&gt; 'kosha (sheaths); reserve (economic sense)' by project-wide decision of 7 October 2026 (AA key term 19).]</t>
         </is>
       </c>
       <c r="G719" s="121" t="n"/>
@@ -26310,7 +26321,7 @@
       </c>
       <c r="B793" s="116" t="inlineStr">
         <is>
-          <t>exploitation, depletion</t>
+          <t>exploitation</t>
         </is>
       </c>
       <c r="C793" s="117" t="inlineStr">
@@ -26320,7 +26331,11 @@
       </c>
       <c r="D793" s="118" t="n"/>
       <c r="E793" s="119" t="n"/>
-      <c r="F793" s="121" t="n"/>
+      <c r="F793" s="121" t="inlineStr">
+        <is>
+          <t>[Updated 'exploitation, depletion' -&gt; 'exploitation' by project-wide decision of 7 October 2026 (AA key term 24: exploitation throughout, of people and of the earth alike).]</t>
+        </is>
+      </c>
       <c r="G793" s="121" t="n"/>
       <c r="H793" s="121" t="n"/>
       <c r="I793" s="121" t="inlineStr">
@@ -29806,7 +29821,7 @@
       </c>
       <c r="B905" s="116" t="inlineStr">
         <is>
-          <t>Production-Work</t>
+          <t>production</t>
         </is>
       </c>
       <c r="C905" s="117" t="inlineStr">
@@ -29818,7 +29833,8 @@
       <c r="E905" s="119" t="n"/>
       <c r="F905" s="121" t="inlineStr">
         <is>
-          <t>[Unconfirmed MVD/SB evidence found (MVD ~p.266) — needs human review; see MD-Mapping-Sources. English excerpt is truncated before reaching the translation of उत्पादन कार्य.]</t>
+          <t>[Unconfirmed MVD/SB evidence found (MVD ~p.266) — needs human review; see MD-Mapping-Sources. English excerpt is truncated before reaching the translation of उत्पादन कार्य.]
+[Updated 'Production-Work' -&gt; 'production' by project-wide decision of 7 October 2026 (AA key term 13): 'production' is sufficient, without 'work'.]</t>
         </is>
       </c>
       <c r="G905" s="121" t="n"/>
@@ -37893,7 +37909,7 @@
     <row r="1158" ht="14.25" customHeight="1" s="114">
       <c r="A1158" s="119" t="inlineStr">
         <is>
-          <t xml:space="preserve">व्यवसाय में स्वालम्बी </t>
+          <t>व्यवसाय में स्वालम्बी, व्यवसाय में स्वावलंबी</t>
         </is>
       </c>
       <c r="B1158" s="116" t="inlineStr">
@@ -43141,7 +43157,7 @@
       </c>
       <c r="B1322" s="116" t="inlineStr">
         <is>
-          <t>family-based self-governance orderliness</t>
+          <t>family-based self-governing system</t>
         </is>
       </c>
       <c r="C1322" s="123" t="inlineStr">
@@ -43153,7 +43169,8 @@
       <c r="E1322" s="119" t="n"/>
       <c r="F1322" s="121" t="inlineStr">
         <is>
-          <t>[Updated 'family based self-governing system' -&gt; 'family-based self-governance orderliness' per MVD priority rule, 2026-07-08. Existing says 'family based self-governing system', but MVD renders व्यवस्था consistently as 'orderliness' (its standard technical rendering throughout), giving 'Humane family-based self-governance orderliness', not 'system'.]</t>
+          <t>[Updated 'family based self-governing system' -&gt; 'family-based self-governance orderliness' per MVD priority rule, 2026-07-08. Existing says 'family based self-governing system', but MVD renders व्यवस्था consistently as 'orderliness' (its standard technical rendering throughout), giving 'Humane family-based self-governance orderliness', not 'system'.]
+[Updated 'family-based self-governance orderliness' -&gt; 'family-based self-governing system' by project-wide decision of 7 October 2026 (AA key term 27).]</t>
         </is>
       </c>
       <c r="G1322" s="121" t="n"/>
@@ -46480,7 +46497,7 @@
       </c>
       <c r="B1427" s="116" t="inlineStr">
         <is>
-          <t>gesture, gesticulation</t>
+          <t>gesture, gesticulation; currency (economic sense)</t>
         </is>
       </c>
       <c r="C1427" s="123" t="inlineStr">
@@ -46494,7 +46511,11 @@
         </is>
       </c>
       <c r="E1427" s="120" t="n"/>
-      <c r="F1427" s="106" t="n"/>
+      <c r="F1427" s="106" t="inlineStr">
+        <is>
+          <t>[Updated 'gesture, gesticulation' -&gt; 'gesture, gesticulation; currency (economic sense)' by project-wide decision of 7 October 2026 (AA key term 16).]</t>
+        </is>
+      </c>
       <c r="G1427" s="121" t="n"/>
       <c r="H1427" s="121" t="n"/>
       <c r="I1427" s="120" t="n"/>
@@ -60802,6 +60823,1437 @@
       </c>
       <c r="J2245" s="0" t="n"/>
       <c r="K2245" s="0" t="n"/>
+    </row>
+    <row r="2246">
+      <c r="A2246" s="0" t="inlineStr">
+        <is>
+          <t>आवर्तनशील अर्थव्यवस्था</t>
+        </is>
+      </c>
+      <c r="B2246" s="0" t="inlineStr">
+        <is>
+          <t>cyclical economy</t>
+        </is>
+      </c>
+      <c r="C2246" s="0" t="inlineStr">
+        <is>
+          <t>avartansheel arthvyavastha</t>
+        </is>
+      </c>
+      <c r="F2246" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 1.</t>
+        </is>
+      </c>
+      <c r="I2246" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 48</t>
+        </is>
+      </c>
+    </row>
+    <row r="2247">
+      <c r="A2247" s="0" t="inlineStr">
+        <is>
+          <t>वर्तुलाकार</t>
+        </is>
+      </c>
+      <c r="B2247" s="0" t="inlineStr">
+        <is>
+          <t>circular (shape)</t>
+        </is>
+      </c>
+      <c r="C2247" s="0" t="inlineStr">
+        <is>
+          <t>vartulakar</t>
+        </is>
+      </c>
+      <c r="F2247" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 2.</t>
+        </is>
+      </c>
+      <c r="I2247" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="2248">
+      <c r="A2248" s="0" t="inlineStr">
+        <is>
+          <t>चक्राकार</t>
+        </is>
+      </c>
+      <c r="B2248" s="0" t="inlineStr">
+        <is>
+          <t>circular (shape)</t>
+        </is>
+      </c>
+      <c r="C2248" s="0" t="inlineStr">
+        <is>
+          <t>chakrakar</t>
+        </is>
+      </c>
+      <c r="F2248" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 2.</t>
+        </is>
+      </c>
+      <c r="I2248" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 15</t>
+        </is>
+      </c>
+    </row>
+    <row r="2249">
+      <c r="A2249" s="0" t="inlineStr">
+        <is>
+          <t>तन-मन-धन रूपी अर्थ</t>
+        </is>
+      </c>
+      <c r="B2249" s="0" t="inlineStr">
+        <is>
+          <t>resources in the form of body, mind and wealth</t>
+        </is>
+      </c>
+      <c r="C2249" s="0" t="inlineStr">
+        <is>
+          <t>tan-man-dhan rupi arth</t>
+        </is>
+      </c>
+      <c r="F2249" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 3-4.</t>
+        </is>
+      </c>
+      <c r="I2249" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="2250">
+      <c r="A2250" s="0" t="inlineStr">
+        <is>
+          <t>धन समृद्धि</t>
+        </is>
+      </c>
+      <c r="B2250" s="0" t="inlineStr">
+        <is>
+          <t>wealthy; being wealthy (noun use)</t>
+        </is>
+      </c>
+      <c r="C2250" s="0" t="inlineStr">
+        <is>
+          <t>dhan samriddhi</t>
+        </is>
+      </c>
+      <c r="F2250" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 4.</t>
+        </is>
+      </c>
+      <c r="I2250" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 38</t>
+        </is>
+      </c>
+    </row>
+    <row r="2251">
+      <c r="A2251" s="0" t="inlineStr">
+        <is>
+          <t>श्रम नियोजन स्थली</t>
+        </is>
+      </c>
+      <c r="B2251" s="0" t="inlineStr">
+        <is>
+          <t>sites for the utilisation of labour</t>
+        </is>
+      </c>
+      <c r="C2251" s="0" t="inlineStr">
+        <is>
+          <t>shram niyojan sthali</t>
+        </is>
+      </c>
+      <c r="F2251" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 6.</t>
+        </is>
+      </c>
+      <c r="I2251" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="2252">
+      <c r="A2252" s="0" t="inlineStr">
+        <is>
+          <t>सदुपयोगिता</t>
+        </is>
+      </c>
+      <c r="B2252" s="0" t="inlineStr">
+        <is>
+          <t>right-use</t>
+        </is>
+      </c>
+      <c r="C2252" s="0" t="inlineStr">
+        <is>
+          <t>sadupyogita</t>
+        </is>
+      </c>
+      <c r="F2252" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 8.</t>
+        </is>
+      </c>
+      <c r="I2252" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="2253">
+      <c r="A2253" s="0" t="inlineStr">
+        <is>
+          <t>आवश्यकता से अधिक उत्पादन</t>
+        </is>
+      </c>
+      <c r="B2253" s="0" t="inlineStr">
+        <is>
+          <t>production in excess of need</t>
+        </is>
+      </c>
+      <c r="C2253" s="0" t="inlineStr">
+        <is>
+          <t>avashyakta se adhik utpadan</t>
+        </is>
+      </c>
+      <c r="F2253" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 10.</t>
+        </is>
+      </c>
+      <c r="I2253" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="2254">
+      <c r="A2254" s="0" t="inlineStr">
+        <is>
+          <t>सामान्य आकांक्षा</t>
+        </is>
+      </c>
+      <c r="B2254" s="0" t="inlineStr">
+        <is>
+          <t>common aspirations</t>
+        </is>
+      </c>
+      <c r="C2254" s="0" t="inlineStr">
+        <is>
+          <t>samanya akanksha</t>
+        </is>
+      </c>
+      <c r="F2254" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 12.</t>
+        </is>
+      </c>
+      <c r="I2254" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 66</t>
+        </is>
+      </c>
+    </row>
+    <row r="2255">
+      <c r="A2255" s="0" t="inlineStr">
+        <is>
+          <t>परावर्तन विधि</t>
+        </is>
+      </c>
+      <c r="B2255" s="0" t="inlineStr">
+        <is>
+          <t>method of projection</t>
+        </is>
+      </c>
+      <c r="C2255" s="0" t="inlineStr">
+        <is>
+          <t>paravartan vidhi</t>
+        </is>
+      </c>
+      <c r="F2255" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 13.</t>
+        </is>
+      </c>
+      <c r="I2255" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="2256">
+      <c r="A2256" s="0" t="inlineStr">
+        <is>
+          <t>लाभ</t>
+        </is>
+      </c>
+      <c r="B2256" s="0" t="inlineStr">
+        <is>
+          <t>profit</t>
+        </is>
+      </c>
+      <c r="C2256" s="0" t="inlineStr">
+        <is>
+          <t>labh</t>
+        </is>
+      </c>
+      <c r="F2256" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 14.</t>
+        </is>
+      </c>
+      <c r="I2256" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 21</t>
+        </is>
+      </c>
+    </row>
+    <row r="2257">
+      <c r="A2257" s="0" t="inlineStr">
+        <is>
+          <t>लाभ हानि</t>
+        </is>
+      </c>
+      <c r="B2257" s="0" t="inlineStr">
+        <is>
+          <t>profit and loss</t>
+        </is>
+      </c>
+      <c r="C2257" s="0" t="inlineStr">
+        <is>
+          <t>labh hani</t>
+        </is>
+      </c>
+      <c r="F2257" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 14.</t>
+        </is>
+      </c>
+      <c r="I2257" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 21</t>
+        </is>
+      </c>
+    </row>
+    <row r="2258">
+      <c r="A2258" s="0" t="inlineStr">
+        <is>
+          <t>लाभोन्मादी अर्थव्यवस्था</t>
+        </is>
+      </c>
+      <c r="B2258" s="0" t="inlineStr">
+        <is>
+          <t>profit-obsessed economy</t>
+        </is>
+      </c>
+      <c r="C2258" s="0" t="inlineStr">
+        <is>
+          <t>labhonmadi arthvyavastha</t>
+        </is>
+      </c>
+      <c r="F2258" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 14.</t>
+        </is>
+      </c>
+      <c r="I2258" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 48</t>
+        </is>
+      </c>
+    </row>
+    <row r="2259">
+      <c r="A2259" s="0" t="inlineStr">
+        <is>
+          <t>लाभाकांक्षी</t>
+        </is>
+      </c>
+      <c r="B2259" s="0" t="inlineStr">
+        <is>
+          <t>profit-seeking</t>
+        </is>
+      </c>
+      <c r="C2259" s="0" t="inlineStr">
+        <is>
+          <t>labhakankshi</t>
+        </is>
+      </c>
+      <c r="F2259" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 14.</t>
+        </is>
+      </c>
+      <c r="I2259" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 46</t>
+        </is>
+      </c>
+    </row>
+    <row r="2260">
+      <c r="A2260" s="0" t="inlineStr">
+        <is>
+          <t>लाभ प्रथा</t>
+        </is>
+      </c>
+      <c r="B2260" s="0" t="inlineStr">
+        <is>
+          <t>profiteering</t>
+        </is>
+      </c>
+      <c r="C2260" s="0" t="inlineStr">
+        <is>
+          <t>labh pratha</t>
+        </is>
+      </c>
+      <c r="F2260" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 14.</t>
+        </is>
+      </c>
+      <c r="I2260" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 52</t>
+        </is>
+      </c>
+    </row>
+    <row r="2261">
+      <c r="A2261" s="0" t="inlineStr">
+        <is>
+          <t>व्यापार</t>
+        </is>
+      </c>
+      <c r="B2261" s="0" t="inlineStr">
+        <is>
+          <t>trade</t>
+        </is>
+      </c>
+      <c r="C2261" s="0" t="inlineStr">
+        <is>
+          <t>vyapar</t>
+        </is>
+      </c>
+      <c r="F2261" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 15.</t>
+        </is>
+      </c>
+      <c r="I2261" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="2262">
+      <c r="A2262" s="0" t="inlineStr">
+        <is>
+          <t>व्यापार विधि</t>
+        </is>
+      </c>
+      <c r="B2262" s="0" t="inlineStr">
+        <is>
+          <t>the method of trade</t>
+        </is>
+      </c>
+      <c r="C2262" s="0" t="inlineStr">
+        <is>
+          <t>vyapar vidhi</t>
+        </is>
+      </c>
+      <c r="F2262" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 15.</t>
+        </is>
+      </c>
+      <c r="I2262" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="2263">
+      <c r="A2263" s="0" t="inlineStr">
+        <is>
+          <t>व्यापारोन्मुखी</t>
+        </is>
+      </c>
+      <c r="B2263" s="0" t="inlineStr">
+        <is>
+          <t>trade-oriented</t>
+        </is>
+      </c>
+      <c r="C2263" s="0" t="inlineStr">
+        <is>
+          <t>vyaparonmukhi</t>
+        </is>
+      </c>
+      <c r="F2263" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 15.</t>
+        </is>
+      </c>
+      <c r="I2263" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 46</t>
+        </is>
+      </c>
+    </row>
+    <row r="2264">
+      <c r="A2264" s="0" t="inlineStr">
+        <is>
+          <t>पत्र मुद्रा</t>
+        </is>
+      </c>
+      <c r="B2264" s="0" t="inlineStr">
+        <is>
+          <t>paper currency</t>
+        </is>
+      </c>
+      <c r="C2264" s="0" t="inlineStr">
+        <is>
+          <t>patra mudra</t>
+        </is>
+      </c>
+      <c r="F2264" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 16.</t>
+        </is>
+      </c>
+      <c r="I2264" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="2265">
+      <c r="A2265" s="0" t="inlineStr">
+        <is>
+          <t>धातु मुद्रा</t>
+        </is>
+      </c>
+      <c r="B2265" s="0" t="inlineStr">
+        <is>
+          <t>metal currency</t>
+        </is>
+      </c>
+      <c r="C2265" s="0" t="inlineStr">
+        <is>
+          <t>dhatu mudra</t>
+        </is>
+      </c>
+      <c r="F2265" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 16.</t>
+        </is>
+      </c>
+      <c r="I2265" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="2266">
+      <c r="A2266" s="0" t="inlineStr">
+        <is>
+          <t>राष्ट्रीय कोष</t>
+        </is>
+      </c>
+      <c r="B2266" s="0" t="inlineStr">
+        <is>
+          <t>reserve bank</t>
+        </is>
+      </c>
+      <c r="C2266" s="0" t="inlineStr">
+        <is>
+          <t>rashtriya kosh</t>
+        </is>
+      </c>
+      <c r="F2266" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 17.</t>
+        </is>
+      </c>
+      <c r="I2266" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 51</t>
+        </is>
+      </c>
+    </row>
+    <row r="2267">
+      <c r="A2267" s="0" t="inlineStr">
+        <is>
+          <t>सुवर्ण द्रव्य मूलक मूल्यांकन</t>
+        </is>
+      </c>
+      <c r="B2267" s="0" t="inlineStr">
+        <is>
+          <t>gold-based valuation; currency pegged to gold</t>
+        </is>
+      </c>
+      <c r="C2267" s="0" t="inlineStr">
+        <is>
+          <t>suvarna dravya mulak mulyankan</t>
+        </is>
+      </c>
+      <c r="F2267" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 17.</t>
+        </is>
+      </c>
+      <c r="I2267" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 51</t>
+        </is>
+      </c>
+    </row>
+    <row r="2268">
+      <c r="A2268" s="0" t="inlineStr">
+        <is>
+          <t>पूँजी</t>
+        </is>
+      </c>
+      <c r="B2268" s="0" t="inlineStr">
+        <is>
+          <t>capital</t>
+        </is>
+      </c>
+      <c r="C2268" s="0" t="inlineStr">
+        <is>
+          <t>punji</t>
+        </is>
+      </c>
+      <c r="F2268" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 18.</t>
+        </is>
+      </c>
+      <c r="I2268" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 44</t>
+        </is>
+      </c>
+    </row>
+    <row r="2269">
+      <c r="A2269" s="0" t="inlineStr">
+        <is>
+          <t>मूल पूँजी</t>
+        </is>
+      </c>
+      <c r="B2269" s="0" t="inlineStr">
+        <is>
+          <t>primary capital</t>
+        </is>
+      </c>
+      <c r="C2269" s="0" t="inlineStr">
+        <is>
+          <t>mul punji</t>
+        </is>
+      </c>
+      <c r="F2269" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 18.</t>
+        </is>
+      </c>
+      <c r="I2269" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 44</t>
+        </is>
+      </c>
+    </row>
+    <row r="2270">
+      <c r="A2270" s="0" t="inlineStr">
+        <is>
+          <t>ब्याज प्रथा</t>
+        </is>
+      </c>
+      <c r="B2270" s="0" t="inlineStr">
+        <is>
+          <t>practice of collecting interest</t>
+        </is>
+      </c>
+      <c r="C2270" s="0" t="inlineStr">
+        <is>
+          <t>byaj pratha</t>
+        </is>
+      </c>
+      <c r="F2270" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 18.</t>
+        </is>
+      </c>
+      <c r="I2270" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 52</t>
+        </is>
+      </c>
+    </row>
+    <row r="2271">
+      <c r="A2271" s="0" t="inlineStr">
+        <is>
+          <t>विनिमय</t>
+        </is>
+      </c>
+      <c r="B2271" s="0" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="C2271" s="0" t="inlineStr">
+        <is>
+          <t>vinimay</t>
+        </is>
+      </c>
+      <c r="F2271" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 20.</t>
+        </is>
+      </c>
+      <c r="I2271" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="2272">
+      <c r="A2272" s="0" t="inlineStr">
+        <is>
+          <t>विनिमय प्रणाली</t>
+        </is>
+      </c>
+      <c r="B2272" s="0" t="inlineStr">
+        <is>
+          <t>exchange system</t>
+        </is>
+      </c>
+      <c r="C2272" s="0" t="inlineStr">
+        <is>
+          <t>vinimay pranali</t>
+        </is>
+      </c>
+      <c r="F2272" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 20.</t>
+        </is>
+      </c>
+      <c r="I2272" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 51</t>
+        </is>
+      </c>
+    </row>
+    <row r="2273">
+      <c r="A2273" s="0" t="inlineStr">
+        <is>
+          <t>वस्तु विनिमय प्रणाली</t>
+        </is>
+      </c>
+      <c r="B2273" s="0" t="inlineStr">
+        <is>
+          <t>barter system</t>
+        </is>
+      </c>
+      <c r="C2273" s="0" t="inlineStr">
+        <is>
+          <t>vastu vinimay pranali</t>
+        </is>
+      </c>
+      <c r="F2273" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 20.</t>
+        </is>
+      </c>
+      <c r="I2273" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="2274">
+      <c r="A2274" s="0" t="inlineStr">
+        <is>
+          <t>श्रम विनिमय प्रणाली</t>
+        </is>
+      </c>
+      <c r="B2274" s="0" t="inlineStr">
+        <is>
+          <t>system of exchange of labour</t>
+        </is>
+      </c>
+      <c r="C2274" s="0" t="inlineStr">
+        <is>
+          <t>shram vinimay pranali</t>
+        </is>
+      </c>
+      <c r="F2274" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 20.</t>
+        </is>
+      </c>
+      <c r="I2274" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 62</t>
+        </is>
+      </c>
+    </row>
+    <row r="2275">
+      <c r="A2275" s="0" t="inlineStr">
+        <is>
+          <t>संग्रहण</t>
+        </is>
+      </c>
+      <c r="B2275" s="0" t="inlineStr">
+        <is>
+          <t>accumulating</t>
+        </is>
+      </c>
+      <c r="C2275" s="0" t="inlineStr">
+        <is>
+          <t>sangrahan</t>
+        </is>
+      </c>
+      <c r="F2275" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 21.</t>
+        </is>
+      </c>
+      <c r="I2275" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="2276">
+      <c r="A2276" s="0" t="inlineStr">
+        <is>
+          <t>संग्रहवादी</t>
+        </is>
+      </c>
+      <c r="B2276" s="0" t="inlineStr">
+        <is>
+          <t>accumulation-oriented</t>
+        </is>
+      </c>
+      <c r="C2276" s="0" t="inlineStr">
+        <is>
+          <t>sangrahvadi</t>
+        </is>
+      </c>
+      <c r="F2276" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 21.</t>
+        </is>
+      </c>
+      <c r="I2276" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 46</t>
+        </is>
+      </c>
+    </row>
+    <row r="2277">
+      <c r="A2277" s="0" t="inlineStr">
+        <is>
+          <t>भोगवादी</t>
+        </is>
+      </c>
+      <c r="B2277" s="0" t="inlineStr">
+        <is>
+          <t>indulgence-oriented</t>
+        </is>
+      </c>
+      <c r="C2277" s="0" t="inlineStr">
+        <is>
+          <t>bhogvadi</t>
+        </is>
+      </c>
+      <c r="F2277" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 22.</t>
+        </is>
+      </c>
+      <c r="I2277" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 46</t>
+        </is>
+      </c>
+    </row>
+    <row r="2278">
+      <c r="A2278" s="0" t="inlineStr">
+        <is>
+          <t>उपभोक्तावादी</t>
+        </is>
+      </c>
+      <c r="B2278" s="0" t="inlineStr">
+        <is>
+          <t>consumerist</t>
+        </is>
+      </c>
+      <c r="C2278" s="0" t="inlineStr">
+        <is>
+          <t>upbhoktavadi</t>
+        </is>
+      </c>
+      <c r="F2278" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 22.</t>
+        </is>
+      </c>
+      <c r="I2278" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="2279">
+      <c r="A2279" s="0" t="inlineStr">
+        <is>
+          <t>विलासिता</t>
+        </is>
+      </c>
+      <c r="B2279" s="0" t="inlineStr">
+        <is>
+          <t>luxury</t>
+        </is>
+      </c>
+      <c r="C2279" s="0" t="inlineStr">
+        <is>
+          <t>vilasita</t>
+        </is>
+      </c>
+      <c r="F2279" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 22.</t>
+        </is>
+      </c>
+      <c r="I2279" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 61</t>
+        </is>
+      </c>
+    </row>
+    <row r="2280">
+      <c r="A2280" s="0" t="inlineStr">
+        <is>
+          <t>सुविधा संग्रह</t>
+        </is>
+      </c>
+      <c r="B2280" s="0" t="inlineStr">
+        <is>
+          <t>accumulation of comforts</t>
+        </is>
+      </c>
+      <c r="C2280" s="0" t="inlineStr">
+        <is>
+          <t>suvidha sangrah</t>
+        </is>
+      </c>
+      <c r="F2280" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 23.</t>
+        </is>
+      </c>
+      <c r="I2280" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 83</t>
+        </is>
+      </c>
+    </row>
+    <row r="2281">
+      <c r="A2281" s="0" t="inlineStr">
+        <is>
+          <t>सुविधावादी मानसिकता</t>
+        </is>
+      </c>
+      <c r="B2281" s="0" t="inlineStr">
+        <is>
+          <t>comfort-oriented mentality</t>
+        </is>
+      </c>
+      <c r="C2281" s="0" t="inlineStr">
+        <is>
+          <t>suvidhavadi mansikta</t>
+        </is>
+      </c>
+      <c r="F2281" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 23.</t>
+        </is>
+      </c>
+      <c r="I2281" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 75</t>
+        </is>
+      </c>
+    </row>
+    <row r="2282">
+      <c r="A2282" s="0" t="inlineStr">
+        <is>
+          <t>दोहन</t>
+        </is>
+      </c>
+      <c r="B2282" s="0" t="inlineStr">
+        <is>
+          <t>extraction</t>
+        </is>
+      </c>
+      <c r="C2282" s="0" t="inlineStr">
+        <is>
+          <t>dohan</t>
+        </is>
+      </c>
+      <c r="F2282" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 24.</t>
+        </is>
+      </c>
+      <c r="I2282" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 68</t>
+        </is>
+      </c>
+    </row>
+    <row r="2283">
+      <c r="A2283" s="0" t="inlineStr">
+        <is>
+          <t>राजगद्दी के कर विधि</t>
+        </is>
+      </c>
+      <c r="B2283" s="0" t="inlineStr">
+        <is>
+          <t>taxation by the throne</t>
+        </is>
+      </c>
+      <c r="C2283" s="0" t="inlineStr">
+        <is>
+          <t>rajgaddi ke kar vidhi</t>
+        </is>
+      </c>
+      <c r="F2283" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 25.</t>
+        </is>
+      </c>
+      <c r="I2283" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="2284">
+      <c r="A2284" s="0" t="inlineStr">
+        <is>
+          <t>कर वसूली</t>
+        </is>
+      </c>
+      <c r="B2284" s="0" t="inlineStr">
+        <is>
+          <t>tax collection</t>
+        </is>
+      </c>
+      <c r="C2284" s="0" t="inlineStr">
+        <is>
+          <t>kar vasuli</t>
+        </is>
+      </c>
+      <c r="F2284" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 25.</t>
+        </is>
+      </c>
+      <c r="I2284" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 138</t>
+        </is>
+      </c>
+    </row>
+    <row r="2285">
+      <c r="A2285" s="0" t="inlineStr">
+        <is>
+          <t>स्वायत्त</t>
+        </is>
+      </c>
+      <c r="B2285" s="0" t="inlineStr">
+        <is>
+          <t>autonomous</t>
+        </is>
+      </c>
+      <c r="C2285" s="0" t="inlineStr">
+        <is>
+          <t>swayatt</t>
+        </is>
+      </c>
+      <c r="F2285" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 26.</t>
+        </is>
+      </c>
+      <c r="I2285" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="2286">
+      <c r="A2286" s="0" t="inlineStr">
+        <is>
+          <t>स्वावलंबी</t>
+        </is>
+      </c>
+      <c r="B2286" s="0" t="inlineStr">
+        <is>
+          <t>self-reliant</t>
+        </is>
+      </c>
+      <c r="C2286" s="0" t="inlineStr">
+        <is>
+          <t>swavalambi</t>
+        </is>
+      </c>
+      <c r="F2286" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 26.</t>
+        </is>
+      </c>
+      <c r="I2286" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="2287">
+      <c r="A2287" s="0" t="inlineStr">
+        <is>
+          <t>परिवार मूलक ग्राम स्वराज्य व्यवस्था</t>
+        </is>
+      </c>
+      <c r="B2287" s="0" t="inlineStr">
+        <is>
+          <t>family-based village self-governing system</t>
+        </is>
+      </c>
+      <c r="C2287" s="0" t="inlineStr">
+        <is>
+          <t>parivar mulak gram swarajya vyavastha</t>
+        </is>
+      </c>
+      <c r="F2287" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 27.</t>
+        </is>
+      </c>
+      <c r="I2287" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 110</t>
+        </is>
+      </c>
+    </row>
+    <row r="2288">
+      <c r="A2288" s="0" t="inlineStr">
+        <is>
+          <t>आबंटन</t>
+        </is>
+      </c>
+      <c r="B2288" s="0" t="inlineStr">
+        <is>
+          <t>allotment</t>
+        </is>
+      </c>
+      <c r="C2288" s="0" t="inlineStr">
+        <is>
+          <t>abantan</t>
+        </is>
+      </c>
+      <c r="F2288" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 29.</t>
+        </is>
+      </c>
+      <c r="I2288" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2289">
+      <c r="A2289" s="0" t="inlineStr">
+        <is>
+          <t>बंटन</t>
+        </is>
+      </c>
+      <c r="B2289" s="0" t="inlineStr">
+        <is>
+          <t>sharing</t>
+        </is>
+      </c>
+      <c r="C2289" s="0" t="inlineStr">
+        <is>
+          <t>bantan</t>
+        </is>
+      </c>
+      <c r="F2289" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 29.</t>
+        </is>
+      </c>
+      <c r="I2289" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2290">
+      <c r="A2290" s="0" t="inlineStr">
+        <is>
+          <t>वितरण</t>
+        </is>
+      </c>
+      <c r="B2290" s="0" t="inlineStr">
+        <is>
+          <t>distribution</t>
+        </is>
+      </c>
+      <c r="C2290" s="0" t="inlineStr">
+        <is>
+          <t>vitaran</t>
+        </is>
+      </c>
+      <c r="F2290" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 29.</t>
+        </is>
+      </c>
+      <c r="I2290" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="2291">
+      <c r="A2291" s="0" t="inlineStr">
+        <is>
+          <t>कुटीर उद्योग</t>
+        </is>
+      </c>
+      <c r="B2291" s="0" t="inlineStr">
+        <is>
+          <t>cottage industry</t>
+        </is>
+      </c>
+      <c r="C2291" s="0" t="inlineStr">
+        <is>
+          <t>kutir udyog</t>
+        </is>
+      </c>
+      <c r="F2291" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 30.</t>
+        </is>
+      </c>
+      <c r="I2291" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 71</t>
+        </is>
+      </c>
+    </row>
+    <row r="2292">
+      <c r="A2292" s="0" t="inlineStr">
+        <is>
+          <t>ग्राम शिल्प</t>
+        </is>
+      </c>
+      <c r="B2292" s="0" t="inlineStr">
+        <is>
+          <t>village crafts</t>
+        </is>
+      </c>
+      <c r="C2292" s="0" t="inlineStr">
+        <is>
+          <t>gram shilp</t>
+        </is>
+      </c>
+      <c r="F2292" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 30.</t>
+        </is>
+      </c>
+      <c r="I2292" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 71</t>
+        </is>
+      </c>
+    </row>
+    <row r="2293">
+      <c r="A2293" s="0" t="inlineStr">
+        <is>
+          <t>ग्रामोद्योग</t>
+        </is>
+      </c>
+      <c r="B2293" s="0" t="inlineStr">
+        <is>
+          <t>village industry</t>
+        </is>
+      </c>
+      <c r="C2293" s="0" t="inlineStr">
+        <is>
+          <t>gramodyog</t>
+        </is>
+      </c>
+      <c r="F2293" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 30.</t>
+        </is>
+      </c>
+      <c r="I2293" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2294">
+      <c r="A2294" s="0" t="inlineStr">
+        <is>
+          <t>कृषि</t>
+        </is>
+      </c>
+      <c r="B2294" s="0" t="inlineStr">
+        <is>
+          <t>agriculture</t>
+        </is>
+      </c>
+      <c r="C2294" s="0" t="inlineStr">
+        <is>
+          <t>krishi</t>
+        </is>
+      </c>
+      <c r="F2294" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 30.</t>
+        </is>
+      </c>
+      <c r="I2294" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 71</t>
+        </is>
+      </c>
+    </row>
+    <row r="2295">
+      <c r="A2295" s="0" t="inlineStr">
+        <is>
+          <t>गोपालन</t>
+        </is>
+      </c>
+      <c r="B2295" s="0" t="inlineStr">
+        <is>
+          <t>cattle-rearing</t>
+        </is>
+      </c>
+      <c r="C2295" s="0" t="inlineStr">
+        <is>
+          <t>gopalan</t>
+        </is>
+      </c>
+      <c r="F2295" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 30.</t>
+        </is>
+      </c>
+      <c r="I2295" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 71</t>
+        </is>
+      </c>
+    </row>
+    <row r="2296">
+      <c r="A2296" s="0" t="inlineStr">
+        <is>
+          <t>ठोस</t>
+        </is>
+      </c>
+      <c r="B2296" s="0" t="inlineStr">
+        <is>
+          <t>solid</t>
+        </is>
+      </c>
+      <c r="C2296" s="0" t="inlineStr">
+        <is>
+          <t>thos</t>
+        </is>
+      </c>
+      <c r="F2296" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 35.</t>
+        </is>
+      </c>
+      <c r="I2296" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 34</t>
+        </is>
+      </c>
+    </row>
+    <row r="2297">
+      <c r="A2297" s="0" t="inlineStr">
+        <is>
+          <t>तरल</t>
+        </is>
+      </c>
+      <c r="B2297" s="0" t="inlineStr">
+        <is>
+          <t>liquid</t>
+        </is>
+      </c>
+      <c r="C2297" s="0" t="inlineStr">
+        <is>
+          <t>taral</t>
+        </is>
+      </c>
+      <c r="F2297" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 35.</t>
+        </is>
+      </c>
+      <c r="I2297" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 34</t>
+        </is>
+      </c>
+    </row>
+    <row r="2298">
+      <c r="A2298" s="0" t="inlineStr">
+        <is>
+          <t>विरल वस्तु</t>
+        </is>
+      </c>
+      <c r="B2298" s="0" t="inlineStr">
+        <is>
+          <t>rarefied (gaseous) matter</t>
+        </is>
+      </c>
+      <c r="C2298" s="0" t="inlineStr">
+        <is>
+          <t>viral vastu</t>
+        </is>
+      </c>
+      <c r="F2298" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 35.</t>
+        </is>
+      </c>
+      <c r="I2298" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 34</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -61262,7 +62714,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Per MD-Mapping ("effort, physical labour"), whose notes state: "We are using 'effort' for shram in the sense of shram-gati-parinam." "Labour" only in economic compounds (श्रम मूल्य \= evaluation of labour, श्रम विनिमय \= exchange of labour, श्रम नियोजन \= utilisation of labour — updated 2026-07-08 per MVD; these compounds have not yet appeared in translated KD text). KD 3.11 (p. 117): श्रम-गति-परिणाम triad → "effort, motion, and result" — aligned with MVD/SB "Effort – Motion – Result"; effort \= grandeur of the existent-state, motion \= spreading of effect, result \= grandeur of a different existent-state</t>
+          <t>Per MD-Mapping ("effort, physical labour"), whose notes state: "We are using 'effort' for shram in the sense of shram-gati-parinam." "Labour" only in economic compounds (श्रम मूल्य \= value of labour, by the project-wide decision of 7 October 2026 that superseded the 2026-07-08 "evaluation of labour"; श्रम विनिमय \= exchange of labour, श्रम नियोजन \= utilisation of labour — updated 2026-07-08 per MVD; these compounds have not yet appeared in translated KD text). KD 3.11 (p. 117): श्रम-गति-परिणाम triad → "effort, motion, and result" — aligned with MVD/SB "Effort – Motion – Result"; effort \= grandeur of the existent-state, motion \= spreading of effect, result \= grandeur of a different existent-state</t>
         </is>
       </c>
     </row>
@@ -65176,7 +66628,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Per MD-Mapping ("effort, physical labour"), whose notes state: "We are using 'effort' for shram in the sense of shram-gati-parinam." "Labour" only in economic compounds (श्रम मूल्य \= evaluation of labour, श्रम विनिमय \= exchange of labour, श्रम नियोजन \= utilisation of labour — updated 2026-07-08 per MVD; these compounds have not yet appeared in translated KD text). KD 3.11 (p. 117): श्रम-गति-परिणाम triad → "effort, motion, and result" — aligned with MVD/SB "Effort – Motion – Result"; effort \= grandeur of the existent-state, motion \= spreading of effect, result \= grandeur of a different existent-state</t>
+          <t>Per MD-Mapping ("effort, physical labour"), whose notes state: "We are using 'effort' for shram in the sense of shram-gati-parinam." "Labour" only in economic compounds (श्रम मूल्य \= value of labour, by the project-wide decision of 7 October 2026 that superseded the 2026-07-08 "evaluation of labour"; श्रम विनिमय \= exchange of labour, श्रम नियोजन \= utilisation of labour — updated 2026-07-08 per MVD; these compounds have not yet appeared in translated KD text). KD 3.11 (p. 117): श्रम-गति-परिणाम triad → "effort, motion, and result" — aligned with MVD/SB "Effort – Motion – Result"; effort \= grandeur of the existent-state, motion \= spreading of effect, result \= grandeur of a different existent-state</t>
         </is>
       </c>
     </row>

--- a/References/Madhyasth-Darshan/KD-Karm-Darshan-English/KD-Translation-Glossary.xlsx
+++ b/References/Madhyasth-Darshan/KD-Karm-Darshan-English/KD-Translation-Glossary.xlsx
@@ -911,7 +911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2298"/>
+  <dimension ref="A1:K2304"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="13.4399995803833" defaultRowHeight="15"/>
   <cols>
     <col width="23.21999931335449" customWidth="1" style="114" min="1" max="1"/>
@@ -61372,7 +61372,7 @@
       </c>
       <c r="B2266" s="0" t="inlineStr">
         <is>
-          <t>reserve bank</t>
+          <t>national reserve(s)</t>
         </is>
       </c>
       <c r="C2266" s="0" t="inlineStr">
@@ -61387,7 +61387,7 @@
       </c>
       <c r="I2266" s="0" t="inlineStr">
         <is>
-          <t>AA-Glossary-Additions.md; AA p. 51</t>
+          <t>AA-Glossary-Additions.md; AA pp. 44-45, 51</t>
         </is>
       </c>
     </row>
@@ -62252,6 +62252,168 @@
       <c r="I2298" s="0" t="inlineStr">
         <is>
           <t>AA-Glossary-Additions.md; AA p. 34</t>
+        </is>
+      </c>
+    </row>
+    <row r="2299">
+      <c r="A2299" s="0" t="inlineStr">
+        <is>
+          <t>राष्ट्रीय मुद्रा कोष, राष्ट्रीय मुद्राकोष</t>
+        </is>
+      </c>
+      <c r="B2299" s="0" t="inlineStr">
+        <is>
+          <t>reserve bank</t>
+        </is>
+      </c>
+      <c r="C2299" s="0" t="inlineStr">
+        <is>
+          <t>rashtriya mudra kosh</t>
+        </is>
+      </c>
+      <c r="F2299" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 17.</t>
+        </is>
+      </c>
+      <c r="I2299" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA pp. 44-45</t>
+        </is>
+      </c>
+    </row>
+    <row r="2300">
+      <c r="A2300" s="0" t="inlineStr">
+        <is>
+          <t>अंतर्राष्ट्रीय मुद्रा कोष</t>
+        </is>
+      </c>
+      <c r="B2300" s="0" t="inlineStr">
+        <is>
+          <t>International Monetary Fund</t>
+        </is>
+      </c>
+      <c r="C2300" s="0" t="inlineStr">
+        <is>
+          <t>antarrashtriya mudra kosh</t>
+        </is>
+      </c>
+      <c r="F2300" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 17.</t>
+        </is>
+      </c>
+      <c r="I2300" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 44</t>
+        </is>
+      </c>
+    </row>
+    <row r="2301">
+      <c r="A2301" s="0" t="inlineStr">
+        <is>
+          <t>अन्तर्राष्ट्रीय कोष, अंतर्राष्ट्रीय कोष</t>
+        </is>
+      </c>
+      <c r="B2301" s="0" t="inlineStr">
+        <is>
+          <t>international reserves</t>
+        </is>
+      </c>
+      <c r="C2301" s="0" t="inlineStr">
+        <is>
+          <t>antarrashtriya kosh</t>
+        </is>
+      </c>
+      <c r="F2301" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 17.</t>
+        </is>
+      </c>
+      <c r="I2301" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 51</t>
+        </is>
+      </c>
+    </row>
+    <row r="2302">
+      <c r="A2302" s="0" t="inlineStr">
+        <is>
+          <t>मुद्रा कोष</t>
+        </is>
+      </c>
+      <c r="B2302" s="0" t="inlineStr">
+        <is>
+          <t>currency reserve</t>
+        </is>
+      </c>
+      <c r="C2302" s="0" t="inlineStr">
+        <is>
+          <t>mudra kosh</t>
+        </is>
+      </c>
+      <c r="F2302" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 17.</t>
+        </is>
+      </c>
+      <c r="I2302" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 45</t>
+        </is>
+      </c>
+    </row>
+    <row r="2303">
+      <c r="A2303" s="0" t="inlineStr">
+        <is>
+          <t>धातु कोष</t>
+        </is>
+      </c>
+      <c r="B2303" s="0" t="inlineStr">
+        <is>
+          <t>metal reserve</t>
+        </is>
+      </c>
+      <c r="C2303" s="0" t="inlineStr">
+        <is>
+          <t>dhatu kosh</t>
+        </is>
+      </c>
+      <c r="F2303" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 17.</t>
+        </is>
+      </c>
+      <c r="I2303" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="2304">
+      <c r="A2304" s="0" t="inlineStr">
+        <is>
+          <t>धातु कोषालय</t>
+        </is>
+      </c>
+      <c r="B2304" s="0" t="inlineStr">
+        <is>
+          <t>metal treasury</t>
+        </is>
+      </c>
+      <c r="C2304" s="0" t="inlineStr">
+        <is>
+          <t>dhatu koshalay</t>
+        </is>
+      </c>
+      <c r="F2304" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026): AA key term 17.</t>
+        </is>
+      </c>
+      <c r="I2304" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 6</t>
         </is>
       </c>
     </row>

--- a/References/Madhyasth-Darshan/KD-Karm-Darshan-English/KD-Translation-Glossary.xlsx
+++ b/References/Madhyasth-Darshan/KD-Karm-Darshan-English/KD-Translation-Glossary.xlsx
@@ -911,7 +911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2304"/>
+  <dimension ref="A1:K2305"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="13.4399995803833" defaultRowHeight="15"/>
   <cols>
     <col width="23.21999931335449" customWidth="1" style="114" min="1" max="1"/>
@@ -62414,6 +62414,33 @@
       <c r="I2304" s="0" t="inlineStr">
         <is>
           <t>AA-Glossary-Additions.md; AA p. 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="2305">
+      <c r="A2305" s="0" t="inlineStr">
+        <is>
+          <t>नियतिक्रम</t>
+        </is>
+      </c>
+      <c r="B2305" s="0" t="inlineStr">
+        <is>
+          <t>natural progression</t>
+        </is>
+      </c>
+      <c r="C2305" s="0" t="inlineStr">
+        <is>
+          <t>niyatikram</t>
+        </is>
+      </c>
+      <c r="F2305" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of 7 October 2026), following KD's front matter. MVD p. 8 and SB render the same passage 'destiny progression'; MVD uses 'natural progression' for अनुक्रम.</t>
+        </is>
+      </c>
+      <c r="I2305" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA PDF p. 6; KD front matter</t>
         </is>
       </c>
     </row>

--- a/References/Madhyasth-Darshan/KD-Karm-Darshan-English/KD-Translation-Glossary.xlsx
+++ b/References/Madhyasth-Darshan/KD-Karm-Darshan-English/KD-Translation-Glossary.xlsx
@@ -911,7 +911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2305"/>
+  <dimension ref="A1:K2309"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="13.4399995803833" defaultRowHeight="15"/>
   <cols>
     <col width="23.21999931335449" customWidth="1" style="114" min="1" max="1"/>
@@ -8757,6 +8757,11 @@
       </c>
       <c r="D238" s="118" t="n"/>
       <c r="E238" s="119" t="n"/>
+      <c r="F238" s="0" t="inlineStr">
+        <is>
+          <t>Confirmed as 'independence' (project-wide decision of the author, 13 October 2026); the AA chapter 7 title is 'Awakening and Independence'. कर्म स्वतंत्रता stays 'freedom of action'.</t>
+        </is>
+      </c>
       <c r="G238" s="120" t="inlineStr">
         <is>
           <t>ownership, identity</t>
@@ -28804,7 +28809,7 @@
       </c>
       <c r="F870" s="121" t="inlineStr">
         <is>
-          <t>in some contexts 'suvidha' has been used for indicating 'luxury'.</t>
+          <t>in some contexts 'suvidha' has been used for indicating 'luxury'. | 'facilities' where सुविधा means public or village services (project-wide decision of the author, 13 October 2026; see the row 'सुविधा (public services)').</t>
         </is>
       </c>
       <c r="G870" s="121" t="inlineStr">
@@ -34777,7 +34782,7 @@
       <c r="E1061" s="119" t="n"/>
       <c r="F1061" s="120" t="inlineStr">
         <is>
-          <t>tva sahit vyavastha, samagra vyavastha me bhagidari</t>
+          <t>tva sahit vyavastha, samagra vyavastha me bhagidari | Confirmed as 'independence' (project-wide decision of the author, 13 October 2026); the AA chapter 7 title is 'Awakening and Independence'. कर्म स्वतंत्रता stays 'freedom of action'.</t>
         </is>
       </c>
       <c r="G1061" s="121" t="n"/>
@@ -43557,7 +43562,7 @@
       </c>
       <c r="B1337" s="116" t="inlineStr">
         <is>
-          <t>doing</t>
+          <t>done</t>
         </is>
       </c>
       <c r="C1337" s="117" t="inlineStr">
@@ -43571,7 +43576,11 @@
         </is>
       </c>
       <c r="E1337" s="119" t="n"/>
-      <c r="F1337" s="120" t="n"/>
+      <c r="F1337" s="120" t="inlineStr">
+        <is>
+          <t>In the triad कृत, कारित, अनुमोदित: done, caused, intended (project-wide decision of the author, 13 October 2026; the author's KD rendering, settled 8 July 2026). Formerly 'doing'.</t>
+        </is>
+      </c>
       <c r="G1337" s="121" t="n"/>
       <c r="H1337" s="121" t="n"/>
       <c r="I1337" s="120" t="inlineStr">
@@ -43590,7 +43599,7 @@
       </c>
       <c r="B1338" s="116" t="inlineStr">
         <is>
-          <t>getting done</t>
+          <t>caused</t>
         </is>
       </c>
       <c r="C1338" s="117" t="inlineStr">
@@ -43606,7 +43615,7 @@
       <c r="E1338" s="119" t="n"/>
       <c r="F1338" s="120" t="inlineStr">
         <is>
-          <t>delegating</t>
+          <t>delegating | In the triad कृत, कारित, अनुमोदित: done, caused, intended (project-wide decision of the author, 13 October 2026; the author's KD rendering, settled 8 July 2026). Formerly 'getting done'.</t>
         </is>
       </c>
       <c r="G1338" s="121" t="n"/>
@@ -43627,7 +43636,7 @@
       </c>
       <c r="B1339" s="116" t="inlineStr">
         <is>
-          <t>consenting</t>
+          <t>intended</t>
         </is>
       </c>
       <c r="C1339" s="117" t="inlineStr">
@@ -43643,7 +43652,7 @@
       <c r="E1339" s="119" t="n"/>
       <c r="F1339" s="120" t="inlineStr">
         <is>
-          <t>consenting, approving, subscribing</t>
+          <t>consenting, approving, subscribing | In the triad कृत, कारित, अनुमोदित: done, caused, intended (project-wide decision of the author, 13 October 2026; the author's KD rendering, settled 8 July 2026). Formerly 'consenting'.</t>
         </is>
       </c>
       <c r="G1339" s="121" t="n"/>
@@ -62441,6 +62450,114 @@
       <c r="I2305" s="0" t="inlineStr">
         <is>
           <t>AA-Glossary-Additions.md; AA PDF p. 6; KD front matter</t>
+        </is>
+      </c>
+    </row>
+    <row r="2306">
+      <c r="A2306" s="0" t="inlineStr">
+        <is>
+          <t>अस्तित्व दर्शन ज्ञान</t>
+        </is>
+      </c>
+      <c r="B2306" s="0" t="inlineStr">
+        <is>
+          <t>knowledge of coexistence</t>
+        </is>
+      </c>
+      <c r="C2306" s="0" t="inlineStr">
+        <is>
+          <t>astitva darshan gyan</t>
+        </is>
+      </c>
+      <c r="F2306" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of the author, 13 October 2026), following the author's wording on AA p. 12. Supersedes MVD's 'knowledge of the holistic view of existence' (MVD p. 259) for this compound; bare अस्तित्व दर्शन and सह-अस्तित्व दर्शन ज्ञान are unchanged.</t>
+        </is>
+      </c>
+      <c r="I2306" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA pp. 12, 19, 47, 99, 102, 113, 121; KD pp. 30, 69</t>
+        </is>
+      </c>
+    </row>
+    <row r="2307">
+      <c r="A2307" s="0" t="inlineStr">
+        <is>
+          <t>कृत, कारित, अनुमोदित</t>
+        </is>
+      </c>
+      <c r="B2307" s="0" t="inlineStr">
+        <is>
+          <t>done, caused, intended</t>
+        </is>
+      </c>
+      <c r="C2307" s="0" t="inlineStr">
+        <is>
+          <t>krit, karit, anumodit</t>
+        </is>
+      </c>
+      <c r="F2307" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of the author, 13 October 2026): the author's KD rendering (settled 8 July 2026) made project-wide; MVD p. 244 has doing, getting done, consenting.</t>
+        </is>
+      </c>
+      <c r="I2307" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA pp. 60, 99; KD-Glossary-Additions.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="2308">
+      <c r="A2308" s="0" t="inlineStr">
+        <is>
+          <t>संतुष्टि</t>
+        </is>
+      </c>
+      <c r="B2308" s="0" t="inlineStr">
+        <is>
+          <t>contentment</t>
+        </is>
+      </c>
+      <c r="C2308" s="0" t="inlineStr">
+        <is>
+          <t>santushti</t>
+        </is>
+      </c>
+      <c r="F2308" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of the author, 13 October 2026). Shares 'contentment' with संतोष (the jeevan value); where the distinction matters, the Hindi word is the guide.</t>
+        </is>
+      </c>
+      <c r="I2308" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA p. 48</t>
+        </is>
+      </c>
+    </row>
+    <row r="2309">
+      <c r="A2309" s="0" t="inlineStr">
+        <is>
+          <t>सुविधा (public services)</t>
+        </is>
+      </c>
+      <c r="B2309" s="0" t="inlineStr">
+        <is>
+          <t>facilities</t>
+        </is>
+      </c>
+      <c r="C2309" s="0" t="inlineStr">
+        <is>
+          <t>suvidha</t>
+        </is>
+      </c>
+      <c r="F2309" s="0" t="inlineStr">
+        <is>
+          <t>AA glossary addition (project-wide decision of the author, 13 October 2026): सुविधा in the sense of village or public services (drinking water, school, roads, post office, bank). Elsewhere सुविधा = comfort(s).</t>
+        </is>
+      </c>
+      <c r="I2309" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA chapter 9</t>
         </is>
       </c>
     </row>
@@ -62458,7 +62575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D186"/>
+  <dimension ref="A1:D190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" style="114" min="1" max="1"/>
@@ -65345,7 +65462,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Settled per Raghava (2026-07-08), superseding this project's earlier "done, caused-to-be-done, and approved"/"consented-to." MD-Mapping's कृत="doing," कारित="getting done," अनुमोदित="consenting" — kept close but simplified; अनुमोदित specifically rendered "intended" rather than "approved"/"consenting" per this decision. Retrofitted in KD-Karm-Darshan-English.md §3.11–3.12 (3 instances, including the related noun अनुमोदन→"intention") and KD-Karm-Darshan-English.md §3.16–3.18 (1 instance) on 2026-07-08</t>
+          <t>Settled per Raghava (2026-07-08), superseding this project's earlier "done, caused-to-be-done, and approved"/"consented-to." MD-Mapping's कृत="doing," कारित="getting done," अनुमोदित="consenting" — kept close but simplified; अनुमोदित specifically rendered "intended" rather than "approved"/"consenting" per this decision. Retrofitted in KD-Karm-Darshan-English.md §3.11–3.12 (3 instances, including the related noun अनुमोदन→"intention") and KD-Karm-Darshan-English.md §3.16–3.18 (1 instance) on 2026-07-08 Made project-wide by the author on 13 October 2026: MD-Mapping and the AA translation now follow it.</t>
         </is>
       </c>
     </row>
@@ -65851,7 +65968,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>CORRECTION, 2026-07-08: MD-Mapping has a direct row for bare दर्शन = "Holistic view, Worldview, Philosophy," plus confirmed compound rows सह-अस्तित्व दर्शन ज्ञान = "knowledge of holistic view of coexistence" and मानव कर्म दर्शन (this book's own title) = "Holistic view of Human Action." MVD independently confirms the exact KD 2 phrase: "अस्तित्व दर्शन ज्ञान" → "knowledge of the holistic view of existence" (MVD p.259, near-verbatim to KD 2's opening line). Retrofitted in KD-Karm-Darshan-English.md (ch. 2) (4 instances: the opening "अस्तित्व दर्शन ज्ञान," "(पूर्ण-दर्शन)," and two "दर्शन-क्षमता" instances) and in KD-Karm-Darshan-English.md (ch. 1) (10 instances, verified page-by-page against the source images: pp.1, 3, 13, 14, 15 (×2), 16 (×2 continuing to 17), 17 (×2)) on 2026-07-08. Excluded from this correction (kept as-is): the proper noun "Madhyasth Darshan" (book/philosophy name, p.19, always transliterated); the दृश/दृश्य/दर्शन seer-triad sense (KD 3.17, see separate row below, a distinct established convention); and the verbal usage "X का दर्शन करना" = "to behold X" (KD 1 p.24, four instances, e.g. "vritti... beholds the mind" — this is the common devotional-register verb "to behold/have sight of," not the noun "holistic view," and one redundant instance ("beholds the darshan of the less-awakened") was simplified to "beholds the less-awakened" accordingly</t>
+          <t>CORRECTION, 2026-07-08: MD-Mapping has a direct row for bare दर्शन = "Holistic view, Worldview, Philosophy," plus confirmed compound rows सह-अस्तित्व दर्शन ज्ञान = "knowledge of holistic view of coexistence" and मानव कर्म दर्शन (this book's own title) = "Holistic view of Human Action." MVD independently confirms the exact KD 2 phrase: "अस्तित्व दर्शन ज्ञान" → "knowledge of the holistic view of existence" (MVD p.259, near-verbatim to KD 2's opening line). Retrofitted in KD-Karm-Darshan-English.md (ch. 2) (4 instances: the opening "अस्तित्व दर्शन ज्ञान," "(पूर्ण-दर्शन)," and two "दर्शन-क्षमता" instances) and in KD-Karm-Darshan-English.md (ch. 1) (10 instances, verified page-by-page against the source images: pp.1, 3, 13, 14, 15 (×2), 16 (×2 continuing to 17), 17 (×2)) on 2026-07-08. Excluded from this correction (kept as-is): the proper noun "Madhyasth Darshan" (book/philosophy name, p.19, always transliterated); the दृश/दृश्य/दर्शन seer-triad sense (KD 3.17, see separate row below, a distinct established convention); and the verbal usage "X का दर्शन करना" = "to behold X" (KD 1 p.24, four instances, e.g. "vritti... beholds the mind" — this is the common devotional-register verb "to behold/have sight of," not the noun "holistic view," and one redundant instance ("beholds the darshan of the less-awakened") was simplified to "beholds the less-awakened" accordingly **Exception (13 October 2026):** अस्तित्व दर्शन ज्ञान = "knowledge of coexistence" by the author's project-wide decision (row below).</t>
         </is>
       </c>
     </row>
@@ -66556,6 +66673,94 @@
       <c r="D186" t="inlineStr">
         <is>
           <t>Settled per Raghava (2026-07-09): **not** "leisure." KD 1 p.14 (PDF p.39) glosses अवकाश (सम्भावना) → "opportunity (possibility)"; body/mind/wealth as means is itself opportunity; paired with अवसर ("occasion") in "necessity, occasion, and opportunity." Distinct from MD-Mapping's आकाश, अवकाश = "void" (space sense). MVD renders अवकाश एवम् अवसर as "opportunity and scope"</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>अस्तित्व दर्शन ज्ञान</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>astitva darshan gyan</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>knowledge of coexistence</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Project-wide decision of the author, 13 October 2026, first made for the AA translation (p. 12); supersedes MVD's "knowledge of the holistic view of existence" for this compound. Applied in the KD body at the front-matter list "10. The Knowledge" and KD pp. 30 and 69 (source images checked), where सहअस्तित्व रूपी अस्तित्व दर्शन ज्ञान reads "knowledge of coexistence (existence in the form of coexistence)". Bare अस्तित्व दर्शन and सहअस्तित्व दर्शन ज्ञान keep the दर्शन row's "holistic view" renderings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>स्वतंत्रता</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>svatantrata</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>independence</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Project-wide decision of the author, 13 October 2026, as in MD-Mapping and MVD ("identity, independence, and authority"). Changed from "freedom" at KD pp. 112, 148 (twice) and 149 (source images checked: स्वत्व, स्वतंत्रता, अधिकार; स्वतंत्रता का अनुभव). कर्म स्वतंत्रता stays "freedom of action" (MD).</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>संतुष्टि</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>santushti</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>contentment</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Project-wide decision of the author, 13 October 2026: shares "contentment" with संतोष (the jeevan value); where the distinction matters, the Hindi word is the guide.</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>सुविधा (public services)</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>suvidha</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>facilities</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Project-wide decision of the author, 13 October 2026, for सुविधा in the sense of village or public services (drinking water, school, roads, post office, bank). Elsewhere सुविधा = comfort(s).</t>
         </is>
       </c>
     </row>
@@ -68061,7 +68266,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>doing</t>
+          <t>done</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -68071,7 +68276,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Settled per Raghava (2026-07-08), superseding this project's earlier "done, caused-to-be-done, and approved"/"consented-to." MD-Mapping's कृत="doing," कारित="getting done," अनुमोदित="consenting" — kept close but simplified; अनुमोदित specifically rendered "intended" rather than "approved"/"consenting" per this decision. Retrofitted in KD-Karm-Darshan-English.md §3.11–3.12 (3 instances, including the related noun अनुमोदन→"intention") and KD-Karm-Darshan-English.md §3.16–3.18 (1 instance) on 2026-07-08</t>
+          <t>Settled per Raghava (2026-07-08), superseding this project's earlier "done, caused-to-be-done, and approved"/"consented-to." MD-Mapping's कृत="doing," कारित="getting done," अनुमोदित="consenting" — kept close but simplified; अनुमोदित specifically rendered "intended" rather than "approved"/"consenting" per this decision. Retrofitted in KD-Karm-Darshan-English.md §3.11–3.12 (3 instances, including the related noun अनुमोदन→"intention") and KD-Karm-Darshan-English.md §3.16–3.18 (1 instance) on 2026-07-08 Made project-wide by the author on 13 October 2026: MD-Mapping and the AA translation now follow it.</t>
         </is>
       </c>
     </row>
@@ -68083,7 +68288,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>getting done</t>
+          <t>caused</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -68093,7 +68298,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Settled per Raghava (2026-07-08), superseding this project's earlier "done, caused-to-be-done, and approved"/"consented-to." MD-Mapping's कृत="doing," कारित="getting done," अनुमोदित="consenting" — kept close but simplified; अनुमोदित specifically rendered "intended" rather than "approved"/"consenting" per this decision. Retrofitted in KD-Karm-Darshan-English.md §3.11–3.12 (3 instances, including the related noun अनुमोदन→"intention") and KD-Karm-Darshan-English.md §3.16–3.18 (1 instance) on 2026-07-08</t>
+          <t>Settled per Raghava (2026-07-08), superseding this project's earlier "done, caused-to-be-done, and approved"/"consented-to." MD-Mapping's कृत="doing," कारित="getting done," अनुमोदित="consenting" — kept close but simplified; अनुमोदित specifically rendered "intended" rather than "approved"/"consenting" per this decision. Retrofitted in KD-Karm-Darshan-English.md §3.11–3.12 (3 instances, including the related noun अनुमोदन→"intention") and KD-Karm-Darshan-English.md §3.16–3.18 (1 instance) on 2026-07-08 Made project-wide by the author on 13 October 2026: MD-Mapping and the AA translation now follow it.</t>
         </is>
       </c>
     </row>
@@ -68105,7 +68310,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>consenting</t>
+          <t>intended</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -68115,7 +68320,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Settled per Raghava (2026-07-08), superseding this project's earlier "done, caused-to-be-done, and approved"/"consented-to." MD-Mapping's कृत="doing," कारित="getting done," अनुमोदित="consenting" — kept close but simplified; अनुमोदित specifically rendered "intended" rather than "approved"/"consenting" per this decision. Retrofitted in KD-Karm-Darshan-English.md §3.11–3.12 (3 instances, including the related noun अनुमोदन→"intention") and KD-Karm-Darshan-English.md §3.16–3.18 (1 instance) on 2026-07-08</t>
+          <t>Settled per Raghava (2026-07-08), superseding this project's earlier "done, caused-to-be-done, and approved"/"consented-to." MD-Mapping's कृत="doing," कारित="getting done," अनुमोदित="consenting" — kept close but simplified; अनुमोदित specifically rendered "intended" rather than "approved"/"consenting" per this decision. Retrofitted in KD-Karm-Darshan-English.md §3.11–3.12 (3 instances, including the related noun अनुमोदन→"intention") and KD-Karm-Darshan-English.md §3.16–3.18 (1 instance) on 2026-07-08 Made project-wide by the author on 13 October 2026: MD-Mapping and the AA translation now follow it.</t>
         </is>
       </c>
     </row>

--- a/References/Madhyasth-Darshan/KD-Karm-Darshan-English/KD-Translation-Glossary.xlsx
+++ b/References/Madhyasth-Darshan/KD-Karm-Darshan-English/KD-Translation-Glossary.xlsx
@@ -911,7 +911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2309"/>
+  <dimension ref="A1:K2310"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="13.4399995803833" defaultRowHeight="15"/>
   <cols>
     <col width="23.21999931335449" customWidth="1" style="114" min="1" max="1"/>
@@ -62471,7 +62471,7 @@
       </c>
       <c r="F2306" s="0" t="inlineStr">
         <is>
-          <t>AA glossary addition (project-wide decision of the author, 13 October 2026), following the author's wording on AA p. 12. Supersedes MVD's 'knowledge of the holistic view of existence' (MVD p. 259) for this compound; bare अस्तित्व दर्शन and सह-अस्तित्व दर्शन ज्ञान are unchanged.</t>
+          <t>AA glossary addition (project-wide decision of the author, 13 October 2026), following the author's wording on AA p. 12. Supersedes MVD's 'knowledge of the holistic view of existence' (MVD p. 259) for this compound; bare अस्तित्व दर्शन = holistic view of existence (row 2310); सह-अस्तित्व दर्शन ज्ञान is unchanged.</t>
         </is>
       </c>
       <c r="I2306" s="0" t="inlineStr">
@@ -62558,6 +62558,33 @@
       <c r="I2309" s="0" t="inlineStr">
         <is>
           <t>AA-Glossary-Additions.md; AA chapter 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="2310">
+      <c r="A2310" s="0" t="inlineStr">
+        <is>
+          <t>अस्तित्व दर्शन</t>
+        </is>
+      </c>
+      <c r="B2310" s="0" t="inlineStr">
+        <is>
+          <t>holistic view of existence</t>
+        </is>
+      </c>
+      <c r="C2310" s="0" t="inlineStr">
+        <is>
+          <t>astitva darshan</t>
+        </is>
+      </c>
+      <c r="F2310" s="0" t="inlineStr">
+        <is>
+          <t>Decision of the author, 13 October 2026, for bare अस्तित्व दर्शन (without ज्ञान): follows KD (दर्शन = the holistic view of X, settled 8 July 2026), row 566 (दर्शन = holistic view) and MVD p. 259. Replaces AA's earlier 'the darshan of existence'. With ज्ञान, see row 2306.</t>
+        </is>
+      </c>
+      <c r="I2310" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA pp. 14, 15, 23, 38, 47, 65, 66, 76, 82, 85, 94, 95, 99, 108, 115; KD-Glossary-Additions.md</t>
         </is>
       </c>
     </row>
@@ -65968,7 +65995,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>CORRECTION, 2026-07-08: MD-Mapping has a direct row for bare दर्शन = "Holistic view, Worldview, Philosophy," plus confirmed compound rows सह-अस्तित्व दर्शन ज्ञान = "knowledge of holistic view of coexistence" and मानव कर्म दर्शन (this book's own title) = "Holistic view of Human Action." MVD independently confirms the exact KD 2 phrase: "अस्तित्व दर्शन ज्ञान" → "knowledge of the holistic view of existence" (MVD p.259, near-verbatim to KD 2's opening line). Retrofitted in KD-Karm-Darshan-English.md (ch. 2) (4 instances: the opening "अस्तित्व दर्शन ज्ञान," "(पूर्ण-दर्शन)," and two "दर्शन-क्षमता" instances) and in KD-Karm-Darshan-English.md (ch. 1) (10 instances, verified page-by-page against the source images: pp.1, 3, 13, 14, 15 (×2), 16 (×2 continuing to 17), 17 (×2)) on 2026-07-08. Excluded from this correction (kept as-is): the proper noun "Madhyasth Darshan" (book/philosophy name, p.19, always transliterated); the दृश/दृश्य/दर्शन seer-triad sense (KD 3.17, see separate row below, a distinct established convention); and the verbal usage "X का दर्शन करना" = "to behold X" (KD 1 p.24, four instances, e.g. "vritti... beholds the mind" — this is the common devotional-register verb "to behold/have sight of," not the noun "holistic view," and one redundant instance ("beholds the darshan of the less-awakened") was simplified to "beholds the less-awakened" accordingly **Exception (13 October 2026):** अस्तित्व दर्शन ज्ञान = "knowledge of coexistence" by the author's project-wide decision (row below).</t>
+          <t>CORRECTION, 2026-07-08: MD-Mapping has a direct row for bare दर्शन = "Holistic view, Worldview, Philosophy," plus confirmed compound rows सह-अस्तित्व दर्शन ज्ञान = "knowledge of holistic view of coexistence" and मानव कर्म दर्शन (this book's own title) = "Holistic view of Human Action." MVD independently confirms the exact KD 2 phrase: "अस्तित्व दर्शन ज्ञान" → "knowledge of the holistic view of existence" (MVD p.259, near-verbatim to KD 2's opening line). Retrofitted in KD-Karm-Darshan-English.md (ch. 2) (4 instances: the opening "अस्तित्व दर्शन ज्ञान," "(पूर्ण-दर्शन)," and two "दर्शन-क्षमता" instances) and in KD-Karm-Darshan-English.md (ch. 1) (10 instances, verified page-by-page against the source images: pp.1, 3, 13, 14, 15 (×2), 16 (×2 continuing to 17), 17 (×2)) on 2026-07-08. Excluded from this correction (kept as-is): the proper noun "Madhyasth Darshan" (book/philosophy name, p.19, always transliterated); the दृश/दृश्य/दर्शन seer-triad sense (KD 3.17, see separate row below, a distinct established convention); and the verbal usage "X का दर्शन करना" = "to behold X" (KD 1 p.24, four instances, e.g. "vritti... beholds the mind" — this is the common devotional-register verb "to behold/have sight of," not the noun "holistic view," and one redundant instance ("beholds the darshan of the less-awakened") was simplified to "beholds the less-awakened" accordingly **Exception (13 October 2026):** अस्तित्व दर्शन ज्ञान = "knowledge of coexistence" by the author's project-wide decision (row below). **Confirmed (13 October 2026):** bare अस्तित्व दर्शन, without ज्ञान, stays "the holistic view of existence"; the author adopted this KD rendering for AA too (MD-Mapping row 2310).</t>
         </is>
       </c>
     </row>

--- a/References/Madhyasth-Darshan/KD-Karm-Darshan-English/KD-Translation-Glossary.xlsx
+++ b/References/Madhyasth-Darshan/KD-Karm-Darshan-English/KD-Translation-Glossary.xlsx
@@ -911,7 +911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2310"/>
+  <dimension ref="A1:K2311"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="13.4399995803833" defaultRowHeight="15"/>
   <cols>
     <col width="23.21999931335449" customWidth="1" style="114" min="1" max="1"/>
@@ -21802,7 +21802,7 @@
       </c>
       <c r="B650" s="28" t="inlineStr">
         <is>
-          <t>societal participation</t>
+          <t>social participation</t>
         </is>
       </c>
       <c r="C650" s="117" t="inlineStr">
@@ -21818,12 +21818,16 @@
       </c>
       <c r="F650" s="120" t="inlineStr">
         <is>
-          <t>societal functioning</t>
+          <t>societal functioning; [Updated "societal participation" -&gt; "social participation" per author decision, 2026-10-16, aligning with JV p. 154.]</t>
         </is>
       </c>
       <c r="G650" s="121" t="n"/>
       <c r="H650" s="121" t="n"/>
-      <c r="I650" s="121" t="n"/>
+      <c r="I650" s="121" t="inlineStr">
+        <is>
+          <t>JV p. 154; AA pp. 72, 94, 114, 116; KD pp. 115-116</t>
+        </is>
+      </c>
       <c r="J650" s="40" t="n"/>
       <c r="K650" s="40" t="n"/>
     </row>
@@ -62585,6 +62589,33 @@
       <c r="I2310" s="0" t="inlineStr">
         <is>
           <t>AA-Glossary-Additions.md; AA pp. 14, 15, 23, 38, 47, 65, 66, 76, 82, 85, 94, 95, 99, 108, 115; KD-Glossary-Additions.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="2311">
+      <c r="A2311" s="0" t="inlineStr">
+        <is>
+          <t>समझदार परिवार</t>
+        </is>
+      </c>
+      <c r="B2311" s="0" t="inlineStr">
+        <is>
+          <t>wise family</t>
+        </is>
+      </c>
+      <c r="C2311" s="0" t="inlineStr">
+        <is>
+          <t>samajhdar parivar</t>
+        </is>
+      </c>
+      <c r="F2311" s="0" t="inlineStr">
+        <is>
+          <t>Project-wide decision of the author, 16 October 2026: wise family for समझदार परिवार, replacing earlier "understanding family" / "understanding-endowed family".</t>
+        </is>
+      </c>
+      <c r="I2311" s="0" t="inlineStr">
+        <is>
+          <t>AA-Glossary-Additions.md; AA pp. 27, 120; KD-Glossary-Additions.md; KD p. 115</t>
         </is>
       </c>
     </row>
@@ -62602,7 +62633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D190"/>
+  <dimension ref="A1:D192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" style="114" min="1" max="1"/>
@@ -66788,6 +66819,50 @@
       <c r="D190" t="inlineStr">
         <is>
           <t>Project-wide decision of the author, 13 October 2026, for सुविधा in the sense of village or public services (drinking water, school, roads, post office, bank). Elsewhere सुविधा = comfort(s).</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>समाज गति</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>samaj gati</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>social participation</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Project-wide decision of the author, 16 October 2026, aligning with Rakesh Gupta's JV p. 154 rendering ("nourishment and protection of our body and social participation") and replacing "societal motion" / "the motion of society" / "societal participation".</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>समझदार परिवार</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>samajhdar parivar</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>wise family</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Project-wide decision of the author, 16 October 2026 ("use 'wise family' instead of 'understanding family'"), replacing "understanding family" / "understanding-endowed family" (KD p. 115; AA pp. 27, 120).</t>
         </is>
       </c>
     </row>
